--- a/MECE_순수고충_v2_댓글검증_전수.xlsx
+++ b/MECE_순수고충_v2_댓글검증_전수.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="마스터_VOC_3배확장" sheetId="1" r:id="rId1"/>
+    <sheet name="마스터_VOC_귀농귀촌포함" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7882" uniqueCount="3648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9454" uniqueCount="4306">
   <si>
     <t>no</t>
   </si>
@@ -10958,6 +10958,1980 @@
   </si>
   <si>
     <t>https://cafe.naver.com/givemecsplz/21746</t>
+  </si>
+  <si>
+    <t>6-1.농작업노동_근골격계손상_만성통증</t>
+  </si>
+  <si>
+    <t>Persona 6 (귀농·귀촌 정착인)</t>
+  </si>
+  <si>
+    <t>귀농 허리 통증</t>
+  </si>
+  <si>
+    <t>허리 아파 보신분 계신가요?</t>
+  </si>
+  <si>
+    <t>저는 오늘 허리가 아파서 꼼짝을 못하겠어요. 왜 아픈지 몰겠어요. 다친것도 아닌데 자고 일어나니 허리가 아파서 뒹굴뒹굴 거리면서 종일 방에 누워 있었답니다. 평생을 안아프던 허리가 첨에는 고사리를 뜯을때 아파서 허리를 펴주고 펴주면 괜찮으니 또 뜯고 했는데 고사리를 안 뜯어서 괜찮았는데 이렇게 많이 아프기는 첨인것 같아요. 병원가는걸 싫어하는데 너무 아파서 한의원 가서 침을 맞으려니 토요일이라서...</t>
+  </si>
+  <si>
+    <t>RE아유 고생하시네요 저도 전에 허리 많이 아팠는데요 우선 수건 적셔서 전자레인지에 3~4분 돌리세요 큰 지퍼백에 넣어 수건 덮고 허리에 대고 누워보세요 우선 급하니까요 내일 일요일이라 어쩌죠</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/happyparm/612726</t>
+  </si>
+  <si>
+    <t>허리 통증 덜하네요</t>
+  </si>
+  <si>
+    <t>허리 통증이 있어서 병원 계속 다녔는데 조금씩 관리도 해야할거같아서 영양제 먹고있네요 류마티스에도 좋다고해서 동생 선물할까 싶어요 선물하기도 좋게 생겨서 괜찮을듯 해요 콘드릭스 알 크기도 크지 않고 개별포장되어 있어서 휴대하기도 편하니까 외출시 들고다니기도 좋아서 꾸준히 먹으면서 관리 제대로 해야겠어요</t>
+  </si>
+  <si>
+    <t>RE저도 요즘 손가락 통증이 좀 있는데 그거에도 좋나요?</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/441948</t>
+  </si>
+  <si>
+    <t>초반엔 하루 종일 앓았는데 이제 몸이 좀 적응한듯 보여요</t>
+  </si>
+  <si>
+    <t>귀농 처음 했을 때는 오전에 밭일 몇 시간만 해도 저녁이면 허리랑 다리가 쑤셔서 아무것도 하기 싫었거든요 근데 요즘은 아침부터 어머니 따라 밭에 나가서 이것저것 하고 들어와도 예전처럼 바로 뻗지는 않네요 오늘도 오전 내내 쪼그려 앉았다 일어났다 반복했는데 점심 먹고 나니까 생각보다 몸이 멀쩡해서 저도 신기합니다 어머니한테 이제 저도 농사꾼 다 된 것 같다고 했더니 아직 멀었다고 바로...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/whduddn0317/1422569</t>
+  </si>
+  <si>
+    <t>딸내미 허리꿈틀 통증 입퇴원</t>
+  </si>
+  <si>
+    <t>금욜 밤에 딸내미 허리가 꿈틀 응급실 입원 며칠 정신 없어서 눈팅만하고 씨앗 차비나눔거에만 댓글달고 퇴원은 하라해서 하긴했는데 아직 허리는 아파서 구부리지는 못하네요 금욜은 걷지도 제대로 못하고 돌려눕는것도 화장실가서못내리는것도 못하고 큰일이다 싶었는데 mri상 다행히 디스크는 크게이상없고 조금 부은정도 허리에 통증주사 맞고서 걷는건 되어서 퇴원은 했어요 정형외과 외래라도 가서 물치라도...</t>
+  </si>
+  <si>
+    <t>RE침 잘 놓는곳 아시면 그리로 가세요. 정형외과 물리치료보다 침이 더 나을거에요~ 집에서 찜질 자주 해주시구요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/happyparm/613163</t>
+  </si>
+  <si>
+    <t>발(발가락)운동으로 건강유지하기</t>
+  </si>
+  <si>
+    <t>다이어트/영양제/식단관리/스트레칭/눈건강/허리통증/어깨결림/무릎관절/손목터널증후군/거북목교정/피부관리/불면증/만성피로/소화불량/혈당관리/은퇴 후 50년</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/eovhskfktmak/22562</t>
+  </si>
+  <si>
+    <t>고령 척추환자</t>
+  </si>
+  <si>
+    <t>나이를 먹으면 먹을수록 많은 사람들이 자연스레 척추관협착증에 걸리는 경우가 많은데 그 병이 허리 뿐만 아니라 골반을 따라 다리까지... 다쳐 허리를 수술하고 딱 1년 만에 뇌출혈로 또 수술을 받았는데 의사가 나를 보고 또라이라고 옆에 오는거 자체를 싫어할 정도로 섬망이... 마지막으로 허리는 하체만 튼튼하면 재수없게 다치는 경우를 제외하고는 노인성 질환으로 허리에 생기는 질환은 거의 예방할수 있다고...</t>
+  </si>
+  <si>
+    <t>RE통증이 많으신가 봅니다 마약성 진통제와 패치를 사용하시는거 보니. 저도 마약성 진통제를 많이 써서 환각증세도 느낀적 있으며 마약성진통제 안쓰면 통증때문에 고통스러웠던 기억이 있습니다. 쾌유를 기원합니다</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/442200</t>
+  </si>
+  <si>
+    <t>허리 아프신 분, 아프셨던 분</t>
+  </si>
+  <si>
+    <t>어떻게 치료 하고 계세요?. 심한 통증은 아니지만 좌측 허리가 살살 통증이 오네요. 일주일에 5일 정도는 조깅 7킬로, 등산(60분), 근육운동(30분)을 하고 있습니다. 그동안 무릎에 통증이 조금 있었는데 요즘엔 허리까지 아파오네요. 이정도에 병원을 갈 정도는 아니라고 생각하고 있는데 혹시, 자가 치료를 하신 분들은 어떤 방법을 취하셨을까요?</t>
+  </si>
+  <si>
+    <t>RE원인과 진단에 따라 치료가 다를진데...일단 병원부터 가십시오 제 경우엔 침대가 원인이었슴당 10년후에 알게됐어요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/438393</t>
+  </si>
+  <si>
+    <t>마취통증의학과나 정형외과에서 허리 시술시 겁나시는 분!!</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Gl-PgpCQ5Vk</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/440671</t>
+  </si>
+  <si>
+    <t>철봉 매달리기로 허리 통증 많이 좋아졌어요</t>
+  </si>
+  <si>
+    <t>5-6년 전부터 골프 라운딩 후에는 허리 통증으로 물리 치료를 1-2주 받았어야 했는데, 금욜 라운딩후에는 통증이 크게 오지 않네요. 올초부터 철봉 매달리기를 아침 저녁으로 한게 통증 완화에 큰 도움이 된 듯 합니다. 과거에는 닥터 디스크로 허리 이완하며 통증을 완화시켰는데 지금은 그냥 철봉 매달리기로 허리 이완 시키고 있습니다. 여름이라서 핫팩 및 찜질은 도저히 못하겠어요 ㅠㅠ 허리 아프신 분들 밑져야...</t>
+  </si>
+  <si>
+    <t>RE나는 빨래요 느낌으로 매달립니다.턱걸이 하면 용을 써야되서 허리가 뻐근해서 안합니다</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/413495</t>
+  </si>
+  <si>
+    <t>허리가 아파서</t>
+  </si>
+  <si>
+    <t>갑자기 허리가 아파서 쩔쩔매는데 저녁약속시간은 다가오고 맨소래담 처발처발하고 나갔다 들어 오는길에 걸었더니 허리에 골반도 뻐근하더라구요, 십분여를 걸으니 골반도 풀리고 허리도 덜 아프더라구요. 이번주 내 공부한다고 앉아있기만한게 탈이 난건가봐요. 옆지기는 운동부족이라고 나도 알지만 인정하기 싫어서 대답안하니 운동하라고 계속 말하며 집에 와서 씻고 누우려니 움직여야된다고 복숭아 달라는 참...</t>
+  </si>
+  <si>
+    <t>RE허리가 아프면 정말 힘들더라구요~~ 복숭아달라는 착한 남편이십니다 ㅎㅎㅎ 얼른 쾌차하시길 바랍니다 저희집에는 허리아프다는 마누라님한테 손주들 봐주러가자고 하는 엄청 착한 할아버지가 있습니다 ㅎㅎ</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/happyparm/607261</t>
+  </si>
+  <si>
+    <t>40대 통증의 원인! 허리디스크예방 자세 7가지와 자가 점검법</t>
+  </si>
+  <si>
+    <t>오늘 소개해 드린 허리디스크예방 자세 7가지 중 단 하나라도 일상에 적용하여 아침이 가벼워지는 변화를 경험해 보세요. 궁금한 점이나 더 좋은 허리디스크예방법이 있다면 댓글로 저한테도 공유 부탁드립니다^^ 다이어트/영양제/식단관리/스트레칭/눈건강/허리통증/어깨결림/무릎관절/손목터널증후군/거북목교정/피부관리/불면증/만성피로/소화불량/혈당관리/은퇴 후 50년</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/eovhskfktmak/11743</t>
+  </si>
+  <si>
+    <t>허리통증 어떻게 치료들 하시나요?ㅜ</t>
+  </si>
+  <si>
+    <t>예전엔 의자에 오래 앉아 있으면 허리가 쑤시는게 있었는데 요즘은 오래 앉아 있지도 않는데 허리통증이 있네요ㅜ 혹시 이건 어떻게들 치료 하셨나요?</t>
+  </si>
+  <si>
+    <t>RE근력 운동해서 허리 근육을 키우는 수 밖에 없어요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/396301</t>
+  </si>
+  <si>
+    <t>25평 텃밭이면 관리기 필요한가요?</t>
+  </si>
+  <si>
+    <t>아직 제가 직접 밭갈이를 안해봤고 이제 내년 농사위해 밭갈이 걱정이 슬슬 드네요 25평(7×10미터)정도 면적이면 혼자 삽으로 할만한가요 아니면 관리기로 해야 할까요? 조언구합니다</t>
+  </si>
+  <si>
+    <t>RE제같으면 미니관리기 씁니다. 물론 삽으로 가능합니다.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1341975</t>
+  </si>
+  <si>
+    <t>안양 교통사고한의원 갑작스러운 통증</t>
+  </si>
+  <si>
+    <t>이런 손상이 발생하면 목 부위에만 통증이 국한되지 않고 어깨 주변 근육까지 과도하게 긴장하면서 근육통으로 이어지곤 합니다. 더불어 목과 맞닿은 척추 전체의 움직임이 둔해지고, 심해지면 목디스크나 허리디스크로까지 발전할 가능성이 있습니다. 교통사고 후유증이란 사고를 겪은 뒤 몸 전반에 나타나는 다양한 이상 증상을 일컫는 말입니다. 그중에서도 앞서 언급한 근골격계 통증이 가장 흔하게 나타나는...</t>
+  </si>
+  <si>
+    <t>RE사고 직후엔 멀쩡하다가 며칠 지나서 갑자기 아픈 게 어혈 때문일 수 있다는 걸 이번에 처음 알았어요. 한약이랑 추나를 같이 하는 이유도 차근차근 풀어주셔서 이해가 쉬웠습니다. 안양 근처에서 사고 후 통증 때문에 고민하시는 분들한테 도움 많이 될 것 같아요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/443191</t>
+  </si>
+  <si>
+    <t>허리 디스크탈출로</t>
+  </si>
+  <si>
+    <t>하루 온종일 허리에서부터 발끝까지 방사통 통증에 시달리다가 다른 종합병원으로 향했었더랬죠 MRA 상 등뼈 5 6번 디스크탈출이라구요 시술을 권하는데 마음이 내키지않더라는요 12년전, 항암 방사선 표적치료 18차례까지 할 땐 마음이 완전히 내려놓아지던데 ... 요번엔 통증중에도 방법이있을것만 같았네요 일주일치 약만 처방받아서 대소변이 자유롭지못할땐 언제든오라고 .. 감사하게도 대소변은...</t>
+  </si>
+  <si>
+    <t>RE안녕하세요 허리 통증이 심하시네요. 일단은 치료 해야 겠어요. 아프면 아무것도 못하고 서럽고 그동안 했던일 안해야 합니다. 치료 하시기 바랍니다</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/happyparm/607439</t>
+  </si>
+  <si>
+    <t>나이 먹으면 원래 정형외과에서 X레이나 MRI로는 보이지 않는 통증들이 이것저것 생기나요?</t>
+  </si>
+  <si>
+    <t>있을때 통증 있거나 그런건 아니구 발 디딜때마다 오른쪽 발등이 삐긋한것처럼 느껴지더라구요 정형외과 가서 엑스레이 찍어보니... 지나니 통증이 말끔히 없어졌고 저는 100퍼센트 회복된걸로 생각했고 약 복용을 중단 하였습니다 근데 약 복용 중단하고 3-4일 정도 지나니깐 약 효과가 떨어졌는건지 발 디딜때 다시 통증이 오더라구요 그래서 약을 한달 가까이 복용했는데 약 복용만 중단하면 다시 발...</t>
+  </si>
+  <si>
+    <t>RE제 부모님과 친구도 모르는 병명을 큰 병원 동네병원 포함 10군데 가까이 다니다 원인을 알게된 경우도 있었습니다.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/425511</t>
+  </si>
+  <si>
+    <t>안마의자 구입 할까요.</t>
+  </si>
+  <si>
+    <t>아침 저녁으로 쌀쌀하네요. 안마의자 구입에 망설이고 있네요. 울마님이 안마 받는걸 뫃아해요. 업소가아닌 남편인 저에게요. 아침에 일어나면 제일먼저 안마을 해주거든요 그런지가 꾀나 오래 되었네요. 사실 허리 디스크파열로 수술을 했는데 수술했어도 계속 힘들어 하네요 그랴서 언머의자를 구입할까 고민하는데 혹시 추천해주고픈 안마의자나 사용해보신 좋은제품 있을까요. 감사합니다.</t>
+  </si>
+  <si>
+    <t>RE요즘 안마의자는 좋은 기능이 많아서 손 안마보다 더 효과가 좋을거예요. 저는 아주 옛날식 안마기 쓰는데 피로회복은 물론 운동효과까지 만족해요. 망가지면 좋은제품 구매할 예정인데 다만 안마의자 부피가 부담스럽게 느껴져요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/435254</t>
+  </si>
+  <si>
+    <t>허리와 테니스..........</t>
+  </si>
+  <si>
+    <t>10년 전부터 허리 즉 정확하게는 좌측 골반뼈 상단 등쪽으로 그 지점이 아파오기 시작한 것이다. 처음에는 원인도 모른체 그냥 뭐 운전을 오래 해서 그런가? 의자에 삐딱하게 앉아서 그런가? 짐작만 했다, 5년 전부터는 점 점 더 아파왔고, 곰곰히 연구해보니 테니스 때문에 생기는 병임을 알았다. 한쪽 방향의 운동인 테니스 때문이다. 오른손 왼손 반반씩 사용한다면 괜찮았겠지만 나는 오른손 잡이라서 아무리...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/437908</t>
+  </si>
+  <si>
+    <t>신장이 안좋으면 증상이 어떤가요 ?</t>
+  </si>
+  <si>
+    <t>동생이 허리가 많이 아프다고 하는데 운동하다가 삐끗했다고 함니다 병원에서 MRI까지 해봤는데 허리는 별 이상은 없다고 하는데 (오빠인 저에게 이야기하기 좀 그래서인지 그냥 둘러대는 듯한 느낌임니다) 혹시 신장쪽에 문제가 있지 않을까 해서요 물론 검사 해보면 당연히 알겠지만 신장이 안좋으면 (예를 들어 심한 염증) 허리도 아프죠 ?</t>
+  </si>
+  <si>
+    <t>RE그렇지 않습니다. 운동하다가 삐긋했는데 신장이 안좋다?? 도저히 이해가 안가는 추론입니다.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/438454</t>
+  </si>
+  <si>
+    <t>노부모 선물 세라잼 선물 괜찮나요?</t>
+  </si>
+  <si>
+    <t>70중반 부모님께서 이번에 재개발된 신축에 입주하시는데, 이것저것 생각해보다, 세라잼(약 670만원) 해드릴려고하는데요. 척추협착증을 앓고 계셔요. 해드려도 될련지..... 조금 나아지는지.....써보신분들 궁금합니다.</t>
+  </si>
+  <si>
+    <t>RE사위가 700만원 짜리 안마기 사줬는데 거의 안씁니다. 50평집 거실에서 자리만 차지 하네요 그냥 현금으로 드리시는 것이 어떨런지요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/436885</t>
+  </si>
+  <si>
+    <t>창동 교통사고한의원 완화를 위해서</t>
+  </si>
+  <si>
+    <t>교통사고 후유증으로 흔히 나타나는 증상은 목, 허리, 어깨, 무릎, 손목과 발목 등 근골격계 부위의 통증입니다. 이 외에도 내부 장기나 조직이 충격을 받아 소화불량, 메스꺼움, 구토, 입맛 저하, 생리통 등이 생기기도 하고, 두통이나 어지럼증, 이명, 손발 저림, 만성적인 피로감이 동반되기도 합니다. 더불어 눈에 보이지 않는 심리적 불편감이 후유증으로 남는 경우도 적지 않습니다. 저희 창동 교통사고한의원에서는...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/443135</t>
+  </si>
+  <si>
+    <t>텃밭과 정원 가꾸는 님과 변비 있는 님들은 보세요ᆢ</t>
+  </si>
+  <si>
+    <t>자연을 힐링하면서 건강 할려고 시골 왔는데... ㅠㅜ 건강은 건강할때 지켜야 하고 건강이 망가지면 노후는 후회와 고통속에 살야야 합니다 ᆢㅠㅜ 아래 그림은 도서관에서 책을 뒤적이다가 참고들 하시라고 ᆢㅎ 배변이 어려운 님들은 참고 하세요 다음은 세수할때 이런 자세로 하면 허리 통증이 덜합니다 https://naver.me/FmGhxAu3</t>
+  </si>
+  <si>
+    <t>RE아주 유용한 팁주셔서 감사합니다 바깥 공기가 상쾌하게 느껴지는 아침입니다 오늘도 행복하게 보내세요 ~~~</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1334482</t>
+  </si>
+  <si>
+    <t>고생끝에 얻은 아픔(허리디스크)</t>
+  </si>
+  <si>
+    <t>당장 저리고 아픈게 사라졌단다 3주간 허리 복대를 차고 잘 회복하면 다시 일상생활은 가능하겠다만 절대로 무거운거 들거나 무리한 작업을 하면 안된단다 디스크는 재발 가능성이 매우 높은 질병이라고 하니 군민님의 직업을 바꾸어야 할거 같다 집수리를 혼자 다 하고선 곧장 일터로 나가 또 같은 일을 반복적으로 하였더니 몸이 과부하가 걸렸는데도 참고 일을 계속한 결과는 더이상 나좀 아껴줘 라는 몸의...</t>
+  </si>
+  <si>
+    <t>RE너무 무리하셨나봐요 저도 2월에 건조된 소나무 지붕해체 작업하느라 힘들어 죽는줄 알았어요 ~ㅜㅜ 디스크 재발위험이 높다고 하니 조심히 일하세요 가능한 당분간 쉬시는걸 권고드립니다 몸 관리 잘하세요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1319314</t>
+  </si>
+  <si>
+    <t>병원에선 죄책감 갖지말라하는데ㅠ</t>
+  </si>
+  <si>
+    <t>안녕하세요 많은정보를 얻고있던중 답답한 마음에 글을 올립니다 현재 82세 친정어머니 요양병원에 계십니다 당뇨 합병증으로 작년6월에 담낭이 염증이 심해 터져 배액술과 담낭제거술도 하니고 12월에 전신마비증세와 목 통증으로 응급실내원하여 경막하 농양으로 경추뼈가녹아내려 응급으로 두번 수술하셨습니다 강압술및기기고정수술하시고한달만에 퇴원하셔셔 요양병원에서 재활하시던중 올8월 허리통증과...</t>
+  </si>
+  <si>
+    <t>RE내버려두면 며칠 후에 의식불명 상태로 빠질 것입니다. 그렇게 하는 것이 환자 본인에게도 좋은 것이지요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/438308</t>
+  </si>
+  <si>
+    <t>주식한다고 차트만 하루10시간이상..</t>
+  </si>
+  <si>
+    <t>그렇게 컴퓨터 앞에 기본 8시간은 이상하고 주말에는 12시간도 넘어가네요 그러다 보니까 뒷목이랑 어깨랑 허리가 뻐근해지고 그러네요. 특히 뒷목이 뻐근하다보니까 머리까지 지끈거려서 오래 하지도 못하고 요즘에는 픽픽 쓰러집니다.. 나이때문인지..참.. 뒷목 뻐근하고 머리 아픈건 몇주전에 딸이 알려준대로집에서 마사지랑 스트레칭 살살 해주니까 많이 좋아지긴했는데 허리는 여전히 아프네요. 오른쪽 허리가...</t>
+  </si>
+  <si>
+    <t>RE요즈음 같은 경기에는 맨탈관리가 최고 인 것 같습니다. 건강관리 잘 하셔서 좋은정보 있으시면 공지해 주세요...^-^</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/413389</t>
+  </si>
+  <si>
+    <t>등이랑 허리가 ...</t>
+  </si>
+  <si>
+    <t>며칠 아니 한달이 넘게 등이랑 허리가 통증이 있는데 한의원 잘하는 곳이 없네요... 식자재마트 1충에 가게가 자주 바뀌어요. 얼마전까지 호두과자랑 커피 판매 하는 가게였는데 성빙으로 바뀌네요~ 살아가는 이야기, 이방은 제목에 맞지 않는 글이 넘쳐 운영진이 일일히 게시물과 맞는 메뉴로 이동을 하고 있습니다. 글을 올리시기 전에 본인의 게시물을 검토하시고, 되도록 글 속성에 맞는 게시판에 글을 올려 주시기...</t>
+  </si>
+  <si>
+    <t>RE정형외과에 물리치료ㆍ허리주사 맞으면 1년은 괜찮은거 같아요 허리 얼른 낫으시길요 ㆍㆍ</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/happyparm/604797</t>
+  </si>
+  <si>
+    <t>귀촌 무릎 관절염</t>
+  </si>
+  <si>
+    <t>퇴행성 관절염 극복기ㅡ7</t>
+  </si>
+  <si>
+    <t>혹시라도 귀농,귀촌에 관심있는 분들 게시면 도움 될까 싶어서요. 도시생활에 찌들리다 보니 훌훌털어버리고 시골로 내려갈까? 하는 생각 한두번 안하본 사람 없을거예요. 그러나 충분한 자금과 귀농후 확실한 수입원이 준비되지 않은 상태에서 귀농을 결심한다는건 결코 쉽지 않죠. 저도 마찬가지 입니다. 귀농을 하고는 싶었지만 자금도 없고 농사에 대해 암것도 모르는 저로서는 걱정이 많았죠. 그러나 제...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kwbc98/2034</t>
+  </si>
+  <si>
+    <t>무릎통증_관절염_하루한스푼으로통증완화_기적의 자연습관</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/q69/1125028</t>
+  </si>
+  <si>
+    <t>나이들수록 역세권 슬세권이 아닌 병세권으로</t>
+  </si>
+  <si>
+    <t>어머니는 무릎에 류마티즘 관절염이 있으셔서 그 부분부터 살폈네요 외국 음식이 짜고 달다보니 혈당이 좀 높아져 주치의 선생님께 혼나고 나오셨답니다 한국 돌아오고 나서는 다시 규칙적으로 생활하고... 하고싶다, 귀촌하고 싶다, 귀농하고 싶다 이런 분들 많잖아요 물론 귀촌 귀농 다 좋지만 나이 들수록 병세권이 중요하다 싶습니다 돌아가실 때까지 제주도 있겠다 하시니.. 다시 서울로 올라오시진 않더라도...</t>
+  </si>
+  <si>
+    <t>RE제주도 계신 지인도 아프면 육지로 나오시더라구요. 병원이 좀 열악하다고 하시네요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/eovhskfktmak/16715</t>
+  </si>
+  <si>
+    <t>류머티즘 관절염의 건강상식 정보</t>
+  </si>
+  <si>
+    <t>류머티즘 관절염 1. 원인 류머티즘은 한대나 열대 지방에서는 별로 발병하지 않는다. 습기가 높고 기후의 변화가 많으며 채광이 좋지 못한 지방에서 많이 일어나며, 우리나라도 발병하기 쉬운 조건을 구비하고 있다고 볼 수 있다. 발열과 신체의 여기저기 관절에 통증이 오게 되는 데, 류머티즘이 가장 많이 일어나는 관절은 역시 평소에 제일 많이 사용하는 관절이다. 그 사람의 직업에 따라 달라진다. 일반적으로 무릅...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/wawawawa24/20824</t>
+  </si>
+  <si>
+    <t>시니어 단독주택 정원 가꾸기와 안전한 마당 관리 요령 및 지자체 지원 혜택 안내</t>
+  </si>
+  <si>
+    <t>시니어 단독주택 정원 가꾸기와 안전한 마당 관리 요령 및 지자체 지원 혜택 안내 은퇴 후 마당이 있는 주택이나 귀촌 생활을 시작하면서 정원과 마당을 가꾸는 시니어가 늘어나고 있습니다. 마당 관리는 신체... 쪼그려 앉아서 장시간 작업하면 무릎과 허리에 큰 부담을 주어 퇴행성 관절염을 악화시킬 수 있으므로 반드시 바퀴가 달린 작업용 의자를 사용하거나 긴 손잡이가 부착된 잡초 제거기를 활용하여 서서...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/senioro/775</t>
+  </si>
+  <si>
+    <t>무릎인공관절 하신분들 언제까지 소염제, 마약진통제 복용하셨나요?</t>
+  </si>
+  <si>
+    <t>제목 : 25글자 이내로 간략하게 내용 : 손상된 부위, 현상황 , 궁금증 등 기재(성격에 맞는 게시판 및 말머리 체크) 무릎 인공관절 하신분들이요. 혹시 언제까지 소염진통제, 마약진통제 복용하셨나요? 어머니 양쪽 인공관절 수술한지 이제 4달 아직 조금 못되었는데 오른쪽다리 바깥쪽 오금부분이 통증이 계속 되어서 통증있다고 하니 기존 관절염으로 복용하던 비스테로이드성 소염진통제하고 추가로 통증시...</t>
+  </si>
+  <si>
+    <t>RE코노펜은 첨 들어본 약물이라서 저희 엄마는 트라마돌 성분의 비마약성 약을 처방해 주셔서 한동안 그걸 먹긴 했는데 저희 엄마도 신장이 조금 안 좋아지셔서(진통제 때문은 아니고요) 저도 엄마한테 진통제 좀 줄이라고 잔소리 해서 서서히 줄이셨어요 3개월 지나면 마약성</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/aclknee/143768</t>
+  </si>
+  <si>
+    <t>무릎통증, 관절염, 골다공증으로 고생 중이신가요? 하루 한 스푼 습관으로 자연치유 루틴....</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ITdvp-9k3_o?si=n59da_b2-9CC-TsX</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/q69/1125041</t>
+  </si>
+  <si>
+    <t>“무릎 관절염 통증,저강도 플리어스초음파로 잡는다”</t>
+  </si>
+  <si>
+    <t>“무릎 관절염 통증, 저강도 플리어스초음파로 잡는다” " "</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/gnbds/109542</t>
+  </si>
+  <si>
+    <t>[기사] 참고 일하다 ‘농부병’ 키웠군요</t>
+  </si>
+  <si>
+    <t>조선대 농업안전보건센터가 농부 411명의 무릎 MRI를 촬영한 결과, 70세 이상 남성의 62.5%, 여자는 84.0%가 골관절염을 앓았다. 젊은 귀농·귀촌 인구도 안심할 수 없다. MRI 검사 결과, 40대 10명 중 1명(11.0%)은 골관절염 진단을 받았다. 대부분 X선 사진에는 정상 소견을 보였거나 통증 등 이상 증상이 없는 경우였다. 이 교수는 “연골은 신경과 혈관이 없어 손상을 즉시 자각하기 어렵다. 다리가 쉽게 붓거나 통증이나...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/godonet/2749</t>
+  </si>
+  <si>
+    <t>6-2.정주환경_마을텃세_심리고립스트레스</t>
+  </si>
+  <si>
+    <t>귀농 텃세</t>
+  </si>
+  <si>
+    <t>서울 근교 귀농 귀촌 많이 가시는 지역이 어디있을까요?</t>
+  </si>
+  <si>
+    <t>서울 근교 두시간 이내로 걸리는 지역에 농촌체류형쉼터를 이용해서 4도 3촌을 계획하고 있습니다. 외지인 귀농 귀촌이 많아 텃세없고 서로 교류가 많지 않은 동네 어디있을까요? 강원 충청 쪽 생각하고 있습니다</t>
+  </si>
+  <si>
+    <t>REcase by case 라서 지역은 별로 중요하지 않은것 같습니다. 원주민 동네 한가운데에 자리잡지만 않으면 원치않는 교류는 피할수 있구요....</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1345730</t>
+  </si>
+  <si>
+    <t>시골은 동네 일부 어르신들이 변해야햔다</t>
+  </si>
+  <si>
+    <t>시골의 텃세는 권리인줄 안다. 시골에 집을 지을 생각이 일 순간에 사라지는 하루였다 젊은 사람들이 유입되어야 시골도 나아질텐데.. 본인들 자식도 감놔라 배놔라 하면 말을 안 듣는데 남의 밭에 사사건건 입을 대면 우쩌겠단건지. 시골집은 못 가겠다</t>
+  </si>
+  <si>
+    <t>RE텃세라기 보다는 관심(?) 입니다, 초보 농부를 보니 이것저것 아는체하시며 대화를 나누고 싶으신 것이죠, 그도 아니라면 그분 성격이 참견을 본인도 느끼지 못하면서 계속 얘기하는 스타일이거나</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1345262</t>
+  </si>
+  <si>
+    <t>시골에 빈집 많다해도 텃세도 많네요</t>
+  </si>
+  <si>
+    <t>전국각지에 시골지역 돌아다니다보면 마을마다 빈집이 많이 보여요 그런데 빈집이 많아도 마을마다 터박고 사는 터주대감이 꼭 있는데 텃세도 많이 부리네요 빈집이 그렇게 많아도 외지인이 들어와서 눈에 알짱거리면 싫어하는건 이미 터박고 살던 사람들 공통심리인것 같습니다 뭔가 싶어 생각해보면 그냥 자기들 혼자 조용히 살다가 누군가 내눈앞에 보이고 소리가 들리면 거슬리고 내키지 않는것같네요 전국에...</t>
+  </si>
+  <si>
+    <t>RE그건 텃세가 아니라 경계하는거에요. 마을 주민 아닌 모르는 사람이 집 주변을 두리번 거리면 당연히 의심의 눈으로 바라볼수밖에 없죠.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1333759</t>
+  </si>
+  <si>
+    <t>전남, 텃세를 두려워하는 귀촌 희망자들을 위한 조언!</t>
+  </si>
+  <si>
+    <t>텃세라는 게 전국 어딜 가나 문제가 될 수 있는 건데 전라남도라고 텃세가 특별하진 않아요. 마을발전기금 강요로 메스컴에 오르내린 고흥, 귀농청년들 등쳐먹은 뉴스로 유명한 남원 등 특정지역이 악명 높긴 해도, 대부분은 그렇지 않습니다. 고흥과 남원도 대부분은 평범할 겁니다. 저는 연고도 없는 영월에서 귀촌생활을 시작했었고, 역시 연고 없는 전남 보성으로 이주한 지 5년차입니다. 아랫집 놀부 영감과 싸우고...</t>
+  </si>
+  <si>
+    <t>RE누가 전남이 텃세가 심하다 하셨나요? 저는 부산 사람인데 팔자가 기구해서 전국을 돌며 사는데 지역마다 다녀보니 지역민들이 살아온 환경 탓에 본성들이 그 지역에 맞춰 살아오느라 만들어 진것 같아요 그러니 외지인이 오면 두려움에 본인들을 지키기 위한 방어적 태세</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1334234</t>
+  </si>
+  <si>
+    <t>시골 동네 텃세, 감정적으로 대응하지 않고 현명하게 해결하는 방법이 있을까요?</t>
+  </si>
+  <si>
+    <t>시골 동네에서 생활하면서 겪는 텃세 문제로 고민이 있어 글을 올립니다. 저희 아버지는 동네 사람들과 잘 지내려고 노력하고, 주변에도 최대한 잘해주면서 생활하고 있습니다. 그런데 일부 주민 때문에... 혹시 시골에서 비슷한 텃세를 겪어보셨거나 이런 상황을 현명하게 해결하신 분들이 계실까요? 무조건 참고 살라는 조언보다는, 실제로 효과가 있었던 대처 방법이나 경험담을 듣고 싶습니다. 저도 동네에서...</t>
+  </si>
+  <si>
+    <t>RE시골에서 경찰서와 법원까지 조서받으러 왔다갔다 변호사 고용하고 이런과정을 한번 격고나면 돈은 대략 1000만원 깨질거라서 그뒤로는 어느누구도 무례한 행동을 못할거에요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1346224</t>
+  </si>
+  <si>
+    <t>아무 연고도 살아본적도없는 타지에서 살수 있을까요?</t>
+  </si>
+  <si>
+    <t>제목 그대로 평생살아왔던 곳을 떠나 생판 모르는 타지에서 은퇴 생활 할수 있을까요? 마을주민들 텃새나 갈등 없다는 전제하에요 ᆢ많이 외로울까요? 어떤 어려운점이 있는지 먼저 해보신 선배님들 댓글 부탁드립니다</t>
+  </si>
+  <si>
+    <t>RE한달살기나 전세부터 살아보세요 이게 생각보다 살만해요 로컬 식당 하나하나 알아가는 재미도 있고 그동네 샅샅이 뒤져서 나만의 계곡이나 쉼터 찾는 재미도 있고 특히 계곡 낀곳은 오지계곡 찾아서 혼자 자연수영장처럼 노는 기분 천국이거든요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/430820</t>
+  </si>
+  <si>
+    <t>시골살이 16년 이야기 [텃세 시작되다]</t>
+  </si>
+  <si>
+    <t>전편에 이어집니다. 이번에는 여러번 중복되는 내용으로 제가 너무 힘들게 보낸 시련기입니다. 2010년 이사하고 2011년 새해 맞이 회관에서 척사대회및 여러번의 회의도 참석하고 아래 윗동네 주민들과 인사도 나누고 모두 반겨주시고 도와주시고 저도 작은 힘이지만 보태드리렸스니다. 어르신 혼자 계시는 집에 고장난것 고쳐드리고 이것 저것 수리도 해드렸습니다. 이사 3년후 1월 어느날에 뒷집 어르신이 우리집으로...</t>
+  </si>
+  <si>
+    <t>RE고생많으셨습니다 마을일을 맡아서 하다보면 꼭 시기하는 사람이 있습니다 저도 경험해서 이해합니다 마을기금 횡령한 내용은 통장과 영수증으로 증명해서 오해를 풀고 그분에게 사과하라고 해야될거같은데요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1344656</t>
+  </si>
+  <si>
+    <t>유튜버 매물보면 남쪽지방이 저렴한데 궁금점이??</t>
+  </si>
+  <si>
+    <t>주택을 마련하고 싶은데 수도권쪽은 아무래도 예산이 안맞고 유튜버 매물들 보면 남해안쪽이 나름 저렴하던데... 특히 전라도쪽이요 왠만하면 4천에서 6천 사이에 형성되어 있던데.. 다른건 다 그렇다쳐도 뭐 텃세가 장난 아니라는 댓글이 많은데 정말 그런가요?? 나중에 팔기 어렵다 이런건 문제가 안되는데.. 텃세 고립 등등 이런 문제가 제일 걱정되서요%~</t>
+  </si>
+  <si>
+    <t>RE그냥 케이스 바이 케이스 입니다. 여기 계시는 분들은 저마다 다른, 또 비슷한 경험을 합니다. 누구는 텃세가 심해서 고생하고, 누구는 텃세가 뭐야? 하고 삽니다. 제일 걱정인게 시골은 무조건 텃세 라는 공식을 무비판적으로 받으들입니다. 아파트를 예로 들어보면 층간소</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1334222</t>
+  </si>
+  <si>
+    <t>한달살기는 이장님 면담부터</t>
+  </si>
+  <si>
+    <t>아니라 귀촌 귀농 지역 정하기의 시작이 되는거 같아요 이장님 만나서 얘기 30분만 해보시면 동네 분위기가 대략 짐작이 됩니다. 텃세가 심한지. 외지인에 대해서 환영하는 분위기인지 등등 특히나 본인 나이의 귀촌, 귀농은들을 반가는지가 중요해보입니다. 젊은 사람들은 좋아해도 50대 60대는 싫어할 수도 있고 반대로 젊은 애들을 싫어하는 곳들도 있더라구요. 분위기 흐리고 개인적이라고 즐거운 귀인이 됩시다.</t>
+  </si>
+  <si>
+    <t>RE이장님과의 면담이 정말 중요하네요. 동네 분위기를 파악하는 데 큰 도움이 될 것 같아요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/makeho/87057</t>
+  </si>
+  <si>
+    <t>귀촌은 선택의 문제</t>
+  </si>
+  <si>
+    <t>최근 SNS나 유튜브를 보다 보면 귀촌이나 전원생활에 대해 부정적인 이야기를 하는 콘텐츠가 유난히 많이 눈에 들어온다.‘시골에 가보니 텃세가 심하더라’, ‘나이 들어 병원 다니기가 힘들더라’, ‘집을... 조용하고 자연이 좋아서 갔는데, 오히려 간섭과 텃세가 힘들고 저녁이면 적막하더라 시골이라고 해서 반드시 마을 주민들과 가까이 지내야 하는 것은 아니다.지역 주민들과는 적당한 거리를 유지하면서 서로...</t>
+  </si>
+  <si>
+    <t>RE글 쓰신 내용 중 2번에 대해서 한가지만 첨언 하겠습니다. 건강하시거나 관리가 가능한 질병분 들은 말씀하신대로 동네 마을이나 읍에 웬만한 개인 의원이나 소규모 병원이 있으니 괜찮습니다. 그리고 병원을 한곳만 자주 가시면 기록이 남아 본의 아니게 의사선생님이 주치</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/425801</t>
+  </si>
+  <si>
+    <t>귀농 귀어 어려운 선택인가요</t>
+  </si>
+  <si>
+    <t>않은 곳 입니다 너무 걱정 앞 세우지마시고 내가 제2의 고향을 만들어야지 하는 마음만 있으면 충분히 정 붙히고 살수 있을거라 생각됩니다 집이나 토지를 구매할때 혹시 이웃과 분쟁의 소지가 조금이라도 있다면 주인이 완벽하게 해결하고 거래를 해야합니다. 이 점만 주의하고 내가 남에게 해를 끼치지 않은다면 큰 문제없이 살수 있으리라 봅니다 귀농.귀어 꿈꾸시는 분 계시다면 조금이나마 도움이 되셨으면 합니다</t>
+  </si>
+  <si>
+    <t>RE부모님이 어촌생활 하셨는데, 정작 저는 농업에 뛰어들었습니다. 어떤 도시든, 지방이든, 농어촌이든 다 사람이 모여서 만들어진 소규모 조직들이 다 있기 때문에 말씀하신 것처럼 하기 나름 같다는 생각이 드네요. 시간을 두고 오고가고 주고받고 하는 관계가 되기까지 시</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/435860</t>
+  </si>
+  <si>
+    <t>시골에서 전원주택으로 10년 넘게 살아보니</t>
+  </si>
+  <si>
+    <t>시골의 텃세는 도시의 아파트 층간소음 문제처럼 답이 없다. 며칠 전 집 뒷 터에 10년 넘게 풀로 방치된 터에 포크레인이 와서 풀도 정리하고... 그래서 시골의 텃세를 조금 줄이는 방향이 전원주택 단지로 가는게 아닐까 싶습니다. 그 곳은 대부분 외부인이 비슷한 성향(은퇴 후 휴식, 조용히 살자)이라서..저는 원주민 마을에서 집 짓고 사는데 장단점이 있는 것 같습니다. 원주민 마을은 텃세가 처음에 있었지만 저는...</t>
+  </si>
+  <si>
+    <t>RE공감하는 부분이 많습니다. 텃세도 문제지만 그것은 세월가면 해결이 되더라구요. 저 갇은 경우는 맑은 공기 맡으러 내려왔더니 비닐 태우고 쓰레기 농약병 주변에 버리고 새떼 쫓겠다고 주택 100m안에서 폭음기 쓰고~~ 강아지 폭염에 방치하고... 이런게 힘들더라구요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1338548</t>
+  </si>
+  <si>
+    <t>아직도 시골텃세 심하나요?</t>
+  </si>
+  <si>
+    <t>이장이 발전기금 주라는등~</t>
+  </si>
+  <si>
+    <t>RE쫌있으면 그 이장들 다 죽을듯 그때 들어갈려구요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/403925</t>
+  </si>
+  <si>
+    <t>귀촌은 텃세가 진짜 심할까요?</t>
+  </si>
+  <si>
+    <t>밤에 괜히 또 한적한데 살고 싶다 이러다 귀촌까지 생각이 뻗어나가는데 ㅎㅎㅎㅎ 시골 텃세 심하다는 말이 있던데 진짜 그럴까요? 인스타보면 지방에 숙소 이쁘게 해놓고 펜션사업 하시는 분들도 많으시던데 저의 로망입니다 &gt;&lt;</t>
+  </si>
+  <si>
+    <t>RE사촌동생이 귀촌했는데 텃세?보단 관심이 과~해서 초반에 힘들어했어요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/skybluezw4rh/14347272</t>
+  </si>
+  <si>
+    <t>귀농하고 후회하시는 분들 계시나요~?</t>
+  </si>
+  <si>
+    <t>어떤 선택이든 단점도 늘 있으니~~ㅎ 귀농하고 싶은데 병원이든..인프라든.. 사실 텃세도 좀 무섭구요ㅎ 혼자 고민만 하고 있는데 후회하시는 분들 계신지 궁금하네요</t>
+  </si>
+  <si>
+    <t>RE후회는 겨울뿐. 추워서요. 제설안해줘서. 다좋아요. 텃세걱정했는데 없습니다. 시내(읍내)가까운곳 가세요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1228328</t>
+  </si>
+  <si>
+    <t>귀농 귀촌하면 텃세가 엄청 나다는데 이유가 뭘까요?</t>
+  </si>
+  <si>
+    <t>특히 어촌이 더 심하다던데 ㅜㅜ 왜그런지 아시는분?</t>
+  </si>
+  <si>
+    <t>RE촌은 오랫동안 주민들의 생활방식이 고착된 곳이라 새사람들은 적응하기 힘들고 불만사항얘기한들 원 주민들은 그게 뭐가 불만이냐 할</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dgmom365/5718985</t>
+  </si>
+  <si>
+    <t>귀농 텃세 과연 원주민만 나쁜 사람들일까?</t>
+  </si>
+  <si>
+    <t>요즘 유투브나 SNS를 보면 귀농 하지 마라, 폭력에 가까운 원주민 텃세 이런 이야기 들이 많이 들립니다. 하지만 원래 사시던 분들의 이야기를 들어보면 귀농인들의 이기심 또한 상상을 초월 합니다. 1. 측량하니 여기는 내땅입니다. 십수년전 맹지를 살리기 위해서 6집이 땅을 조금씩 내어서 길을 만들고 택지로 개발 합니다. 그중 한집이 귀농인에게 집을 팔고나서 문제가 생깁니다. 새로온 귀농인은 측략을 한 뒤 '땅을...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/jejumam/838735</t>
+  </si>
+  <si>
+    <t>시골 동네 텃세?</t>
+  </si>
+  <si>
+    <t>회원님들, 혹시 시골 동네의 텃세란게 감이 잘 안오는데 타 지역 사람들이 이사오면 대부분 텃세가 심한가요?! (길들이기?) 충북 금산쪽 리 단위의 작은 마을에 부모님 나대지가 있어 측량하고 소형주택 지어 주말 쉼터로 사용할 예정인데 부모님은 시골이웃들 심기 거스르면 큰일 나는걸로 아시고 너무 조심스러워하셔서요. 이걸 어디까지 조심하고 어디까지 기어?야하는지 감이 안오네요. 지금 느낌 아닌 느낌 상...</t>
+  </si>
+  <si>
+    <t>RE시골 사는분들 대부분이 조상대대로 살아온 사람들입니다. 수십년전에 이사와서 정착한 사람도 외지인 취급 받기 십상입니다. 더구나 집성촌일 경우는 대부분의 이웃들이 사촌, 육촌, 팔촌등의 인척으로 얽혀져 있기에 외지인에 대한 텃세가 있기는 합니다,</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/243353</t>
+  </si>
+  <si>
+    <t>시골텃세 장난 아닙니다, 시골텃세 이기는 방법</t>
+  </si>
+  <si>
+    <t>준비 없이 귀농·귀촌을 시작하면 낭만이 아닌 생존 게임이 될 수 있습니다. 특히 시골 텃세 문제는 단순한 불편을 넘어 수천만 원의 손실로 이어질 수 있습니다. 1. 통계와 현실의 간극 농림축산식품부 자료에 따르면 귀농인의 약 30%가 5년 내 다시 도시로 돌아옵니다. 하지만 실제 현장에서는 집이 팔리지 않아 억지로 버티거나, 생활 갈등으로 고통받는 사례가 많습니다. 체감 실패율은 훨씬 높다는 것이 전문가들의...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/samunjin0089/1365</t>
+  </si>
+  <si>
+    <t>농촌 원주민과의 트러블 해결 방법 여쭙니다</t>
+  </si>
+  <si>
+    <t>안녕하세요 눈팅만 열심히 하다가 도저히 답이 안나와 여기 계신 선배님들께 여쭙니다 최근 2-3주 전에 농지를 하나 사서 이렇게저렇게 꾸미고있는데요, 원주민들의 텃세가 너무 도를 지나칩니다 기존에 저희 땅을 빌려 농사짓던 분이 이제 농사를 짓지못하게되자 있지도 않은 소문을 퍼트리더라고요. 저희가 본인에게 쌍욕을 퍼부었다면서요. 그분들이 부추겨서 그런지, 사전에 아무런 소통도 없이 이장님은...</t>
+  </si>
+  <si>
+    <t>RE쓰레기 같은 놈들이 많네요 재산상 피해를 입증해서 재판을 통해서 피해 보상 받아낼 수 없나요? 없다면 그것은 법이 제대로 만들어진 것 같지 않은데...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/264974</t>
+  </si>
+  <si>
+    <t>시골로 귀촌 왔는데 여자들 텃세 때문에 미쳐버리겠네요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/jihosoccer123/3639867</t>
+  </si>
+  <si>
+    <t>귀농 감소의 진짜 이유, 시골 텃세 때문일까?</t>
+  </si>
+  <si>
+    <t>귀농 실패의 진짜 원인 많은 사람들이 귀농 실패 원인을 텃세라고 생각하지만 실제 조사에서는 다른 이유가 더 많습니다. 1. 준비 부족 농사를 너무 쉽게 생각하는 경우 2. 수익성 부족 생산은 했지만 판매가 어려운 경우 3. 자금 부족 시설 투자 후 운영자금 부족 4. 가족 갈등 배우자나 자녀가 적응하지 못하는 경우 5. 지역사회 적응 실패 주민들과의 관계 형성 실패 즉, 텃세만이 문제가 아니라 전반적인 준비 부족이 더...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/aisi5630/716</t>
+  </si>
+  <si>
+    <t>무개념 상팔자~귀농인~저주할꺼임</t>
+  </si>
+  <si>
+    <t>여름 뙤약볕에 콩을 심었음 어제 가보니 누가 콩밭을 쑥대밭 만들어놨음 수소문 해보니 우리동네 귀농인 집에 두메부추도 뽑아다 뒤뜰에 심어두고 콩도 영글지도 않은걸 두소쿠리나 따놨음 저 무개념이... 모르고 텃세한다 씨브리겠지? 저 자슥이 따놓은거 봉투에 담아서 가져온거 어제밤 한번 쪄묵고~ 오늘 두번찌고~남은게 15키로 뽑아와서 콩따는데~ 올캐 영글지도 않았는데~ 단풍도 아직 안들었는데~ 아~씨브랄...</t>
+  </si>
+  <si>
+    <t>RE해도해도 넘~하네. 아무리 귀농이라도 쥔이 있는지 없는지는 옆에라도 물어보구 확인하는게 상식일건데... 확 절도 신고하셔야지~ 기냥 두셨어요? 속상타요!</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/happyparm/611060</t>
+  </si>
+  <si>
+    <t>귀농후 신세한탄 feat.텃세</t>
+  </si>
+  <si>
+    <t>여기는 텃세에 불친절에..금전적 피해도 서슴없고 당당하게 주네요.. 제가 귀농한 지역이 고향인 타지서만난 친한분들이.. 거기는 가지말라고 말릴때 알아봤어야했는데.. 저는 친화력이 좋아서 쉽게친해진다고 생각했는데.. 높은담이있네요.. 이해할수없는..배려없고..무식한지역.. 답답해서 적어봅니다.. 여기서 돈만벌고 다른지역에서 돈써야겠습니다..</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/wjdxorduq/92434</t>
+  </si>
+  <si>
+    <t>귀촌할 때 인심 좋은 마을 고르는 꿀팁?!</t>
+  </si>
+  <si>
+    <t>마지못해 최소한만 내놓고는 기부채납도 거부한 채, 지금까지도 "내 땅이니 밟지 말라"며 길을 막아서는 사례도 드물게 있고, 그 땅을 구입해 들어와 텃세를 부리며 똑같이 길을 막는 새 주인도 많아지고 있다네요. 실제로 경기도 광주시의 한 한적한 시골 마을은 이 작은 이기심 때문에 공동체가 통째로 무너졌습니다. 수년간 이웃들이 다 함께 드나들던 유일한 통행로가 사유지라는 이유로, 한 주민이 갑자기 펜스를...</t>
+  </si>
+  <si>
+    <t>RE좋은 팁이네요 ^^ 땅에게 길은 핏줄이지요 피가 잘통해야 합니다^^</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1341067</t>
+  </si>
+  <si>
+    <t>귀촌 텃세 갈등</t>
+  </si>
+  <si>
+    <t>시골살이 16년 이야기 [이웃집 편]</t>
+  </si>
+  <si>
+    <t>그말했다고 그집 부부가 술이 취해서 저한테 삿대질하면 큰소리로 대들고 손님들도 가재는 게편이라고 같이 합세해서 이웃집 텃세가 나쁘다면서 같이 덤비는데 대책이 없더군요. 결국은 제가 미안하다하고 들어왔습니다. 앞집은 날마다 잔치를 벌여서 한달 가까이 잔치집이 되었구요. 어느날 밭에 가려고 준비하는데 앞집 여자가 길을 막고 그렇게 살지 마라 말이 많다 등등 그래서 다시 전쟁이 발발 이아줌마가...</t>
+  </si>
+  <si>
+    <t>RE사실 이집이 살인사건이 나서 몇명이 죽어나간 흉가라고 한마디 슬쩍 했으면 바로 이사갔을수도 있지 않았을까요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1344156</t>
+  </si>
+  <si>
+    <t>앞집 남자</t>
+  </si>
+  <si>
+    <t>가만히 생각해 보면 국가 공무원이 안그래도 시골애 사람이 없고 정부차원에서 귀촌을 중요하게 생각하고 있는데 사사건건 꼬투리를 잡고 생떼를 부리는 것은 권력남용으로 밖에 보이지 않습니다. 기분이 나쁜 것도 있지만 저희 카페에 글 보면 안하무인들이 너무 많은 것 같아 어떻게든 혼을 내줄 생각입니다. 혹시 비슷한 사례나 좋은 아이디어가 있으시면 부탁드리겠습니다. 시시콜콜한 내용이지만 비슷한 일들이...</t>
+  </si>
+  <si>
+    <t>RE"이런 걸 신문고에 내도 되나?" 슬쩍 주위에 흘려보세요. 119나 고위공무원, 시의원 등 아시고 계신 것처럼도 해보세요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1337293</t>
+  </si>
+  <si>
+    <t>텃세에 대한 고찰 feat 귀촌귀농의 장벽</t>
+  </si>
+  <si>
+    <t>있습니다 귀촌귀농을 하면서 어려움? 이런 주제였는데 마을주민과 갈등을 겪은 적이 있다는 분들이 무려 40%가까이 된다는 사실입니다 지역주민들의 텃세때문에 힘들어 하는 분들이 꽤 많고 오죽하면 2023년에 국회에서 발의된 법안이 하나 있습니다 바로, '텃세금지법' ㅎㅎ 지역 텃세를 절대 간과해서는 안 됩니다 지역 주민들의 텃세를 지혜롭게 풀어가는 것이 성공적인 귀촌귀농의 첫걸임입니다 벌써부터 한숨이...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/selfzipsuri/18</t>
+  </si>
+  <si>
+    <t>귀농 1년 차가 느낀 '시골 텃세' 극복하는 현실적인 소통법</t>
+  </si>
+  <si>
+    <t>초기 정착 과정에서 겪는 갈등을 지혜롭게 풀어내면, 시골은 나를 감시하는 곳이 아니라 든든하게 지켜주는 울타리가 되어줍니다. 먼저 다가가는 인사와 작은 나눔이 만드는 기적 사실 시골 어르신들이 가장... 당신도 마을에서 없어서는 안 될 소중한 구성원이 되어 있을 거예요. #귀농귀촌 #시골생활 #텃세극복 #스마트팜 #수경재배 #농촌체류형쉼터 #치유농업 #도시농업 #귀농일기 #마을공동체 #귀농정책 #전원주택생활</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/adangzzang/4261</t>
+  </si>
+  <si>
+    <t>시골 텃세</t>
+  </si>
+  <si>
+    <t>요즘에 TV에서 보면 시골 사람 없다고 하던데 참 내가 시골에 내려가서 살다 보니 참 이장님 동네 사람들 두루두루 텃세를 하는지 참 이상하네요. 시골로 이사와서 같이 살자고 하면 얼마나 좋아요? 서울은 못 가고 수도권으로 이사해야 되겠네요 ㅠ</t>
+  </si>
+  <si>
+    <t>RE텃세라고 느끼는 것이 어떨 땐 상대적일 때가 많습니다, 왜? 나를 싫어하는 것 같은지? 한번 그동안의 일들을 되세겨보시길 추천드립니다. 그리고나서 아니다 싶으시면 해당 마을분들은 님과 맞지 않는 상황이라 판단하고 땅을 매도하고 다른 마을로 가시거나 다시 도시로</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1302889</t>
+  </si>
+  <si>
+    <t>[헤럴드경제 라이프칼럼] 전환점에 선 ‘귀농·귀촌 전성시대’</t>
+  </si>
+  <si>
+    <t>이처럼 귀농·귀촌인이 겪는 갈등은 비단 지역주민의 텃세 때문만은 아니다. 귀농·귀촌인 간 갈등도 심각한 상황이다. 원주민끼리의 갈등도 빼놓을 수 없다. 넓게는 지역갈등에서부터 마을갈등, 개별갈등, 그리고 행정갈등에 이르기까지 얽히고설켜 있다. 귀농·귀촌 주무 부서인 농림축산식품부가 올 들어 ‘찾아가는 마을단위 지역주민-귀농·귀촌인 융화교육’을 대대적으로 실시하고 있지만 농촌 지자체의...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/rmnews/24956</t>
+  </si>
+  <si>
+    <t>올바른 귀농 귀촌 10 - 갈등</t>
+  </si>
+  <si>
+    <t>귀농이든..귀촌이든.. 하게 되면.. 부부애가 남달라집니다. 산속에서 이야기 할 대상이.. 애들이랑.. 와이프 밖에 없기 때문에 ^^ 와이프랑 이런... 우선 이러한 갈등의 요인의 가장 큰 포인트는 "사고의 기준이 다름"에서 오는데.... 직설적으로 말하기 머 하지만.. 많이 다릅니다. 사고의 기준이 제가 살고 있는 평창 대화는 아직은.. 외지인들이..많이 사고 있는 곳이 아니라.. 지역적 텃세가 좀 심한 편입니다.. 전에 살던...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/eprettylife/17031</t>
+  </si>
+  <si>
+    <t>인간의 심리..</t>
+  </si>
+  <si>
+    <t>즤친정부모님은 나는자연인이다 를 꿈꾸시다 귀촌하셨거든여.. 말이 많으신 분들도 아니고.. 동네분들이랑도 되게 잘지내시구 좋아요 그러다 어제.... 아침에 엄마저나와서 부들부들 떠시더라고요? 오랜만에 엄니의 육두문자들었고요 보이시나요.... 누군가가 고추를 가위로 똑똑, 짤랐어요... 오른쪽 고랑보면 응급처치로 검은색테이프로 붙여놨고 유난히도 올해 동네에서 고추농사 젤 잘된집이었는데.. 즤엄마...</t>
+  </si>
+  <si>
+    <t>RE헐...사진확대해서봤어요 검은테이프 ㅜㅜ 진짜못된 ..이건자식이상으로정성들인건데 어찌이런짓을 할수있나요 ㅜㅜ 어머님 화가나실만한데 진짜 나쁜사람이네요 대체왜그러는거지?</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/gwanjeoheart/17258</t>
+  </si>
+  <si>
+    <t>귀농귀촌, 갈등</t>
+  </si>
+  <si>
+    <t>귀촌이든.. 하게 되면.. 부부애가 남달라집니다. 산속에서 이야기 할 대상이.. 애들이랑.. 와이프 밖에 없기 때문에 ^^ 와이프랑 이런 저런... 우선 이러한 갈등의 요인의 가장 큰 포인트는 "사고의 기준이 다름"에서 오는데.... 직설적으로 말하기 머 하지만.. 많이 다릅니다. 사고의 기준이 제가 살고 있는 평창 대화는 아직은.. 외지인들이..많이 사고 있는 곳이 아니라.. 지역적 텃세가 좀 심한 편입니다.. 전에 살던...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/qotthr12/49100</t>
+  </si>
+  <si>
+    <t>노은 동네 작은 저수지로 낚시를 갔더니 동네사람 이라면서 여기서 낚시하지 말라고 한다. 어디서 왔냐 묻기에 동네에서 왔다고 하고 말섞기 싫어서 돌아왔다. 내가있는 삼통마을은 60가구중 70%가 외지에서 귀촌한 사람들이다. 저수지는 대부분 농어촌공사와 충주시에서 관리 하는데 동네사람이 텃세를 부린다.잘먹고 잘 살아라. 스트레스 풀려고 낚시갔는데 스트레스 받고왔다. 다른 곳으로 낚시가야지 ㅎ</t>
+  </si>
+  <si>
+    <t>RE이것은 텃세 축에도 못 낍니다. 리장이 있는 동네의 외지인들에 대한 텃세는 지구 최강 입니다. 이런것들이 마을 발전을 막는 근본 원인 이죠 &gt;&gt;&gt;</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/cjyeonsu/569978</t>
+  </si>
+  <si>
+    <t>6-3.농가주택_기름보일러_난방비_지하수수질</t>
+  </si>
+  <si>
+    <t>시골집 기름보일러 난방비</t>
+  </si>
+  <si>
+    <t>“시골집 기름보일러 쓰시는 분들!” 10월 25일 놓치지 마세요</t>
+  </si>
+  <si>
+    <t>특히 시골집이나 단독주택에서 도시가스 대신 기름보일러나 LPG로 난방하는 분들은 겨울철 부담이 만만치 않은데요. 지난해 등유·LPG 난방비 추가 지원을 받으셨다면 꼭 확인해 보세요! 요즘 기름값도 부담스러운데 이미 받은 지원금만큼은 기한 놓쳐서 못 쓰는 일이 없었으면 좋겠네요!!</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/chaejipso/82</t>
+  </si>
+  <si>
+    <t>보일러 트나요? 시골아줌마 겨울나기☃️</t>
+  </si>
+  <si>
+    <t>정해진 인생.. ) 도시가스가 아닌 기름보일러에 멘붕이였슴다ㅋㅋ 월동준비한다고 일단 50만원어치 등유 넣어놓고 보통 얼마나 쓰냐 묻더니 ㅋㅋㅋ두번은 더넣어야 겨울보낼거라구... 오메 난방비... 기후취약계층에 이제 채니도 넣어주세요... 이 시골집에서 2살아들과 남편과... 아직덥다구 보일러안튼다는데..흑..시골아줌마..힘내보자 19개월동안 항생제한번 안먹고 건강하게 커주는 아들..시골집에서도 강하게 잘...</t>
+  </si>
+  <si>
+    <t>RE만삭이 신데... 이렇게 정성들여서 찍고 쓰고 그리고 게시해 주셔서 항상 감사합니다.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/danhsaju/18231</t>
+  </si>
+  <si>
+    <t>시골집(기름보일러) 난방비 얼마나 쓰시나요?</t>
+  </si>
+  <si>
+    <t>아이들이 방학이고 코로나로 바깥활동을 하지 않다보니 주말은 시골집에서 보내구요. 주중에는 동생네 가족이 가끔 가서 1박2일정도 지냈어요. 제가 추위에 약해서 보일러를 강하게 틀었고 아이들이 마당에서 노천탕을 즐긴다고 뜨거운 물을 많이 사용하였습니다. 그렇다고 해도 월 10일정도 사용한건데요. 기름이 기름이 상상초월이네요ㅠ 보일러가 고장나서 기름이 어딘가에서 새고 있는걸까요? 다른분들은...</t>
+  </si>
+  <si>
+    <t>RE전 보일러 타이머로.. 오후5시-오전7시까지. 온돌 운전. 하루에 대략 11리터씩 소비되네요. 완전 따뜻이도 아닌데. ㅠㅠ</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/860012</t>
+  </si>
+  <si>
+    <t>시골집 보일러 교체하려는데요??</t>
+  </si>
+  <si>
+    <t>심야전기요금이 겨울에는 40-50만원 정도 나와서 비용대비 효과가 낮은 거 같아요. 6-7년 전에 시골집 전체 리모델링해서 시골집 단열은 새로 다 해 놓았습니다. 아버지 혼자 계시니 주로 안방 또는 거실만 주로 사용하고 자식들이 올때만 다른방 난방을 하는 편입니다. 문의사항 1) 어떤 보일러(가스, 기름, 기타)를 설치하면 좋을까요? - 시골이 현재는 도시가스는 안들어 옵니다. - 난방비 적에 나오고, 온수 자유롭게...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1322047</t>
+  </si>
+  <si>
+    <t>시골집 에너지 자립에 대한 고찰(집수리할때 챙겨야되는)?</t>
+  </si>
+  <si>
+    <t>시골로 터전을 옮기기 위해 촌집을 수리하면서 가장 중요하게 생각했던게. 일단 따듯한 집. 그리고 겨울철에도 따듯하게 지내면서... 도시가스는 안들어오고 기름값은 비싸고 해서 따로 보일러는 설치 안했는데, 아직은 딱히 에너지 비용이 안들면서 실내에서 반팔 입고... 화목보일러를 . 제작? 해야하고. 태양광으로 생산되는 전기로 라지에타 또는 전기보일러로 보조해가면서 지내면 추운 겨울에도 난방비가 크지...</t>
+  </si>
+  <si>
+    <t>RE아하 구조는 알겠습니다 순환모터는 어떤걸 쓰셨어요?</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1287791</t>
+  </si>
+  <si>
+    <t>시골집 심야전기보일러</t>
+  </si>
+  <si>
+    <t>어머님이 마지막까지 사시던 집이라 팔기도 그렇고 세컨 하우스로 두고 살려고 하는데 유지비용이 만만치 않네요 11월 18일부터 12월 17일 까지 난방비가 30만원.ㅠㅠ 시골집은 관리 차원에서 주말에만 가서 쓰고 평소 보일러 온도 10도, 온수온도 65도 설정해놓고 있어요. 어머니 계실때 춥게 사셨는데도 80만원까지 난방비가 나왔는데 난방비는 그렇다쳐도 고장이라도 안나면 좋겠어요.ㅠㅠ 암튼 넋두리는 그만하고...</t>
+  </si>
+  <si>
+    <t>RE지금은 심야전기보일러 안쓰고 있어요. 가격차이가 없다고 하더라구요. 기름이나 다른종류로 교체하세요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1292567</t>
+  </si>
+  <si>
+    <t>화목난로 괜찮나요?</t>
+  </si>
+  <si>
+    <t>저희집은 심야보일러 전기요금 넘 많이 나오고 요금 아끼려다 보니 따뜻하지도 않아요 화목난로를 거실에 설치할지 고민인데요 화목난로 써 보신 분의 경험담 듣고 싶어요 또 화목이 좋은지 펠렛이 좋은지도 모르겠구요 화목난로를 산다 해도 제품이 너무 많다 보니 못 고르겠어요 도와주세요</t>
+  </si>
+  <si>
+    <t>RE안녕하세요~ 화목난로 장작공급만 어렵지않다면 좋은 선택일수 있구요 구옥에서 10년째 등유보일러&amp;화목난로 사용 중입니다</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1340660</t>
+  </si>
+  <si>
+    <t>단독주택사시는 분계신가요?</t>
+  </si>
+  <si>
+    <t>수도권말고 지방권에서 단독주택살고 싶은데 사면 다시는 못팔거 같아서 그게 젤 두렵네요 ㅠ 그리고 말들으니깐 기름보일러가 생각보다 많이들어서 겨울에 힘들다고 그러더라구요 대신 태양열 설치하면 에어컨이나 전기는 빵빵쓴다고 하네요 ㅎ</t>
+  </si>
+  <si>
+    <t>RE아시는분 이야기중 제일힘들었던건 쥐.. 벌레. 그밖에 잡초관리 잔고장 등이러고합니당. 그족은물론좀 도시는아니었어요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/skybluezw4rh/14296605</t>
+  </si>
+  <si>
+    <t>기름보일러 불편한점. 조언 부탁드립니다.</t>
+  </si>
+  <si>
+    <t>목욕탕하고 주방 두 개 설치해야하고, 전기온수기도 자리를 생각보다 많이 차지하고 설치 비용도 만만치 않네요(자가 설치는 유투브를 봐도.. 제 목욕탕과 주방을 보니 자신이 생기질 않습니다). 고민하다가... 가스비가 감당이 어렵다고 하나.. 역시 기름보일러는 적응이 좀 어렵네요. 혹시나 제가 기름보일러를 잘못사용하고 있는 걸까요? 도움 주시면 감사하겠습니다. ㅠ</t>
+  </si>
+  <si>
+    <t>RE온수사용하실때 가스보일러대비 온수가 얼마 나오지 않고 미지근하거나 찬물이 나옵니다</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1328294</t>
+  </si>
+  <si>
+    <t>시골집 기름보일러 어떻게 채우나요?</t>
+  </si>
+  <si>
+    <t>진입이 어려운데이러면 말통으로 채워야하나요? 아니면 기름차 호스가 갈 수 있나요? 그리고 기름차는 배달비 얼마나 받나요?!</t>
+  </si>
+  <si>
+    <t>RE그런집 많아서 최대진입하고 호스 빼서 넣어요~~ 저희집도 시골집인데 됩니다ㅎㅎ 그리고 돈은 똑같이 차 리터계산하듯이 받습니다 보통 한드럼~ 가능할거에요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/overseer/1483038</t>
+  </si>
+  <si>
+    <t>시골집 기름보일러 쓰다가 이제 lpg배관망 들어와서 그걸로 바꿨는데 이전보다 좋을지 안 ....</t>
+  </si>
+  <si>
+    <t>기름보일러 쓰다 lpg배관망 공사 들어간다 해서 당시 기름보일러보다 난방비 절약된다랑 거의 동네에서 다 바꾸는? 분위기라 백만원 넘게 주고 바꾸고 이제 공사 끝나고 사용하기 시작하는데 그 사이 먼저 lpg배관망으로 바꾼 동네 주민한테 물어보니 난방비가 오히려 더 나온다 백만원 주고 바꿀 필요없었다 속았다 등 안 좋은 평이 많아서 걱정되네요 일단 좋은 점은 이전 기름보일러에 비해 공간 차지하는게...</t>
+  </si>
+  <si>
+    <t>RE동네에 가스통 큰거? 에 각 집 분배 하는거는, 들어보니 그것도 꽤 나온다 들어습니다. 도시가스보다는 훨 많이 나오겠죠</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1299507</t>
+  </si>
+  <si>
+    <t>시골집난방에 기름보일러도 괜찮네요.</t>
+  </si>
+  <si>
+    <t>보일러는 12월 중순부터 가동했는데 보름동안 낮에는 창문 다 열고 16~7도로 바닥미장 말렸고, 이후 한 달 상시 거주한 기름값 계산해 보니 하루 평균 1만원이네요.(베이크아웃 비용 포함) 지금은 설정온도를 낮에 21도 밤엔 22도로 해두는데, 이른 아침에 한 번 점화되고, 초저녁에 한 번 점화되고 있어요. 도시가스가 안들어와서 피치못하게 기름보일러를 설치했는데, 비용이 괜찮네요.</t>
+  </si>
+  <si>
+    <t>RE주유소 전화하면 직접 와서 주유해주고 4드럼이면 그것도 자주 안하셔도 되겠네요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1218749</t>
+  </si>
+  <si>
+    <t>기름보일러 1년 사용량</t>
+  </si>
+  <si>
+    <t>기름보일러 1년 온전히 정상 사용했어요. 사용 환경은 -79년 세멘블럭조, 외단열 롱브릭외장, 리얼징크판넬 지붕, ls이중창으로 리모델링 한 집(실내 옛내장을 살리느라 우풍 쪼쪼금 있음) - 1층 17평에 다락 6~7평 - 2식구, 설겆이 보일러 온수사용, 동계 세탁기... 주1회이상 보일러 온수세탁, 실내온도 낮엔 19~20도 저녁엔 21도 - 보조난방기 없음 사용한 등유는 1,100리터 조금 못 미치네요. 단가는 리터당...</t>
+  </si>
+  <si>
+    <t>RE나는시골집.기름보이러.꺼두고다녀요.빈집이라서.생돈들어가니까요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1299307</t>
+  </si>
+  <si>
+    <t>시골집 난방 관련</t>
+  </si>
+  <si>
+    <t>겨울철 난방 중에 가장 가성비 있고 따뜻하게 보낼수 있는게 어떤 것이 좋을까요? 기름보일러,심야전기보일러,화목난로,전기판넬,냉난방기~~~ 등등</t>
+  </si>
+  <si>
+    <t>RE시골집은 기름보일러가 좋은것 같아요.. 도시가스는 들어오지 않았고 lpg 는 너무 비싸다라구요..</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/sigoljipmarket/15074</t>
+  </si>
+  <si>
+    <t>주택 신축 LPG 가스보일러와 기름보일러 선택</t>
+  </si>
+  <si>
+    <t>시골에 주택 신축을 계획하고 있는데, 기름보일러를 설치할 지, LPG 가스보일러를 설치할 지 고민이네요. 저희 군에서는 도시가스 공급을 현재 읍 지역까지만 하고있기에 향후 10년 이내에 저희 지역까지... LPG 벌크통을 설치할 경우 초기 비용이 300만원 정도 들게 되어 부담이 큰데요. 그럼에도 불구하고 가스보일러로 하는게 좋을지 그냥 기름보일러를 쓰는게 나을지 고민이 됩니다. 선택에 도움 주시면...</t>
+  </si>
+  <si>
+    <t>RE가스보일러 설치하세요. 보일러는 온수 전용으로 사용하고 난방은 참나무 장작 난로를 설치하는 것이 어떨까요? 난로 설치비가 비싸긴 한 데 난방비가 가스 대비 참나무 장작이 훨씬 저렴하고 화력이 좋아 실내온도를 25도 정도로 유지해도 별 부담이 없어요. 양평 전원주택</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1293805</t>
+  </si>
+  <si>
+    <t>기름 보일러 교체 고민</t>
+  </si>
+  <si>
+    <t>안녕하세요? 보일러 교체할지 고민하고 있습니다. 조언 부탁드려요. 현재 가스보일러인데 도시가스가 아니라 그런지 가스비가 엄청나오네요. 겨울에는 한달에 40만원 정도 기름보일러로 교체하면 연료비 절감이 가능할까요? 난방 면적은 방2, 거실포함 20평입니다. 새로 설치하는 비용과 연료비 비용 고려했을 때 교체해야 할지 고민 되네요. 날씨가 춥습니다. 다들 건강 잘 지키시길 ~</t>
+  </si>
+  <si>
+    <t>RE현재 LPG 단가를 먼저 확인하셔야 할 것 같습니다. 지역이나 개개인별로 LPG 단가가 천차만별이라서요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1220306</t>
+  </si>
+  <si>
+    <t>시골집 난방: 전기판넬에 대한 고려</t>
+  </si>
+  <si>
+    <t>보일러 난방(바닥 엑셀 파이프)을 생각하고 있었는데 상시 거주를 하지 않는 경우 동파 우려가 없다는 점을 들어 전기판넬이 좋다고 강추하는 분을 만난 후 흔들리고 있습니다. 전기판넬의 장단점을 다음과... 가스 또는 기름값)는 검토 대상에서 뺐는데 겨울철에 1~2일 거주하는 경우에도 난방비 차이가 클지는 모르겠습니다. 경험하신 분들의 고견을 부탁드립니다. 감사합니다.</t>
+  </si>
+  <si>
+    <t>RE바닥만 뜨겁고 공기는 차갑다가 가장 큰 단점 입니다.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1107021</t>
+  </si>
+  <si>
+    <t>기름보일러 겨울에 한달 얼마정도 쓰세요?</t>
+  </si>
+  <si>
+    <t>9월 요금 평균 5만원도 안넘었습니다 정속형 에어컨 두대 풀가동 했는데 말이죠 제가 더위를 별로 안타서 여름은 견디는데 겨울은 정말 울고 싶습니다 ㅠ 뼛속까지 시려워요 시골 오래된 집이라 보일러도 낡아가지고 .. 난방이 형편없습니다 보통은 가스비로 고민하시죠 저는 기름값이 걱정입니다 겨울에 바우처 지원되더라도 최대 50정도면 기름 채우는게 30만원이니까 .. 한달에 30 정도 쓰는것 같은데 아주아주...</t>
+  </si>
+  <si>
+    <t>RE예전에 기름보일러 쓸때 명절때 기름이 딱 떨어져서..주유소에서 기름통에 기름받아 손으로 나르던 생각나네요.. 월세방에 기름통이 작아서 자주 넣어야 하는데 퇴근시간 늦어서 넣는 시기 놓치던 생각 나네요..</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/cafe1535/1436839</t>
+  </si>
+  <si>
+    <t>시골살이 16년 이야기 [새집을 짓다]</t>
+  </si>
+  <si>
+    <t>난방은 1도 안되는 기름 보일러 24시간 가동해도 얼어죽기 딱 좋은 그런집이였습니다. 더구나 전주인이 이사가면서 기름통에 진짜로... 내 나이 70 평생에 우리 부부 시골살이 11년만에 꿈에 그리던 새집에서 살게 되었습니다. 동네 지인 몇분이 집들이 선물로 가전제품 그리고... 사실 우리집이 한달만 늦게 시작했으면 중단되거나 추가비용이 엄청 늘어났을지도 모릅니다. 돌이켜 생각해보니 앞집 여자가 싸움을 늦게...</t>
+  </si>
+  <si>
+    <t>RE재밌는 소박한 시골살이 글 늘 즐감합니다 감사합니다 다음편 기대요~^^</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1344282</t>
+  </si>
+  <si>
+    <t>시골집 단독주택 추위 외풍</t>
+  </si>
+  <si>
+    <t>시골집 직거래 시 기름보일러 난방비 꼭 확인해야 하는 이유</t>
+  </si>
+  <si>
+    <t>전국 시골집 직거래 매물 정보는 네이버카페 "시골어때"에서 확인 가능합니다. 기름보일러는 쉽게 말하면 "기름으로 집을 따뜻하게 만드는 난방기"입니다. 시골집이나 오래된 전원주택에는 아직도 기름보일러 사용하는 집이 많습니다. 도시 아파트처럼 관리비에 포함되는 게 아니라 직접 기름을 넣어 사용해야 합니다. 실제로 자주 생기는 상황 봄이나 여름에 집 보러 갔을 때는 괜찮아 보여서 계약했는데, 겨울이...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/buyland87/7253</t>
+  </si>
+  <si>
+    <t>연식 오래된 단독주택 볼때 팁 알려주세요~</t>
+  </si>
+  <si>
+    <t>중개인하고 통화할땐 집주인이 고양이 키워도 된다고 했다고 하고, 집 수리할거나 고장난거 있으면 직접 고쳐써야 한다고 했다네여.. 이런말 너무 불안한데.. 독채이긴한데 지역과 연식에 비해 좀 비싼거 같기도 하고..(비용지불에 무리는 없어요.) 지방이라.. 단독주택이나 전원주택 월세매물이 너무 귀하긴 합니다. 단독주택 사시는 분이나 기름보일러 잘 아시는 분 조언 부탁드립니다! 뭐봐야되고 뭐체크하면...</t>
+  </si>
+  <si>
+    <t>RE기름 보일러면 절대 들어가지 마세요. 24평 기준 겨울에 기름값 50~70만원입니다. 이것도 아꼈을 경우이고 한달 기름값입니다..한겨울에 시골가면 할머니들 모두 마을 회관 모여 있는 이유가 있어요. 전기 장판 필수구요.. 81년이면 옛날 단열 안됐다면 더 들어요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/ilovecat/7927111</t>
+  </si>
+  <si>
+    <t>시골이라 도시가스가 안들어오는데...난방을 어떻게 해야 할까요?</t>
+  </si>
+  <si>
+    <t>집이 단독인데 산밑이고 도시가스도 안들어오는데.. 장마철에는 비도세고 겨울에는 우풍이 심해서.. 바닥이 아무리 따뜻해도 잘 때 너무 춥습니다. 다름이 아니라 요새는 어떤식으로 난방을 할까요?... 하는지 아니면 그냥 기름보일러를 하시는지 ... 단독주택은 다들 어떤식으로 난방을 하시나요? 새로나온 공법이나. 추천해주실 수 있는 방법 있으신지 고견 여쭤봅니다. 집이 50평대 2층집 입니다. 감사합니다.</t>
+  </si>
+  <si>
+    <t>RE전기판넬은 절대 비추세요. 전기요금 폭탄인데 복사난방 효과가 없어서 돈은 돈대로 쓰고 난방효율이 돈 값을 못합니다</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1302847</t>
+  </si>
+  <si>
+    <t>45년된 단독주택 단열후 메탈사이딩 으로 마감 하고 있어요</t>
+  </si>
+  <si>
+    <t>안녕 하세요 25년간 아파트 생활접고 단독으로 이사온지 2년 되었습니다. 처음에는 집을 새로 지을까 해서 알아 보았고. 목조 구조로 지으면 비용은 많이들지 않을것 같아 그리하려 했으나 본 집은 부모님께서 지으셨고 제가 25살까지 거주했던 추억이 있는 집이이서 고민 하다가 수리해서 우선 살아보기로 하여 입주전 내부 인테리어를 했고. 외부 벽돌들이 오래 되다보니 그 기능도 못하는 상황이어서 여러 마감을...</t>
+  </si>
+  <si>
+    <t>RE최고입니다 ᆢ자신이 살던 집을 다시 손봐서 고쳐서 살면 되지요 ᆢ다 털어버리고 다시 지은것 보다 더 장감있고 ᆢ한 오십년 살다가 싫증나면 문제 생기면 그때 아들보고 새로지어 살아라 하면 되요 ᆢ아니면 손자보고 새로 지어라 하면되고 ᆢ</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1221068</t>
+  </si>
+  <si>
+    <t>겨울 시골주택의 문제점 입니다.</t>
+  </si>
+  <si>
+    <t>경기 연천 청산면 초성리에 있는 30년된 단독 주택 입니다. 매도자는 어차피 집의 단점은 말하지 않고 매도 하니 지내면서 문제점들이 나타 나는지도 모르 겠네요. 제일 심각한건 결로 입니다. 거실쪽은 안쪽 창이 있고 25센티 정도로 여유두고 다시 바같 창이 있어서 그런지 아무래도 결로가 그나마 덜 합니다. 방3개와 주방쪽 창문과 뒷문의경우는 심하구요. 전체 방통을 했기때문 인지도 모르지만 안과 밖의...</t>
+  </si>
+  <si>
+    <t>RE단순 창문의 성능문제인지 아니면 실내측과 외부측 온도차로 발생되는 결로인가를 먼저 판단하시고 창문을 바꾸던 단열을 보강하던 결정하셔야 될겁니다. 지금보면 단순 창문만 바꾼다고 해결되 보이진 않습니다.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/981450</t>
+  </si>
+  <si>
+    <t>꼭대기층?어떤가요?</t>
+  </si>
+  <si>
+    <t>흔히 최상층은 어름에 덥고 겨울에 춥다고 하잖아요~ 요즘지어지는 아파트들은 어떤가요? 단열이 잘되어 그렇지 않다 하시는분도있고 ..실제 살아보신분들 어떤라요?</t>
+  </si>
+  <si>
+    <t>RE마자염..윗분말처럼 단점을 말하자면 엘베 오래기다리는거? 외에는 없어요. 층간소음없고 뷰좋고 ㅎㅎ</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/krokr/663006</t>
+  </si>
+  <si>
+    <t>20년된 시골 단독주택 문의입니다.</t>
+  </si>
+  <si>
+    <t>강원도 원주소재의 단독주택입니다. 패시브하우스로 리모델링 가능할까요? 준공연도 : 1996년 건평 : 30평(1층 단독) 건축 : 콘크리트 벽돌(빨간벽돌의 시골집). 지붕 : 큰크리트 슬라브옥상(누수는 없음) 베란다 유무 : 건물 전면은 시멘트바닥과 손잡이만 있는 외부형 베란다. 뒷면은 부엌과 연결된 베란다로 판넬과 창문으로 둘러쳤음(그러나 매우 추워서 겨울에 세탁기 꽁꽁 엄) 대지 : 170평 난방 : 심야전기(한겨울...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/smartgtec/857</t>
+  </si>
+  <si>
+    <t>lpg 가스 보일러 2달 사용기...</t>
+  </si>
+  <si>
+    <t>집 현황 대략 32평정도이고 단열수준은 와풍이 느껴지지 않는 수준. 5인가족 , 온수는 36도로 고정. 온수사용시간은 매일 2~3시간 내외. 삼시세끼 꼬박꼬박 가스렌지 사용. 보일러는 경땡 콘덴싱 27k 2. 가스... 추위타는 사람은 약간 썰렁함 느낄정도. 하루 사용량 2.9루베 (기스렌지 사용량 미포함) ★ 온돌모드는 꾸준히 사용해야 효율이 좋음듯함. 낮동안 식은 바닥 데우기 위해 소모량이 많은듯함. d. 밤부터...</t>
+  </si>
+  <si>
+    <t>RE3년째 lpg가스 어떻게 해야 덜 나올까 따뜻하게 지낼까 아직도 해답을 모르겠어요 25평 온수사용(전기)외풍이 심해서 온돌 가장 낮은온도로 사용해보니 3루베 쓰더라구요 엄청 따뜻하지는 않지만 약간 훈훈한정도..한파 아니면 예약모드로 4시간에 20분(밤과 새벽 4번정도1시간</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1113794</t>
+  </si>
+  <si>
+    <t>주택사시는 분들^^ 많이 추우실까요? 주택가고파요~~~</t>
+  </si>
+  <si>
+    <t>어려서 혹시나 저녁에 너무 추울까 걱정되서 겨울되고는 자고 온적은 없어요 (윗지방 사시는분 들에 비해 따듯한 남쪽이지만요 ^^) 항상 주택에 대한 로망은 있지만^^;; 주택 = 춥다 는 생각이 함께 있어요~~ 이번에 꽃씨를 나눔받고 또~ 나눔받게 되다보니 이쁜 꽃을 항상 보고 싶은 맘이 더 커지네요 토지를 보고 주택은 나중에 지을 생각을 해야하는지 토지 보고 왠만한 주택 리모델링할 생각을 해야하는지 요즘 주택은...</t>
+  </si>
+  <si>
+    <t>RE신축1층 필로티 2층 3층 주거인데 어제밤에 보일러 1시간정도 돌리고 지금까지도 22도 유지되어서 보일러가 안도네요 설정온도는 20도로 설정해놨거든요 구축아파트 살다가 왔는데 따뜻하고 좋아요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1105162</t>
+  </si>
+  <si>
+    <t>난방비 얼마나 나오시나요?</t>
+  </si>
+  <si>
+    <t>수도권에서 살때는 지역난방이라 23도로 살아도 한달에 2만원정도 나왔고 20평대인데 보일러를 안틀어도 바닥이 따뜻했어요. 주택에 살아보니 도시가스 지역난방이 안들어와서 기름보일러 쓰고있습니다. 단층만 보일러틀면 30평이고 추워도 16도로 사는데 한달에 기름 1드럼채워요 (25만원) ㅠㅠㅠㅠ 저희옆집은 애들이있어서 한달에 4드럼 채운다네요..(100만원 후덜덜)</t>
+  </si>
+  <si>
+    <t>RE남해안 집을 단열 빵빵하게 지어 겨울에도 외풍 전혀 못느껴서 아파트 같은데 내복 입고 기름보일러 2드럼이면 안춥게 1년 넉넉할 것 같아요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1118434</t>
+  </si>
+  <si>
+    <t>황토벽돌방 단열문의</t>
+  </si>
+  <si>
+    <t>단독주택을 신축했는데 그 중 방 하나를 황토방으로 만들었습니다. 골조는 콘크리트인데 벽면을 그 안으로 30cm 황토벽돌을 쌓아서 만들었는데요.. 바닥은 일반 강화마루입니다. 일반적으로 알기를 황토는... 창도 크지않고...엘지2중창에 한옥창으로 덧대었고 혹시나 몰라 외풍인가 싶어 창쪽에 커튼까지 치고 자는데 시골집처럼 바닥은 따뜻하고 공기는 차갑습니다. 이불을 어깨까지 덮지 않으면 시려요......</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/tujunkr/1274</t>
+  </si>
+  <si>
+    <t>경남 창원 북면 외감리 주택거주후기</t>
+  </si>
+  <si>
+    <t>유형 : 단독주택 작성 방법: 원룸, 오피스텔, 빌라, 아파트, 단독주택, 상가, 사무실, 고시원, 쉐어하우스, 지식산업센터 중 선택 ❓ 주소 :경남 창원시 의창구 북면 외감리 449번지 작성 방법: 상단의... 단점 : 시골이라서 기름보일러인점 겨울에 외풍이 있어 추운편 ❓ 그 외 거주 후기 : 없음 작성 방법: 없을 경우 '없음' 기재 ❓ 이 집을 다른 사람에게 추천하시나요? (예/아니오) 예 : 예 작성 방법: 예...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kig/18538884</t>
+  </si>
+  <si>
+    <t>바다가 예쁜 협재 해수욕장 근처 농가주택 한달 살기 있습니다.</t>
+  </si>
+  <si>
+    <t>날씨가 추워지는 11월 부터 3월까지 비수기 기간동안 저렴한 가격에 한달살기 예약을 드리고 있습니다. 3개월 이상 예약하시는 손님들께는 한달살이 요금에서 조금 더 할인 해 드려요~ ^^ *** 농가주택의 특성상 겨울에 외풍이 조금 있습니다. 해서 겨울동안 할인된... ^^ &lt;301 호&gt; 한달살기 60만원 / 보증금 30만원 / 전기 가스 요금 별도 / (1월 1일부터 가능) 작은 마당이 있고 옛날 마루가 멋진 시골 집입니다....</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/seogwipoguesthouse2/39334</t>
+  </si>
+  <si>
+    <t>날씨가 덥네요ㅠㅠ</t>
+  </si>
+  <si>
+    <t>84년만의 5월 더위랍니다ㅜㅜ 우리아가 단독주택의 외풍과 하체는 거의 벗겨키워서 그런지 열이 많은 편인것같아요. 또 어제... 아이고~~~ 겨우겨우 남편이 80미리 더먹이고(잘 때는 항상 200미리 먹여요), 꽁꽁 닫아둔 창문도 살짝열었어요(집 근처 공장있고 시골이라 밤에... 잘때 선풍기 틀어주시나요? 요렇게 창문 열고 자면 새벽에 춥겠죠? 겨울엔 추위걱정, 여름엔 더위걱정ㅠㅠ걱정인형 장만해야겠어요ㅋㅋ</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/cottondiaper/127670</t>
+  </si>
+  <si>
+    <t>5살 현서 - 126일</t>
+  </si>
+  <si>
+    <t>아토피 때문인지...^^; 빰에 뾰루지 같은건 참.. 지치지도 않나... 끊임이 없네요. 한개 올라와서 다 뽑아냈나 싶음 10개도 올라오고... 오늘은 요만큼.. 계속 비누샤워만 해도 될까요? 물론 파우더해야 더 좋은줄은 알지만.......... 외풍 심한 단독주택.. 게다가 파주 산밑 시골마을.. 많이 추워요ㅋ 알죠.. 핑곈거.....^^;;;;;;;;;; 댓글 주시는거 보고 내일 주문할게요. 제품이 다들 가벼워져서 이번엔 싹 해야할듯 싶어요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/atopycompletecure/13089</t>
+  </si>
+  <si>
+    <t>몬스 겨울 바람막이 패딩 방한커튼 장단점</t>
+  </si>
+  <si>
+    <t>날씨가 갑자기 확 추워지니 따뜻하다고 느끼던 집이 다시 추워져서 3개 더샀어요...ㅋㅋ 거실에 3개 겹쳐달았더니 너무 좋은거있죠??ㅋㅋ 보일러 2시간 틀었는데 더워서 베란다 왓다갓다햇어요 냉기차단 진짜... 누빔이중커텐으로(시골 주택엄마집은 작년에 이 커텐으로 도배하다시피) 넓은 1층 거실창은 넓은 폭 누빔속커튼으로. 기존 커텐의 분위기 유지시켜주고 .. 폭이 좁거나 층고낮은 창은 이 누빔커튼으로...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/goodgart/16384</t>
+  </si>
+  <si>
+    <t>6-4.의료인프라_응급상황_골든타임결핍</t>
+  </si>
+  <si>
+    <t>귀촌 병원 멀어서 응급</t>
+  </si>
+  <si>
+    <t>귀촌 준비할 때 지역 선택 기준을 이렇게 잡았어요</t>
+  </si>
+  <si>
+    <t>귀촌을 결심했을 때 지역 선택이 제일 어려웠어요 여기저기 좋다는 말은 많은데 막상 어디로 가야 할지 기준이 없었어요 저는 이런 기준으로 좁혀갔어요 의료 인프라 거리 나이가 들수록 병원이 가까운 게 중요해요 응급 상황이 생겼을 때 30분 안에 갈 수 있는 병원이 있는지 큰 병원까지의 접근성도 함께 봤어요 가족이 오기 편한 거리 명절이나 가끔 자녀들이 방문할 때 KTX나 고속도로 접근이 편한지를 봤어요 너무...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/fmjs5/20037</t>
+  </si>
+  <si>
+    <t>귀농·귀촌 전에 알아두면 좋은 준비사항 50가지</t>
+  </si>
+  <si>
+    <t>귀농·귀촌 전에 알아두면 좋은 준비사항 50가지 박 흥열추천 0조회 2126.10.19 11:04댓글 0 게시글 본문내용 귀농·귀촌 전에 알아두면 좋은... 진입도로 직접 이용해 보기 승용차뿐 아니라 이삿짐차, 택배차, 응급차가 접근할 수 있는지도 살펴보세요. 27. 폭우 때 물길 확인하기... 병원까지 걸리는 시간 확인하기 평소 진료받는 진료과와 응급실을 실제로 이용하기 편한지 살펴보세요. 42. 약국과 장보기 동선 확인하기...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/jungsukgo/40604</t>
+  </si>
+  <si>
+    <t>귀촌지를 찾을 때 병원의 위치에 대한 저의 생각...</t>
+  </si>
+  <si>
+    <t>'아는 사람이 55살인데 물을 마시다가 사레를 들렸는데, 응급실로 가야만 했고 그길로 중환자실에 들어가서 삶을 마감했습니다. 늙어서 사는 곳에서 병원은 가까운 게 최고이니 병원 가까운 곳에 사는 분들은 절대 거주지를 옮기지 마시길...' 저는 이런 생각이 들었습니다. '나... 나랑 비슷한 나이대인데 그런 사소함으로 삶을 달리했네. 안타깝네... 병원 접근성이 좋은 서울에 살아도 어쩔 수 없는 일이 생기는구나....</t>
+  </si>
+  <si>
+    <t>RE딱 정답 이네예ᆢ 내 편한곳에서 즐기다 깨꼬락찌 할람미더ᆢㅎㅎ</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1286535</t>
+  </si>
+  <si>
+    <t>귀촌 생활에서 예상보다 중요한 의료시설 접근성</t>
+  </si>
+  <si>
+    <t>처음에는 집과 농지, 주변 풍경만 중요하게 생각하기 쉽지만 생활을 시작하고 나면 병원과 약국, 응급의료시설까지의 거리가 예상보다 큰 영향을 미친다는 사실을 체감하게 됩니다. 귀촌은 단순히 거주지를... 응급실이 있는 병원까지 이동 시간이 얼마나 걸리는지, 야간 진료가 가능한 의료기관이 있는지도 미리 확인하는 것이 좋습니다. 지역을 선택할 때는 병원뿐 아니라 약국과 보건지소, 보건소의 위치도 함께...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/adangzzang/9275</t>
+  </si>
+  <si>
+    <t>귀촌 후에 편의시설 거리가 멀어서 불편한 점은 없으셨나요?</t>
+  </si>
+  <si>
+    <t>특히 아이들이 아직 어려서 갑자기 아프거나 하면 큰 병원까지 이동 시간이 길어질까 봐 염려됩니다. 지금 생각하는 귀촌지는 가장 가까운 읍내 마트나 병원까지 차로 20분 정도 걸린다고 하더라고요. 실제로 귀촌해서 살아보신 선배님들은 이런 불편함을 어떻게 해결하고 계신가요? 혹시 장 볼 때는 한 번에 많이 사두시는 편인가요? 아니면 정기적으로 도시를 나가시는지 궁금합니다. ㅠㅠ</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/adangzzang/5065</t>
+  </si>
+  <si>
+    <t>저는 완전 귀촌은 못할 듯 합니다.</t>
+  </si>
+  <si>
+    <t>응급상황이었을 때는 모두 위험한 상태였고 응급 수술 받으신 적도 있었기에 대형 병원이 멀지 않은 곳에 있는 게 무척 다행이라고 느낀 적이 여러번이었습니다. 게다가 입원을 하시더라도 자주 들를 수... 다시 돌아오신 이유도 병원 때문이었습니다. 글이 좀 어수선하고 조금 신세 한탄조도 들어가긴 했습니다만, 저 아래쪽에 어느 분이 쓰신 귀촌지 조건을 묻는 글을 보고.. 오늘 고생하면서 새삼 의료 서비스의...</t>
+  </si>
+  <si>
+    <t>RE맞습니다 저도 이번에 친정 아부지가 많이 편찮으시니 지방이라도 나이들면 대학병원 근처에 살아야 겠다고 절실히 느꼈습니다</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/972929</t>
+  </si>
+  <si>
+    <t>귀촌 초보자라면 집부터 사지 마세요｜세컨하우스·전원생활 시작 전 꼭 확인할 것</t>
+  </si>
+  <si>
+    <t>너무 외진 곳은 병원·마트 이용, 제설, 응급상황, 차량 이동, 보안, 택배, 인터넷 등에서 불편할 수 있습니다. 따라서 '완전히 고립된 집'보다는 생활 편의시설과 너무 멀지 않으면서 이웃과 일정한 거리를 확보할 수 있는 곳을 찾는 것이 현실적입니다. 이웃과는 '가깝게'보다 '예의 있게' 귀촌했다고 해서 모든 마을 행사에 적극적으로 참여하거나 모든 이웃과 친해져야 하는 것은 아닙니다. 반대로 아무에게도 인사하지...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/nongchondle/863</t>
+  </si>
+  <si>
+    <t>귀농 귀촌 준비 체크리스트: 생활비, 교육, 의료, 교통까지</t>
+  </si>
+  <si>
+    <t>건강할 때는 병원 거리가 크게 느껴지지 않지만, 정기 진료나 응급 상황이 생기면 접근성이 중요한 기준이 됩니다. 특히 50대 이상이나 은퇴 후 귀촌을 준비하는 경우라면 가까운 병원, 약국, 보건소, 응급실까지의 이동 시간을 반드시 확인해야 합니다. 생활 인프라가 부족한 지역은 조용하다는 장점이 있지만, 장기 거주에서는 불편이 커질 수 있습니다. 교통 역시 귀농귀촌 현실에서 자주 부딪히는 문제입니다. 농촌...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/adangzzang/8549</t>
+  </si>
+  <si>
+    <t>노후에 근처 대형병원이 그렇게 중요한가요?</t>
+  </si>
+  <si>
+    <t>저는 귀농귀촌 카페이서도 활동 하는데 게시글 중에서 나이 많으면 병원 때문에 도시에 살아야 하냐는 분에 대한 댓글이 있어서 가져와 봤습니다. 남해안 땅 끝 시골 사람이나 동탄에 사는 사람이나 죽게... 삼성병원에 가게 됩니다. 왠만한 질병은 지역마다 거점 병원 다 있구요. 그리고 생각보다 사람 생명 질깁니다. 인명은 재천이라고 응급실 가깝다고 살 사람은 살고 조금 멀다고 죽는것 아니예요. 도시에 사는 30...</t>
+  </si>
+  <si>
+    <t>RE직접 경험해보지 못한 것을 당장 이해하기는 어렵습니다. 눈을 들어 주변을 돌아보시면 다양한 삶의 모습들이 눈에 들어옵니다.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/ehdxks2/699495</t>
+  </si>
+  <si>
+    <t>귀농·귀촌 준비 체크리스트: 생활비, 교육, 의료, 교통까지</t>
+  </si>
+  <si>
+    <t>특히 고령층 귀촌인의 경우, 의료 접근성은 삶의 질을 좌우하는 요소예요 확인해야 할 사항 읍내까지 병원 이동 시간 (응급실 기준 30분 이내가 이상적) 보건소 진료일 및 야간 운영 여부 근처 약국·응급차 배치 현황 요양병원이나 재활의학과 존재 여부 이건 정말 현실적인 포인트예요. 농촌에서는 단순 감기약도 “차 타고 읍내까지 가야” 하는 경우가 많습니다. 또, 일부 지역은 119 구급차가 ‘타 지역 관할’인...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/adangzzang/2888</t>
+  </si>
+  <si>
+    <t>은퇴 후 귀촌 준비, 병원 접근성 어떻게 해야 할까요?</t>
+  </si>
+  <si>
+    <t>병원 외에도 약국이나 응급 상황 발생 시 대처하는 것이 정말 중요하다고 느껴요. 그래서 여러 동네를 둘러보면서 교통편이나 병원 위치를 체크하고 있는데, 확실히 중요한 요소 같아요. 귀촌할 시기에 무엇보다도 필요한 것이 병원까지의 접근성이겠죠. 혹시 귀촌하신 분들이나 계획 중인 분들께 여쭤보고 싶은 것이 있어요. 은퇴 후 귀촌을 고려할 때 병원 접근성 문제는 어떻게 해결하셨나요? 실제로 느꼈던 불편한...</t>
+  </si>
+  <si>
+    <t>RE병원 접근성에 대한 고민, 저도 공감해요. 주변에 병원이 가까운 곳을 찾는 게 정말 중요하죠.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/makeho/94301</t>
+  </si>
+  <si>
+    <t>농촌살이의 의료 환경, 어떤 점을 미리 알아봐야 할까요?</t>
+  </si>
+  <si>
+    <t>요즘 이사하려는 지역의 의료 기관을 돌아보며, 응급 상황 시에 얼마나 빠르게 대처할 수 있는지, 그리고 주변에 돌봐줄 수 있는 응급 요원이 있는지도 따져봐야겠다는 생각이 들었습니다. 특히 농촌 지역에서 생활하면서 만약 제가 아프거나 가족 중 누군가가 병원에 가야 할 상황이 생기면 정말 걱정될 것 같아요. 의료 환경이 과연 적절한 수준인지, 또 의사 선생님들이 신뢰할 수 있는 분들인지가 제게는 사소한...</t>
+  </si>
+  <si>
+    <t>RE농촌에서의 의료 환경은 정말 중요한 문제죠. 저도 비슷한 고민을 했던 적이 있는데, 가까운 의료 기관의 평판을 미리 체크하는 게 좋더라고요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/makeho/92955</t>
+  </si>
+  <si>
+    <t>은퇴 후 귀촌, 의료 접근성 걱정이 크네요</t>
+  </si>
+  <si>
+    <t>마땅한 병원이 없더라고요. 이곳의 의료 환경은 어떻게 되는 건지 걱정이 앞서요. 예를 들어, 일상적인 건강검진이나 응급상황이 발생했을 때 대처할 수 있는 시스템이 제대로 갖춰져 있을지 의문이 드네요.... 혹시 은퇴 후 귀촌을 하신 분들 중에, 병원 접근성을 고려한 경험담이나 유용한 정보가 있을까요? 좀 더 어떤 점을 체크하고 확인해야 할지 알고 싶어서요. 여러분의 다양한 조언이나 이야기를 듣고 싶습니다.</t>
+  </si>
+  <si>
+    <t>RE병원 접근성 문제는 정말 중요한 고민이죠. 제가 아는 지역도 처음엔 불편했는데, 이사 후에 점점 알게 된 병원들이 생겼어요. 이런 것들이 시간이 지나면서 해결될 수 있으니 너무 걱정만 하진 마세요!</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/makeho/92820</t>
+  </si>
+  <si>
+    <t>전원주택을 선택할 때 교통 접근성을 놓치면 안 되는 이유</t>
+  </si>
+  <si>
+    <t>특히 자녀가 있는 가정이나 부모님과 함께 거주하는 경우에는 응급 상황에 대한 대비도 필요합니다. 실제 귀농귀촌 사례를 살펴보면 자연환경에는 만족했지만 병원 접근성이 좋지 않아 생활에 불편을 느끼는 경우도 종종 있습니다. 겨울철과 장마철 교통 여건도 함께 확인해야 합니다. 평소에는 괜찮아 보이는 도로도 눈이 많이 오거나 비가 많이 내리면 상황이 달라질 수 있습니다. 특히 경사가 심한 지역이나 폭이...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/adangzzang/8950</t>
+  </si>
+  <si>
+    <t>(후기) 아○대학교 요양병원 이용 중 느낀점</t>
+  </si>
+  <si>
+    <t>귀촌 언니가 정보 나눔해 주셨지만 결정 내리기 어려웠음. ㅠㅠ 요양 병원에 대해 미리 고민은 했으나 결정은 못한 상태에서 퇴원 임박하여 아주대학교요양병원에 입원 문의 하고 들어옴. (요양병원 입원... 아침 07시 / 점심 12시 / 저녁 17시 나는 집이 너무 멀어서 ㅠㅠ 병실 언니들이 반찬 선물 받으면 식사 때마다 나눠주시고 막내라고 이것 저것 챙겨주셔서 감사함. 5. 택배 시킬 수 있음: 쿠빵_프레시 완전 좋아요....</t>
+  </si>
+  <si>
+    <t>RE수술 후 열오르는것 유심히 관찰 해 보셔야 해요ㅠ 아주대 치료받는 분들께 아주 유용한 정보가 되겠네요 깨끗한고 원내 시설이다보니 진료나 응급조치 편하겠어요 다만 식사가 일반적인 요양병원비해 간소한단 느낌 든단 얘기 들은듯해요 시설이랑 식판 사진도 궁금해</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/gabomcafe/8391</t>
+  </si>
+  <si>
+    <t>충남 서천 귀촌향 집+밭 팝니다.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/binjib/68328</t>
+  </si>
+  <si>
+    <t>도시를 떠나 귀촌해서 조용히 살고 싶은 분들이 있다면 읽어 보세요.(첫번째)</t>
+  </si>
+  <si>
+    <t>아시겠지만 대형병원 하나 없는 농촌은 응급 상황 발생시 이동하다가 죽을 확율이 높아요. 단양은 제천시내와 차로 약 30분 거리이고 대형병원과 대형마트등 대도시에 있을만한 것들이 다 있어서 괜찮겠다 싶었습니다. 원주까지는 차로 약 1시간 거리이고... 이 정도면 되겠다 싶었어요. 서울도 사실 차가 막혀서 북쪽동네에서 남쪽 동네에 있는 병원으로 가려면 30분가지고는 어림도 없어요. 제천시는 규모가...</t>
+  </si>
+  <si>
+    <t>RE저는 단양 놀러 바람 쐬러 두번정도 간 거 같아요. 개인적인 생각이지만 단양 물,음식이 몸에 잘받아서 좋은기억이 있는지역입니다, 지금은 김포에 살고있지만 봄,여름.가을에는 본가인 강화도로 2주에 한번은 꼭 갑니다. 일하러갑니다, 사실 똑 까놓고 얘기하면 시골 텃새</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1290958</t>
+  </si>
+  <si>
+    <t>귀어 정착교육 지역 선택 시 교통, 병원, 생활편의 중 무엇을 우선해야 할까요?</t>
+  </si>
+  <si>
+    <t>예를 들어, 교통이 편리하면 이동하는 데 수월하긴 한데, 병원이 멀면 아프거나 응급 상황일 때 걱정이 되기도 합니다. 반대로, 병원이 가까우면 안심이 되지만, 교통이 불편하면 가족이 자주 오기 힘들겠죠. 생활 편의시설이 풍부한 지역도 그 자체로 매력적이긴 하지만, 너무 복잡한 곳은 또 불편할 수 있잖아요. 전반적으로 어떤 요소를 가장 중요하게 여기는지 궁금해요. 제가 이 세 가지 중에 무엇에 가장 중점을...</t>
+  </si>
+  <si>
+    <t>RE교통 편의성은 정말 중요한 것 같아요. 아무리 병원이 가까워도 이동이 불편하면 힘들죠.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/makeho/96000</t>
+  </si>
+  <si>
+    <t>귀농 자금 지역 선정 시 교통·병원·생활편의 중 무엇을 먼저 고려해야 할까요?</t>
+  </si>
+  <si>
+    <t>농사를 짓다 보면 몸이 아플 수도 있고, 갑자기 응급 상황이 생길 수도 있잖아요. 그런데 생각해보니, 병원이 가까운 것만으로는 부족할 것 같다는 느낌이 들었어요. 교통이 불편하면 병원에 가는 것도 쉽지 않을 테고, 외부와 연결이 끊기면 일이 다소 힘들어질 것 같아서요. 또한, 생활편의 시설이 부족하면 기본적인 생활이 어려워질 것 같다는 걱정도 듭니다. 식료품을 사러 나가야 할 때마다 너무 멀다면 상황이 더욱...</t>
+  </si>
+  <si>
+    <t>RE교통이 정말 중요해요. 병원도 필요하지만, 외부와의 연결이 끊기면 생활이 불편하니까요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/makeho/95579</t>
+  </si>
+  <si>
+    <t>귀농(귀촌)을 위해 토지 구입 유의점</t>
+  </si>
+  <si>
+    <t>그런데 사람들은 대부분 막연한 전원생활의 상상만 하고, 귀농인지 귀촌인지 용도를 특정짓지 않고 오는 경우가 참 많네요. 전원주택을 짓고, 빈 방을 민박이나 게스트하우스로 꾸미겠다고... 아니면... - 뇌출혈 등 나이들면 병원에 다닐일이 많고 응급상황이 발생했을 때 촌각을 다투게되는데, 첩첩 산중에 나홀로 집을 지은 경우는 큰 애로를 겪게됩니다. 우리집에서는 5분내에 강릉 아산병원에 도착이 가능. 8....</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/dlxogns01/19183</t>
+  </si>
+  <si>
+    <t>전원주택에서 반려동물과 함께 생활할 때 고려해야 할 점</t>
+  </si>
+  <si>
+    <t>가까운 동물병원과 반려동물 용품점, 응급 상황에 이동할 수 있는 도로 여건 등을 미리 확인하면 예상하지 못한 상황에도 빠르게 대응할 수 있습니다. 도심에서는 당연했던 편의시설이 농촌에서는 거리가 먼 경우도 있기 때문입니다. 이웃과의 생활도 중요한 부분입니다. 반려견의 짖는 소리나 산책 동선은 이웃과의 관계에 영향을 줄 수 있습니다. 서로 배려하는 생활 습관을 유지하면 전원생활의 만족도도 더욱...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/adangzzang/9129</t>
+  </si>
+  <si>
+    <t>귀촌 주택 구입 후 주변 생활시설이 걱정이에요</t>
+  </si>
+  <si>
+    <t>또한, 만약에 응급 상황이 생긴다면 제일 가까운 병원은 얼마나 될지 궁금해요. 시골에서의 생활은 나름의 매력이 있지만, 생활의 기본적인 요소를 따지다 보니 점점 더 혼란스럽더라고요. 이런 고민이 더해지면서, 혹시 귀촌 생활 하시는 분들은 주변 시설은 어떻게 이용하시는지도 궁금해졌어요. 실제로 귀촌을 경험한 분들의 조언이 절실합니다. 여러분들은 주변 생활시설은 얼마나 괜찮으신가요?</t>
+  </si>
+  <si>
+    <t>RE주변 생활시설 걱정 정말 공감해요. 저도 귀촌했을 때 마트가 멀어서 처음엔 힘들었거든요. 하지만 시간이 지나면 지역 주민들과의 관계가 더 소중해지더라고요!</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/makeho/88820</t>
+  </si>
+  <si>
+    <t>공주 시민이자 맘카페 회원님들의 다양한 현실 질문을 공주시장 후보님께 전해보려 합니....</t>
+  </si>
+  <si>
+    <t>✔ 병원, 교육, 교통은 나아질까? ✔ 지금 불편한 것들이 해결될 수 있을까? 이런 현실적인 이야기들을 회원님들 목소리로 직접 전달하고 싶어요. 이런 질문들 남겨주세요! 아이 키우기 좋은 공주 만들 계획 있나요? 소아과·응급의료 부족 문제 어떻게 해결하나요? 교육 때문에 세종 가는 현실 바뀔 수 있나요? 주차·교통 불편 해결 방법은요? ️ 지역 상권 살릴 방안은요? 젊은 부부가 공주로 오게 할 정책 있나요? 공원...</t>
+  </si>
+  <si>
+    <t>RE대형마트나 아이들병원은 대전세종으로 다니고있고 중학교를 몇년뒤 보내는 입장에서 시내로 가는 교통수단도 힘들다는데 시집와서 11년사는동안 발전된게 없네요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/gongju2008/672656</t>
+  </si>
+  <si>
+    <t>시골 아플때 병원 가기 힘들어</t>
+  </si>
+  <si>
+    <t>시골살이 16년 이야기 [돈 벌다]</t>
+  </si>
+  <si>
+    <t>전편에 적었듯이 시골에서 수입은 너무 어렵더군요. 농삿일 쉬워 보여도 처음 하는 사람은 병원이나 약국 돈벌어주기 바쁘더라구요. 나이들어 돈때문에 힘들어지니 인생이 고달퍼지고요. 돈은 도시에서 버는게 좋을것 같은 생각에 다시 돌아갈려니 그것도 이제 불가능으로 다가오고 심각해집니다. 살고있는 집하나만 달랑있으니 더구나 옆지기 고생하는 모습을 보고있으려니 가슴이 아프더군요. 이런 산골에서...</t>
+  </si>
+  <si>
+    <t>RE요즘 우리동네도 보면 자손들이 하는게 아니라 벌초대행을 하시더라구요. 남자분 예초기로 깍으면 여자분이 갈퀴로 긁어내시고.. 혹시 현덕님? ㅎ</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1345095</t>
+  </si>
+  <si>
+    <t>하소연 한번 하겠습니다 (아빠 고집 ~~~~~)</t>
+  </si>
+  <si>
+    <t>모시고 병원에 영양제 맞으러 갔더니 입원하는게 좋겠다고 하여 5일동안 입원 하셨고 저는 황금같은 10월 두번째 연휴에 병원에서 간병인을 했습니다 퇴원하고 근처에 사는 언니가 자주 들러서 식사 챙기고 했어요 16일에 치과치료 완료(임플란트+틀니)해서 식사를 좀 잘 하시려나 했는데 주말에 갔더니 아직 죽만 드시더라고요 어제 아침도 밥을 국에 말아서 쬐끔 드셨어요 힘도 없을것 같은데 오전 10시쯤되니...</t>
+  </si>
+  <si>
+    <t>RE저희 시골 동네의 저희 어머님 포함 동네 어르신들이랑 비슷하네요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1345663</t>
+  </si>
+  <si>
+    <t>20261013(화)</t>
+  </si>
+  <si>
+    <t>안될거같아 시골에 내려갈 생각을 했찌만 그것도 쉽지않을거라는 현실조언도 듣구 두런두런 했던 이야기들 모두가 넘 따뜻하구 행복하구 이게 일상의 행복인가 싶었져요 목이가 아파서 오래는 못봤는데 오랜만에 와서 2시간남짓만 있더서 넘넘 미안하구... 그럼에두 봐주어서 정말정말 감쟈했져요 히히 내일은 좀더 건강한 모습으로 갈게요 아메리칸 아카디아가 넘 하구싶은데 만약 힘들다면 곰탕이들 프사그리기...</t>
+  </si>
+  <si>
+    <t>RE오랜만에 만나서 다른 거 안 하고 이야기 나눠서 너무 좋앗서! 게임이 어디 도망가는 건 아니니까 천천히 회복하는 한 주 만들기 오늘 다시 행복한 하루를 열어줘서 고마쯘니다↕️ 좋은 밤 보내고 내일 좀 더 건강한 모습으로 만나자</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/ahtang/1993</t>
+  </si>
+  <si>
+    <t>멀쩡했던 마당고양이가 갑자기 죽었어요… 이유가 뭘까요? (사진있음)</t>
+  </si>
+  <si>
+    <t>이렇게 잘 뛰고 제 앞에 앉아있고 멋있는 아이가 힘이없이 축 늘어져있더니 이렇게 옆으로 쓰러져 버렸어요 그리고 얼마 지나지않아 고별로 떠났답니다.... 아시는분 있으면 댓글 꼭 부탁드려요ㅠㅠ + 병원 가봤습니다.... 범백이 아니라 독극물이라고하네요.... 얼마나 고통스러웠을지 정말 상상조차 안갑니다 ㅠㅠㅠ 쿠키야 고양이별에선 맛있는거 많이먹고 꼭 행복해야해</t>
+  </si>
+  <si>
+    <t>RE범백은 잠복기 길게 2주까지도 보는데. 발현 후엔 급성으로 이삼일만에도 죽을 수 있어요. 고양이 독성물질은..ㅎ.. 헤아리기 어려울 정도로 많지요. 우리가 쓰는 세제,향수,디퓨져, 꽃들 중 대다수, 화학물질 거의 다.. , 파,마늘 양념류..등등. 그냥 개복치인 애들인데 애들이</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/ilovecat/8321783</t>
+  </si>
+  <si>
+    <t>가을타는 갱년기 ㅋ</t>
+  </si>
+  <si>
+    <t>소소한 병원비는 두분이 내셔야 하고.. 친구들도 만나실거고 또 아빠의 보험없음으로 인해 엄마는 보험을 많이 드셔서 ㅋ 아무튼. 저희 시댁은 엄청나게 부유하진 않아도 시골에 땅 갖고 계시고 농사 지으시고.. 두분이 정말 너무나도 성실하고 자애로우셔서 용돈은 드리면 받긴 하는데, 되려 더 주시는 타입이죠. 저 결혼할 때 200만원 갖고 결혼했고 ㅎ 저희쪽 식대, 예식장, 드레스비용까지 전부 시댁에서 다...</t>
+  </si>
+  <si>
+    <t>RE세월에 무상함… 강인한 아버지때문에 더 강인한 사장님을 만든거겠죠. 무서운DNA군요^^ 저가 아싸 가입한지 10년정도 됐는데 사장님은 걱정1도 안되요. 전반에 3:0으로 지고 있어도 후반에 반드시 역전시키는 믿음이랄까... 지가 뭐라고 생각할수도 있겠지만 엄지척은 엄지척이</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/jihosoccer123/3769105</t>
+  </si>
+  <si>
+    <t>성인 목통증+기침…으허ㅠㅠ</t>
+  </si>
+  <si>
+    <t>시골이라 병원 선택지가 별로 없어여ㅠㅠ) 걍 목이 좀 부었다고만…ㅠㅠ그래도 항생제랑 줬는데 자려고 누우면 기침에 미칠거 같아요 어느정도냐면 기침하다가 오줌 싸겠어요ㅠ 목통증하고 기침이 거의 독감급인데 열이나 근육통이 전혀 없어서 독감검사 안해주는거 같아요 제 생각에도 목이 이렇게 아프면 열이 나야 하는데 이상해요ㅠㅠ 낼 다른병원 찾아서 가볼까요..???ㅠㅠㅠㅠ 괴롭 ㅜㅜㅜㅜ</t>
+  </si>
+  <si>
+    <t>RE이번감기가 그런가봐요..약을 먹어도 피가 나올정도로 기침 심해요 ㅜㅜ</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/skybluezw4rh/14921176</t>
+  </si>
+  <si>
+    <t>남편한테 눈치보여요(긴글주의)</t>
+  </si>
+  <si>
+    <t>저는 병원에 와서 아빠 보호자로있구요 시골이라 간병인도 없어서 안구해져서 어쩔수없이 식구들이 한답니다 무튼 밭에서 일한다고 토욜오전에 가서 일욜 저녁에오는데 엄마는 운전못하셔서 남동생이... 이런적이 한번이 아니에요 차타고오는 애도 고생이고 낼출근해야하는데 무리다 힘들다해도 좀만고생하면 안되냐고 남동생은 밭에서 일해서 힘들다고하고..하..밭일을 안하면되는데 농민수당받아서 안하면...</t>
+  </si>
+  <si>
+    <t>RE눈치볼거없이 맘님 선에서 차단하세요 4시간운전 쉽지않죠 ㅜㅜ...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/skybluezw4rh/14803639</t>
+  </si>
+  <si>
+    <t>냥이들 돌보는 일 그만 할까봅니다..</t>
+  </si>
+  <si>
+    <t>눈꼽 때문에 눈도 제대로 뜨지 못하고, 까만 코딱지가 가득 차 숨 쉬기조차 힘들어하던 아이들이었어요. 매일 안약도 넣어주고 밥이랑 분유를 챙겨주니, 거짓말처럼 아픈 흔적이 사라지고 상태가 아주 좋아지더라고요. 하지만 그 행복도 잠시였네요. 아이들이 건강하게 자라주는 모습을 보았더라면 이런 글을 올리지도 않았을 텐데… 돌보기 시작한 직후 두 마리가 떠났고, 지난주 일요일에 또 한 마리가 세상을...</t>
+  </si>
+  <si>
+    <t>RE집사님 .. 집사님 덕에 그 아이들이 그래도 이 세상에 태어나서 잠깐이나마 행복한 생활을 하다 간거에요... 슬프지만 별에 간 아이들이 그걸 원하진 않을듯해요... 자연의 섭리에 맞기시면 됩니다... 우리도 결국엔 가는걸요...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/ilovecat/8319567</t>
+  </si>
+  <si>
+    <t>시골의 몰락..</t>
+  </si>
+  <si>
+    <t>종합병원이 10분 이내에 소재 하는 동네 인데 50여호 정도 모여사는 꽤 오래된 동네 입니다 작은 동네 이지만 인재들이 많이 배출된 곳인지 도시로 나간 자녀들이 성공하여 동네에 기부금을 많이 내는듯... 합니다 시골 심각하다.. 앞으로 5년 후면 어떻게 될까.. 막연한 걱정을 하곤 했습니다 노령인구가 많고 새로운 인구유입은 없으니 노인들 그것도 대부분 할어니들 혼자 사시는 분들 한두분씩 가시고 나면 동네에...</t>
+  </si>
+  <si>
+    <t>RE시골에 대한 추억이 남아있는 베이비부머 1,2세대들이 은퇴후 귀향 귀촌하는 캠페인이 필요하고 이를 뒷받침하는 정부의 적극적인 지원책이 필요합니다. 그렇지 않으면 지방소멸 및 대도시집중으로 인한 엄청난 문제점들로 더 큰 댓가를 치르게 될 것입니다.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1338143</t>
+  </si>
+  <si>
+    <t>병원에서 모욕적인 말을들엇어요</t>
+  </si>
+  <si>
+    <t>사는곳이 시골인데 2급병원이 30분거리에 생겼어요 작년에 폐렴 연속 두번,독감한번 걸렸고 낫는데 굉장히 힘들었어요.동네의원 두곳에서 한달이 넘게 감기가 안났는데 감기약과 수액만 주셔서 갈비뼈가 나가는통증.기침,열을 동반했었어요. 작년까지 의료수급자가 아니였고 올해 의료 수급자가 되어서 상급병원 한군데 알아두자 싶어 오늘 새로생긴 병원에 감기몸살로 내원햇더니 보건소나 의원에서 의뢰서를...</t>
+  </si>
+  <si>
+    <t>RE첨방문하는곳에서 의뢰서부터 끊어달라고하면 대부분 싫어해요 수급자아니더라도요 다니던곳이 안들어서 상위병원갈려고 요구했을때도 싫은티 낸병원도 있어서요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/cafe1535/1893206</t>
+  </si>
+  <si>
+    <t>타그리소 복용 16개월, 투병 20개월... 목요일이 49재입니다.</t>
+  </si>
+  <si>
+    <t>엄마(당시 79세)는 24년 12월 5일 첫 진단이 이미 말기였고, 친정이 시골이라 서울 큰 병원 가라고 해서 가장 빨리 예약이 됐던 강동ㄱㅎㄷ... 입원할 때 원장님이 평균 4주라고 하셨지만 엄마는 16주나 버텨주셨습니다. 그리고 8월 21일 주무시다가 떠나셨습니다. 호스피스 병동을... 병원에 계속 있었으면 일단 시끄럽고 이런저런 검사하러 다니고 금식하고... 엄마가 더 힘들어하셨을것 같아요. 가장 큰 부분은 통증조절...</t>
+  </si>
+  <si>
+    <t>RE더이상아프지않은조은곳으로가셧읍니다 고인의명복을빕니다</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/lung/324285</t>
+  </si>
+  <si>
+    <t>제욕하는 시누들의 카톡을 보고난후..</t>
+  </si>
+  <si>
+    <t>첫번째병원에서 검사결과 아주 나쁘지는않으셔서 저희부부는 시댁에 들어가 집을 치우기로하고 아주버님은 옮기는 병원으로 가기로하고 시누이들은 경기도권에서 내려오기로 하였습니다. 집안자체가 원래... 제몸이 아파도 병원한번 안가고 아무튼그랬는데 일이 이지경인데 매일 아무렇지않게 저한테 이야기하고 저는 대답도안하고 이런생활이 벌써 3개월째입니다 속상해서 주저리 주저리..여전히 대화없이...</t>
+  </si>
+  <si>
+    <t>RE님의 그런 희생 가족들이 몰라요. 나중에 알아도, 왜 그랬어? 무슨 도움 된다고? 이럴 수도. 얼른 보험부터 드세요. 부정맥이나 척추 협착증, 관리해야죠. 언제 무슨 일 있어도 쌓인 설움 없게 스스로에게 잘해 주세요. 더 이상 알뜰살뜰 희생은 노노.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/remonterrace/34922334</t>
+  </si>
+  <si>
+    <t>6-5.생태위생_해충출몰_작업동선위생</t>
+  </si>
+  <si>
+    <t>시골집 지네 물려서</t>
+  </si>
+  <si>
+    <t>지네가 정말 미치도록 많아요 시골집 가면 두마리정도는 기본으로 보네요 사람물기까지 ....</t>
+  </si>
+  <si>
+    <t>습한 집이라 이렇게 지네가 많은줄은 미처 몰랐네요 이제 사람까지 물고 정말 미쳐 버리네요 구멍을 다 막았다고 생각하는데 어디서 이렇게 잘도 들어 오는지 강력한 지네약 추천좀 해 주세요 농약처럼 집둘에 바깥에다 마구 뿌려야 하는지 정말 대책이 안서네요 지네약도 촘촘히 갔다 놓고 하는데도 어디서 그렇게 출몰하는지 선배님들 완전 박멸시키는 강력한 방법좀 알려 주셔요 시골이 가기 싫어지네요 주말마다...</t>
+  </si>
+  <si>
+    <t>RE실내에는 전자파 꽂아놓고는 안보였어요 농막인데,둘레에는 가루약뿌리고, 징글징글</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1332785</t>
+  </si>
+  <si>
+    <t>엉엉 시골집 지네 나와요</t>
+  </si>
+  <si>
+    <t>지네 가루약을 장판아래 다 뿌렸다 했는데 천장에서 나와요ㅠㅠ 급 찾아보니 닭뼈 냄새맡고 온다나 머라나 근데 오늘 닭뼈는 아니고 족발 먹었거든요 그 냄새맡고 오나 싶어요 부랴부랴 제미나이가 물티슈에 주방세제 적셔서 잠자는곳 주변 두르라는데 효과있을지ㅠ 잠 못자고 있어요 무서워요</t>
+  </si>
+  <si>
+    <t>RE어우 애들없나요? 애들있음 저 바로 집에 갈거같아요 ,,</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/skybluezw4rh/14802530</t>
+  </si>
+  <si>
+    <t>자다가 지네에 물렷어요</t>
+  </si>
+  <si>
+    <t>공주랑 안방에서 자다가 지네에 물렷어요ㅠㅠ 순간 따끔해서 다람쥐가나왓나 잡아야겟다해서 불켯더니 베개밑으로 길쭉한게 쑤욱 깜놀해서 거실서자던 신랑 불러 겨우잡앗어요 공주가 안물려서 얼마나 천만다행인지ㅠㅠ 딸기철에 신랑 한번 저까지 벌써 두번째ㅠㅠ 업체 불러야할까봐요ㅠㅠ 으앙 아파ㅠㅠㅠ</t>
+  </si>
+  <si>
+    <t>RE두마리 잡으셨어요? 정확치는않지만 예전에 어디서들었고 저희도 전에물렸을때 두마리잡았거든요...지네는 습기가있는곳이나 옆에 밤나무?가있으면 있데요,.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/cjsam/5103348</t>
+  </si>
+  <si>
+    <t>지네 잘 아시는분??</t>
+  </si>
+  <si>
+    <t>시골집 3개월차입니다 시골이 살아보니 넘 좋은데 딱 하나 지네가 문제입니다 ㅎㅎ 지네약을 뿌려놨는데 어느새 약효가 줄었는지 남편이 자다가 한번 물렸어요 ㅜㅜ 엄청 아파하더라고요 ;;;;; 혹여나 야밤에 애들이 물릴까봐 그게 걱정입니다 잘때되면 지네나올까봐 무서워요ㅡㅜ 60년대 지어진 흙집이라 틈새가 많아요 심지어 바로 옆 뒤가 대나무숲입니다 뒷쪽에 돌담틈새 엄청많고요 하수구트랩하고...</t>
+  </si>
+  <si>
+    <t>RE저희도 지네 무서워 원터치 텐트 치고 있어요~ 낮에 장판밑에도 바퀴약 뿌리고 집안 곳곳 뿌려요...몇시간후 비실비실 기어나오면 밖에서 없애고 있어요... 저희도 마늘 수확땜에 시골에 가야 하는데 걱정입니다.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1321861</t>
+  </si>
+  <si>
+    <t>세상에나~</t>
+  </si>
+  <si>
+    <t>지네에 물려본 사람만이 알수 있는 고통입니다. 얼마나 놀랬는지 정신이 하나도 없네요.ㅋ~ 옆에 있는 거로 잡다가 도망가고 잡다가 도망가고 근근히 잡았어요. 전에 한번 휴지로 잡다가 손을 물려 몇날몇일 고생 한적 있거든요. 해서 손 안물리게 마침 등 긁은것이 있어서 잡았답니다 에휴 시골에 살면 끔쩍끔쩍 놀랍니다. 조용히 가만 있어가 살짝 들어보니 잽싸게 도망가요 해서 등긁은거로 미리.대처 해가 내리쳐서...</t>
+  </si>
+  <si>
+    <t>RE다이소에도팔아요 쿠팡서도팔고 분필처럼그어놓으면 개미 지네 못들어온다고 들었어요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/happyparm/607586</t>
+  </si>
+  <si>
+    <t>간밤에 지네한테 물렸네요</t>
+  </si>
+  <si>
+    <t>집이 산에 딱 붙어있어서 지네가 잘 나와요. 비가 오거나 하면 지네가 집으로 들어오기도 하는데 지네가 부드러운걸 좋아해서 빨레감이나 이불에 잘 들어가 있거든요. 간밤에 이불 덮고 좀 뒤척이다보니 한 이불을 덮고 있던 지네가 자기를 괴롭히는 줄 알고 제 발가락을 물었네요. 자다가 깜짝 놀라 일어나서 보니 15cm 길이의 지네가 이불 속에 숨어있었네요. 아직 화가 풀리지 않은건지 이불을 막 깨물고...</t>
+  </si>
+  <si>
+    <t>RE저도 어릴때 밤늦게 불꺼진 거실에서 돌아다니다 절지류 한테 물린적이 있네요.. 불 켜보니 도망간것으로 보아 그리마로 추정하지만.. 지네 였으면 어떻게든 발견했을텐데 새끼 발가락에 물렸었는데 드라큘라 마냥 독니 자국이 있더라구요.. 느낌은 피부를 불에 지지는 느낌</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/audiodudu/865887</t>
+  </si>
+  <si>
+    <t>난감한 문의해요</t>
+  </si>
+  <si>
+    <t>시골이다보니 숙소에 지네가 출몰해 손님중 한분을 물었어요. 깨끗하게 소독하고 7년동안 이런적이 한번도 없었는데 저 또한 너무 무섭네요.. 이런 경우 어떻게 해야ㅠ할지 모르겠어서 여쭤봐요.. 오늘 1박 더 하셔야 하는데 요즘 성수기라 다른곳으로 옮길 수도 없는터라 난감해요</t>
+  </si>
+  <si>
+    <t>RE일단 병원조치부터 하시고 게스트와 이야기 하세요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/maplepath/114276</t>
+  </si>
+  <si>
+    <t>농촌 집에 지네 없습니까</t>
+  </si>
+  <si>
+    <t>아파트에 살다가 농촌집에 외서 살아보니까요. 지네 때문에 노이로제 걸렸습니다 이마에 물리니까 너무 아픕니다.</t>
+  </si>
+  <si>
+    <t>RE흰색가루약인가 있어요 지네퇴치 검색하면 노란색통입니다 올해 자다가 뭐가 스슥거려서보니 지네때문에 식겁한적있습니다</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/wjdxorduq/242710</t>
+  </si>
+  <si>
+    <t>여러분 지네 조심하세요ㅜㅜ 아파요..</t>
+  </si>
+  <si>
+    <t>새끼지네인데 많이 길더라고요.. 저는 당황하면 침착해지는 스타일이라서 얼른 휴지로 잡고 비닐에 봉해뒀지만 엄지발가락이 퉁퉁 붓기 시작하면서 발가락이 바늘로 찌르는 느낌이 엄청 아팠어요 어떨땐 불타는것 같기도 하고 바늘로 막 찌르는 것 같기도 하고 까진 상처에 알콜 뿌리는 것 같기도 하고.. 시골이라서 벌레가 많은건 이제 체념 했지만 무는 벌레는 용납 못해요ㅠㅠ 보통 공격하면 물지 않나요.. 잘...</t>
+  </si>
+  <si>
+    <t>RE지네는 물리면 위험하다던데, 그래도 응급처치 잘 하시고. 지금은 좀 나아지셨다니 다행입니다.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/druidcafe/296917</t>
+  </si>
+  <si>
+    <t>와~ ㅠㅠ 방안에 지네가 나왔어요...ㅠㅠ</t>
+  </si>
+  <si>
+    <t>제가 사는곳은 시골이라 지네가 자주 나오거든요...ㅠㅠ 그래서 예전에 실리콘으로 구멍이란 구멍은 모두 막았는데, 이놈이 어떻게 들어왔는지...와 잠도 못자고 미치겠네요.... 무시하고 자다가 물리면 바로 응급실행이거든요 ㅠㅠ 와 빨리 지네 기어 나와서 잡아야 하는데, 걱정이네요.... 제발 빨리 나와서 제가 파리체로 잡아야 하는데 ㅠㅠ 미치겠네요... 이거 어디 말할대도 없고....해서 여기에 글남겨요 .... 제가...</t>
+  </si>
+  <si>
+    <t>RE돈벌레 같은거 아닌가요? 한국 가정집에 지네 같은 네임드 벌레가 나올 수 있나요? ㄷㄷ</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/moopung/357540</t>
+  </si>
+  <si>
+    <t>자다가 지네가 나왔어요ㅠㅠㅠ</t>
+  </si>
+  <si>
+    <t>제가 예민해서... 자는데 뭔가 다리에 기어가는 느낌이 들길래 뭐야 하고 쳤는데, 그 어두운상황에 길다란게 기어가는게 보이더라구요ㅠㅠㅠㅋㅋㅋ 애들 다 깨우고 애들이랑 소리지르면서 밀대로 내리쳐서 죽였는데도 안죽어서 초강력 살충제를 뿌렸어요..ㅋㅋ 사체는 첫째가 용기를 내서 젓가락으로 잡아서 변기통에 넣었구요 ㅠㅠ 둘째는 무섭다고 징징.ㅠㅠ 저는 오늘 날밤을 새게 생겼네요.. 텐트를 하나 사서 치고...</t>
+  </si>
+  <si>
+    <t>RE집안으로 못들어오게 현관문, 창틀 주변으로 지네약을 뿌리세요!</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/contryschool/12002</t>
+  </si>
+  <si>
+    <t>시골집에 지네 퇴치법 알려주세요</t>
+  </si>
+  <si>
+    <t>저희 친정이 시골입니다 요근래 엄마랑 통화하면 제가 항상 묻거든요 지네 나왔는지 말벌은 안 오는지요 아니나 다를까 잘때 지네가 매일 나와서 몸을 세게 물고 도망 간대요 ㅠ.ㅠ 그젠 눈옆을 물어서 넘 퉁퉁부어 안 가라앉아서 주사 맞고 오셨다고 해요 약을 그렇게 뿌려놔도 소용이 없나봐요 정말 어떤 방법을 써야 덜 나올지 알려주세요 추석때도 애들 물릴까봐 걱정되구 엄마도 넘 걱정되구 지네땜에 속상하네요...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/jaynjoy/261909</t>
+  </si>
+  <si>
+    <t>지네 물려보셨나요?</t>
+  </si>
+  <si>
+    <t>시댁이 시골 주택이라 그런지 간혹 지네가 나오는데 이게 사람을 물더라구요.. 생명에 지장은 없지만 벌레를 안좋아하는 저에게는 정신적으로 큰 충격을 받네요ㅠㅠ 엄마가 되면 강해지고 담대해 진다는데 애를 두명이나 낳았어도 벌레 앞에선 작아지는게 쉽게 변하지 않네요 흑흑 ㅠㅠ 제가 먼저 건드린 것도 아닌데 왜 꼭 물고 갈까요? 지금 두번째 물리다 보니 의문이 생기네요.. 새벽에 자다 물렸더니 애들 잘때...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/cjsam/1130406</t>
+  </si>
+  <si>
+    <t>자다가 지네물렸어요.</t>
+  </si>
+  <si>
+    <t>지네나왔다고 이사한다고하면 남은 월세 어쩌죠? 너무소름끼쳐서 잠을 못잤어요.ㅠ 숙소에서 오늘은자고 시내로나오고싶어요. 집옆에 방치된밭이 있어여. 작은 스침에도 소스라치게 놀라서 집에 정이 뚝 떨어졌어여. ㅠㅠ</t>
+  </si>
+  <si>
+    <t>REㅋㅋ 타란튤라..맞아요..저도 서울에 살다가 여기 와서..거미며 지네 사이즈 보고 깜짝 놀랐어요...그렇게 큰지네는 경동시장에서나 약으로 쓴다고 말려서 묶여있는 넘들만 봤지..여기선 모든게 다 크더라구요..전 시골 주택이라 10년 넘게 살다보니 익숙해져서 이젠 다양한</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/jejumam/1260153</t>
+  </si>
+  <si>
+    <t>지네 때문에 미치겠어요 ㅠㅠ</t>
+  </si>
+  <si>
+    <t>시골집을 사서 대수선으로 공사를 싹 다시 하고 입주를 했어요 겨울엔 괜찮았는데 봄이 되니 지네가 미친듯이 나와요 ㅠㅠ 밖에서는 그나마 괜찮은데 집안에서 계속 나타납니다 ㅠㅠ 이젠 꿈에서도 나올꺼 같아요 판데스 사다가 집 주변으로 짝 뿌려놨는데 집안에는 우찌 해야 할까요ㅠㅠ</t>
+  </si>
+  <si>
+    <t>RE저희집에도 비슷한 환경입니다 예전에 올린글에도 있겠지만 여러가지 해봤는데 집밖은 올데스가 좋았고 실내에는 스프레이가 냄새도없고 효과좋더군요 현관안쪽 중문 등 창문안쪽으로 뿌려두 편해요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1312500</t>
+  </si>
+  <si>
+    <t>시골집 지네 세스코 효과있나요?(매너사진)</t>
+  </si>
+  <si>
+    <t>주말에 부모님 시골집 다녀왔는데 지네가 있더라구요. 어디서 들어온건지 모르겠는데 시골이라 어쩔 수 없다해도 가끔 애들도 가고 부모님도 물리실까 걱정이 돼요. 찾아보니 세스코나 일반 방역 방법이 있는 거 같은데 하면 지네도 잡히나요ㅠㅠ효과만 있으면 어디든 당장 월요일에 업체 연락하려구요!!! 오늘 잡은 놈들이에요ㅠㅇㅠ오마이갓</t>
+  </si>
+  <si>
+    <t>RE저희 일층이라 세스코 사용하는데 지네때문에 사용한건 아니였고 이사 오기전 집에서 바퀴벌레 나와서 사용하면서 좋아서 이사 온 후까지 사용하는데요~ 세스코 덕분인지 벌레는 없더라규요~ 아마 세스코 1회 방문체험 할 수 있는걸로 알고 있어요~</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/hongsam09/6352133</t>
+  </si>
+  <si>
+    <t>자다가 지네에게 물렸어요.</t>
+  </si>
+  <si>
+    <t>시골 생활 하다보니 지네에게 두번째 물렸네요. 첫번째는 장화를 신었는데 따끔거리고 아파서 벗어보니 지네새끼가 튀나왔어요. 깜짝 놀라 장화발로 문질러 버렸는데 몇날 몇일 퉁퉁붓고 고생을 했지요. 해서 그후론 장화를 절대 바로 신지 않고 후딱 던져놨다가 한참후에 신습니다. 오늘 방금 두번째 지네에게 물렸는데 다리가 따끔거려 퍼득 불을켜고 이불을 살펴보니 지네새끼가 도망가고 있네요. 다행히 새끼라...</t>
+  </si>
+  <si>
+    <t>RE오늘밤에 작은새끼가 방벽에서 천장쪽으로기어 가는걸 잡았어요 징거러워서 . 큰지네 갈비뼈근처에 한번물려 병원서 해독주사맞은적도있어요.집근처 야산에 나무가 많아요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/happyparm/499426</t>
+  </si>
+  <si>
+    <t>자다가 지네에 물렸는데 못잡았어요ㅠㅠ</t>
+  </si>
+  <si>
+    <t>시골 주택에 살고 있어요 자다가 손가락에 통증이 생겨서 일어났더니 이불 위를 지네가 기어다니고 있는거에요 자는 엄마 깨우러 간 사이에 지네는 사라지고 없고ㅠㅠㅠㅠ 원래 저희집 고양이가 지네는 기가막히게 찾아내는데 오늘은 하필 저랑 떨어져서 거실에서 자고 있었던게 문제였어요ㅠㅠㅠㅠ 진짜 아무것도 없는 구석을 빤히 쳐다보고 있으면 거기엔 꼭 지네나 벌레가 있거든요 지네 못잡아서 잠도 못자겠네요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/ilovecat/7941236</t>
+  </si>
+  <si>
+    <t>집안으로 지네가 들어오는 집이 많을까요?</t>
+  </si>
+  <si>
+    <t>그런데 며칠전 그 꿈을 송두리째 흔들어버린 사건이있는데요 남편이 외할머니댁에서 거실에서 자려고하다 지네에 물렸어요 캠핑가서 한번보고 기겁했는데 집에 어떻게 들어온건지..... 지은지 10년된 집이에요 15센치는 더 된 징그런 놈... 다른벌레들은 그런가보다하는데 지네라니요ㅠㅠ 집안에 지네가 시골의 일상다반사인건지 궁금합니다 이모 외삼촌은 응 가끔 들어와이러시네요 닭을 안키우니 더하다면서요</t>
+  </si>
+  <si>
+    <t>RE시골은 자주 들어 옵니다 뱀도 들어 오는대요^^ 지네는 귀여운 놈이조^^</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1254529</t>
+  </si>
+  <si>
+    <t>공포의 지네..</t>
+  </si>
+  <si>
+    <t>시골에 살다보니 더러운 바퀴는 없는데 무시무시한 지네가 가끔 나옵니다.. 요놈들이 항상 쌍으로 다녀서 한마리 죽이면 다른놈이 복수하러 잘때 몰레와서 뭅니다.. 어제 밤부터 부스럭거리는 지네소리가 천정에서 계속 들렸는데 보통은 잘 안내려오는데 아침에 보니 천정에 왕대물 지네가 붙어있네요.. 얼른 수건으로 생포한 후 밖에 가서 처리했습니다. 마당에 뱀도 왠만하면 놓아두는데 지네는 다시 자기 집으로...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/franssu/41636</t>
+  </si>
+  <si>
+    <t>지네 물린곳 벌침후기</t>
+  </si>
+  <si>
+    <t>그러나 지네 독은 가려움읗 유발하는 히스타민덩어리라서 목숨을 위험하게 하지는 않습니다. 어릴적 시골 집에는 비상약으로 암모니아와 소다가 준비되어 있어서 벌레에 물리면 바르곤 했는데 암모니아는... 좋은 사람은 벌침으로 2차감염까지 예방할 수 있다는 것을 이번기회에 경험해봅니다. 지네 퇴치법 시골에서는 살충제가루를 장판 밑에 깔아둔답니다. 바퀴약 분사가 좋아요. 일단 약에 취하면 물지 못한답니다.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/rmaqjf/9432</t>
+  </si>
+  <si>
+    <t>시골집에 자다가 지네 물렸네요(사진징그럼)</t>
+  </si>
+  <si>
+    <t>타사이트에 올리고 여기에도 올리네요 새벽에 자다가 먼가 따끔해서 모기인줄 알았는데 욱신욱신 거리길래 핸드폰 후레쉬 켰더니 스르르륵 지나가는 지네 ㅎ 와 통증이 엄청나네요 발가락이 아직두 부었네요 첫날에는 걷는데 절뚝절뚝 ㅎㅎ 사진은 모형이 아니라 진짜 찍은 지네입니다 ㅠㅠ</t>
+  </si>
+  <si>
+    <t>RE오마나 무서워랑;;병원 가보셔야 하는거 아니예요?;;</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/newgenesisdh/1875050</t>
+  </si>
+  <si>
+    <t>시골집과 지네 그리고 침대</t>
+  </si>
+  <si>
+    <t>그리고 지네도 거기도 알을 낳고, 봄이 된 것을 용케 알아챈 알들이 부화되어 벽 밖으로 나오려고 혈안이 되었을 거라는 추측입니다. 그래서 오늘 부터 안 쓰는 콘센트는 모두 막고, 꽂혀있는 콘센트도 구멍을 막도록 하려고 합니다. 그래도 지네가 침대로 기어올라오는 지 지켜보겠습니다. 시골에 사시는 분들 중에 저처럼 지네를 싫어하시는 분이 계시면 콘센트를 잘 지켜보시기 바랍니다.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/189452</t>
+  </si>
+  <si>
+    <t>지네에 물렸어요 어떻게 해야 하나요ㅠㅠ???</t>
+  </si>
+  <si>
+    <t>신랑이 거실에서 자다가 지네에게 물려서 이시간에 깼데요ㅜ 인터넷 보고 일단 버물리 듬뿍발랐는데 어떻게 해야하나요?? 저희집이 11층인데...집에서 나온건 아니겠죠? 시골에서 가져온 음식들중에서 나온거라 생각하고있는데ㅜ 쌍으로 산다는 소리에 또 어디서 나올까 잠도안와요ㅜㅜㅜㅜ</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/cjsam/1131359</t>
+  </si>
+  <si>
+    <t>지네에 물리면 어떻게해야 하나요?</t>
+  </si>
+  <si>
+    <t>저희애가 5살인데 어버이날이라 시골갔는데 부엌에서 앉아서 놀다가 갑자기 비명을 지르더라구요 발이 따갑다 해서 그냥 무심코 지나갔어요 근데 한 2시간인가 지나서 또 비명을 지르는 거예요 그래서 달려가봤더니 아들 목뒤에 옷 카라 위에 진짜 무지막지 큰 지네가 있는거예요 빨리 애 옷을 벗기고 몸을 확인했는데 몸엔 물린자국이 없더라구요 2시간 전에 아프다고 한 발을 보니 가운데 발가락이 발게지고...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/glove/436791</t>
+  </si>
+  <si>
+    <t>집에 지네 없애는 방법 있을까요?</t>
+  </si>
+  <si>
+    <t>시골집에서 아빠가 지네 물리셨는데요 이거 아주 없애버리는 방법 있을까요?ㅠ</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/cjsam/3293121</t>
+  </si>
+  <si>
+    <t>지네에게 물렸을땐??</t>
+  </si>
+  <si>
+    <t>어제 시골왔다가 밤에 자려고 불끄고 누워있는데.. 볼이 엄청 따끔하더니 얼굴위로 뭔가 스스슥~~ 지나가더라구요.. 놀래서 불켜봤더니 그다지 크지는 않은 지네가 똭!! 완전 놀랐네요~ 양옆으로 애들이 누워있었거든요~ 애들이 아니라 다행이다 싶었지만 너무 아파서 잠을 못잤네요.. 치과 치료할때 마취한것처럼 감각도 없고 볼은 후끈후끈 뜨겁고 바늘로 계속 찔러대는 것처럼 아프고ㅠㅠ 아침이 되서 좀 괜찮아지나...</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/cjsam/1318321</t>
+  </si>
+  <si>
+    <t>처음으로 자다가 지네한테 물렸습니다.</t>
+  </si>
+  <si>
+    <t>어제밤 시골집에서 잠을 자는데 갑가지 뒷 목이 따금해서 반사적으로 몸이 튕겨져 일어나면서 목 뒤를 손으로 쎄게 몇번 때리게 됬습니다. 상당한 고통이 있어서 지네가 문듯한 느낌이 들어 이불을 털어보지 엄청큰 지네가 ㅎㅎ 막 도망가는거 순식간에 약을 가지고와 막 뿌리니 지네가 도망다가 행동이 느려져 수거해서 처리하고... 밤 12시에 꿀잠자다 벙진느낌... 지네한테 물린곳이 욱신욱신 통증이 상당하더군요....</t>
+  </si>
+  <si>
+    <t>RE지네~~~ 걔도 강적을 물었다가 홈키파세례를 받았네요.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/nepoengel/282587</t>
+  </si>
+  <si>
+    <t>지네에 물릴뻔했어요..</t>
+  </si>
+  <si>
+    <t>점심먹으려고 음식준비하는데 느낌이 이상해서 내려다보니 바로 발밑에 시커먼게있어서 지네있길래 얼른 나무젓가락으로 잡았어요. 모르고 그대로 밟았으면..ㅠㅠ 오래된 흙집이고 시골집이라그런지 날이 따땃해지면 어김없이 등장하는 불청객~ 큰아들이 어릴때 지네에물려 큰일날뻔 했는데..ㅠ오늘은 엄마침대에서 자야되나..</t>
+  </si>
+  <si>
+    <t>RE안물려서 다행입니다. 한참 선수시절 허리가 아파서 그거 왕지네 가루를 먹었었는데, 세상에 그보다 지독한 맛과 냄새는 없었습니다.</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/nepoengel/303668</t>
+  </si>
+  <si>
+    <t>시골집 뱀 지네 퇴치</t>
+  </si>
+  <si>
+    <t>5도2촌하는 저희 밭에 뱀이 있어요. 저는 어떻게 해요? ㅠㅠ</t>
+  </si>
+  <si>
+    <t>한참 작업중인 집 공사 구경가서 열심히 구상을 하고 있는데, 밭에 붙은 야산에서 뭔가 움직였어요. 공사때문에 내려오신 이사님께서 깜짝 놀라서 말씀해주셨기에 알았네요. 아주 작은 뱀이었는데, 처음엔... 집은 이미 공사를 시작해서 열심히 올리고 있는데, 뱀과 쥐를 지척에 두고 이런 야생에서 어떻게 살죠? 밤새 뱀 쫒는 방법을 찾아보다 뀅한 눈을 부릎뜨고 글을 올리네요. 무슨 좋은 방법이 있을까요? 울고 싶어요~~~</t>
+  </si>
+  <si>
+    <t>RE집 주변에 길고양이들을 많이 모이게 해보셔요 쥐랑 뱀은 코빼기도 안보일거에요 즤집도 산 붙은 집인데 15년째 살면서 올해 뱀 처음 봤네요 그뱀도 제초제랑 벌레약 진하게 바닥전체 치고나선 안보이고요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1339649</t>
+  </si>
+  <si>
+    <t>시골 살이 뱀~ ~ 어케하나용?</t>
+  </si>
+  <si>
+    <t>시골집..전원주택등등 사시는분들께 뱀 퇴치 조언 구하고자 글 올립니다 시골로 집을 지어 이사간 언니한테 톡이왔어요 집 지어서 이사간지 3년 되 가는것 같은데요 첫 해에 봄에 토실토실한 살모사 마당에... 글쎄 뱀이~~~ 집 안 에서 발견 ㅎㅎㅎㅎ (지네 바글바글 한 우리시댁 시골집은 뱀은 없다냥^^ 푸하하하하 ) 집 주변 주의에 뱀 망은 다 쳐놓은거 같은데. 집주변 뱀퇴치 어떻게 해야 할까요? 약품...살충제 등등</t>
+  </si>
+  <si>
+    <t>RE뱀,두더쥐는 후각이 예민해서 유황,나프타렌,,이런거 효과있어요..옛날 어른들은 구렁이가 집에 또아리 틀고 있으면 머리카락 태워서 쫓았어요..</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1324931</t>
+  </si>
+  <si>
+    <t>시골집 미스테리</t>
+  </si>
+  <si>
+    <t>개미가 안보이니 새끼 지네들이 이방 저방에서 나와요.. 대체 어디로 들어오는걸까요... 편백루바로만 돼 있는 속이 비어있는 벽 하나 두고 지네랑 온갖것들이랑 공존하는 것 같아요. 대대대대대대대적으로 모든 구멍 다 막고 몇달간 지네가 안보여서 너~~~뮤 너무 행복했거든요 새끼들이 여기저기서 막 보여요 ㅠㅠ 얘네가 틈으로 들어오는 걸까요? 그리고 자라나는 걸가요...?? 울고 싶네요 그리고 대왕 콧물(?)같은...</t>
+  </si>
+  <si>
+    <t>RE새끼 지네가 여러 방에서 반복적으로 나온다면 외부에서 그때그때 들어오는 것뿐 아니라 편백루바 뒤 빈 공간이나 바닥·벽체 내부에 숨어 있던 개체에서 어린 지네들이 흩어져 나오는 가능성도 있습니다. 구멍을 막는 것도 중요하지만 집 주변 낙엽·돌·목재 밑 습기와</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1336264</t>
+  </si>
+  <si>
+    <t>방금 지네가 들어왔다고 초인종 ㅠ</t>
+  </si>
+  <si>
+    <t>이른아침부터 초인종소리에 누군가 했더니 옆집이사하는데 이삿짐센터 아저씨께서 크고 다급한 목소리로 댁에 엄청 큰 지네가 들어갔다고 알려주셨어요ㅠㅠ 일단 감사하다고 하고 신랑이 현관쪽을 찾는데... 너무 충격받아서 지금 멘붕이예요 숲세권아파트라 그런가 저런게 너무 많아요ㅜㅜ 이층인데 여까지 올라왔네요 현관밑에 지네같은거 못들어오게하는 테잎?머 그런거 뭘로 검색해야하나요 방지팁좀...</t>
+  </si>
+  <si>
+    <t>RE으악 집게벌레들어와도 기겁인데 그정도 크기에 지네는 상상이 안되네요</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/remonterrace/35081701</t>
+  </si>
+  <si>
+    <t>뱀과 지네 (사진 없음) 그리고 3가지 궁금증</t>
+  </si>
+  <si>
+    <t>단어조차 혐오스러운 뱀, 지네 그런데 주말농장을 하시거나 전원생활을 하시는 분 께서 위 두가지 동물을 약3년 정도 기간에 한 번도 본 적이 없으시다면 그 가치는 토지+건물 비용에 플러스 해서 1억 정도... 시골 부친댁에 황토방 지네는 정말 퇴치 불가입니다. 출몰한지 15년정도 되었고 방안에서 약 20마리 정도 잡았습니다. 완전퇴치를 위해 약도 뿌려보았고, 강력 끈끈이도 가구 밑에 여러개 뒀지만 퇴치 불가...</t>
+  </si>
+  <si>
+    <t>RE1. X 2. 길냥이는 뱀을 아주 잘 잡습니다. 최고의 킬러입니다. 보은이라기보단 아마 주 영역이라서 갖다 놓은 거 같아요. 3. 구렁이,독사- 거의 도망 안갑니다. 사람이 뱀 있는 지 모르고 지나가다 물리는 경우는 많습니다. 독사와 구렁이만 잘 구별하셔서 적당히 잡아주시면 그래</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/kimyoooo/1322656</t>
+  </si>
+  <si>
+    <t>봄과 함께 찾아오는 지네, 퇴치법 2탄(빌라, 아파트 편 포함 수정)</t>
+  </si>
+  <si>
+    <t>특히 마당에 출몰하는 뱀, 또 집안까지 들어오는 지네 때문에 깜짝 깜짝 놀라기도 하고, 무서울 때도 있죠 마당에 들어오는 뱀 때문에 깜짝 깜짝 놀라시는 분들, 집안에서 지네를 더이상 보지않게 퇴치하고 싶은 분들은 댓글 남겨주시면 챗으로 방법을 알려드리겠습니다. "싸이메트"만큼 효과가 아주 좋습니다 요즘이 지네 퇴치를 위한 최적기 입니다. 제가 사는 시골 집도 근처에 산과 소나무 밭이 있어서 부엉이도 살고...</t>
+  </si>
+  <si>
+    <t>RE어릴때 살던 집이 단독주택이었는데 집터에 과수원도 텃밭도 있는. 우리엄마는 붕산을 집주변으로 놔뒀어요. 혹시 그런 방법일까요?</t>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/jejumam/1202117</t>
   </si>
 </sst>
 </file>
@@ -11335,7 +13309,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J876"/>
+  <dimension ref="A1:J1051"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -39377,6 +41351,5603 @@
       </c>
       <c r="J876" s="3" t="s">
         <v>3647</v>
+      </c>
+    </row>
+    <row r="877" spans="1:10">
+      <c r="A877" s="2">
+        <v>876</v>
+      </c>
+      <c r="B877" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C877" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D877" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E877" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F877" s="2" t="s">
+        <v>3651</v>
+      </c>
+      <c r="G877" s="2" t="s">
+        <v>3652</v>
+      </c>
+      <c r="H877" s="2" t="s">
+        <v>3653</v>
+      </c>
+      <c r="I877" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J877" s="3" t="s">
+        <v>3654</v>
+      </c>
+    </row>
+    <row r="878" spans="1:10">
+      <c r="A878" s="2">
+        <v>877</v>
+      </c>
+      <c r="B878" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C878" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D878" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E878" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F878" s="2" t="s">
+        <v>3655</v>
+      </c>
+      <c r="G878" s="2" t="s">
+        <v>3656</v>
+      </c>
+      <c r="H878" s="2" t="s">
+        <v>3657</v>
+      </c>
+      <c r="I878" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J878" s="3" t="s">
+        <v>3658</v>
+      </c>
+    </row>
+    <row r="879" spans="1:10">
+      <c r="A879" s="2">
+        <v>878</v>
+      </c>
+      <c r="B879" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C879" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D879" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E879" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F879" s="2" t="s">
+        <v>3659</v>
+      </c>
+      <c r="G879" s="2" t="s">
+        <v>3660</v>
+      </c>
+      <c r="H879" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I879" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J879" s="3" t="s">
+        <v>3661</v>
+      </c>
+    </row>
+    <row r="880" spans="1:10">
+      <c r="A880" s="2">
+        <v>879</v>
+      </c>
+      <c r="B880" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C880" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D880" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E880" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F880" s="2" t="s">
+        <v>3662</v>
+      </c>
+      <c r="G880" s="2" t="s">
+        <v>3663</v>
+      </c>
+      <c r="H880" s="2" t="s">
+        <v>3664</v>
+      </c>
+      <c r="I880" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J880" s="3" t="s">
+        <v>3665</v>
+      </c>
+    </row>
+    <row r="881" spans="1:10">
+      <c r="A881" s="2">
+        <v>880</v>
+      </c>
+      <c r="B881" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C881" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D881" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E881" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F881" s="2" t="s">
+        <v>3666</v>
+      </c>
+      <c r="G881" s="2" t="s">
+        <v>3667</v>
+      </c>
+      <c r="H881" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I881" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J881" s="3" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="882" spans="1:10">
+      <c r="A882" s="2">
+        <v>881</v>
+      </c>
+      <c r="B882" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C882" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D882" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E882" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F882" s="2" t="s">
+        <v>3669</v>
+      </c>
+      <c r="G882" s="2" t="s">
+        <v>3670</v>
+      </c>
+      <c r="H882" s="2" t="s">
+        <v>3671</v>
+      </c>
+      <c r="I882" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J882" s="3" t="s">
+        <v>3672</v>
+      </c>
+    </row>
+    <row r="883" spans="1:10">
+      <c r="A883" s="2">
+        <v>882</v>
+      </c>
+      <c r="B883" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C883" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D883" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E883" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F883" s="2" t="s">
+        <v>3673</v>
+      </c>
+      <c r="G883" s="2" t="s">
+        <v>3674</v>
+      </c>
+      <c r="H883" s="2" t="s">
+        <v>3675</v>
+      </c>
+      <c r="I883" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J883" s="3" t="s">
+        <v>3676</v>
+      </c>
+    </row>
+    <row r="884" spans="1:10">
+      <c r="A884" s="2">
+        <v>883</v>
+      </c>
+      <c r="B884" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C884" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D884" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E884" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F884" s="2" t="s">
+        <v>3677</v>
+      </c>
+      <c r="G884" s="2" t="s">
+        <v>3678</v>
+      </c>
+      <c r="H884" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I884" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J884" s="3" t="s">
+        <v>3679</v>
+      </c>
+    </row>
+    <row r="885" spans="1:10">
+      <c r="A885" s="2">
+        <v>884</v>
+      </c>
+      <c r="B885" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C885" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D885" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E885" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F885" s="2" t="s">
+        <v>3680</v>
+      </c>
+      <c r="G885" s="2" t="s">
+        <v>3681</v>
+      </c>
+      <c r="H885" s="2" t="s">
+        <v>3682</v>
+      </c>
+      <c r="I885" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J885" s="3" t="s">
+        <v>3683</v>
+      </c>
+    </row>
+    <row r="886" spans="1:10">
+      <c r="A886" s="2">
+        <v>885</v>
+      </c>
+      <c r="B886" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C886" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D886" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E886" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F886" s="2" t="s">
+        <v>3684</v>
+      </c>
+      <c r="G886" s="2" t="s">
+        <v>3685</v>
+      </c>
+      <c r="H886" s="2" t="s">
+        <v>3686</v>
+      </c>
+      <c r="I886" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J886" s="3" t="s">
+        <v>3687</v>
+      </c>
+    </row>
+    <row r="887" spans="1:10">
+      <c r="A887" s="2">
+        <v>886</v>
+      </c>
+      <c r="B887" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C887" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D887" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E887" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F887" s="2" t="s">
+        <v>3688</v>
+      </c>
+      <c r="G887" s="2" t="s">
+        <v>3689</v>
+      </c>
+      <c r="H887" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I887" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J887" s="3" t="s">
+        <v>3690</v>
+      </c>
+    </row>
+    <row r="888" spans="1:10">
+      <c r="A888" s="2">
+        <v>887</v>
+      </c>
+      <c r="B888" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C888" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D888" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E888" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F888" s="2" t="s">
+        <v>3691</v>
+      </c>
+      <c r="G888" s="2" t="s">
+        <v>3692</v>
+      </c>
+      <c r="H888" s="2" t="s">
+        <v>3693</v>
+      </c>
+      <c r="I888" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J888" s="3" t="s">
+        <v>3694</v>
+      </c>
+    </row>
+    <row r="889" spans="1:10">
+      <c r="A889" s="2">
+        <v>888</v>
+      </c>
+      <c r="B889" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C889" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D889" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E889" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F889" s="2" t="s">
+        <v>3695</v>
+      </c>
+      <c r="G889" s="2" t="s">
+        <v>3696</v>
+      </c>
+      <c r="H889" s="2" t="s">
+        <v>3697</v>
+      </c>
+      <c r="I889" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J889" s="3" t="s">
+        <v>3698</v>
+      </c>
+    </row>
+    <row r="890" spans="1:10">
+      <c r="A890" s="2">
+        <v>889</v>
+      </c>
+      <c r="B890" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C890" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D890" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E890" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F890" s="2" t="s">
+        <v>3699</v>
+      </c>
+      <c r="G890" s="2" t="s">
+        <v>3700</v>
+      </c>
+      <c r="H890" s="2" t="s">
+        <v>3701</v>
+      </c>
+      <c r="I890" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J890" s="3" t="s">
+        <v>3702</v>
+      </c>
+    </row>
+    <row r="891" spans="1:10">
+      <c r="A891" s="2">
+        <v>890</v>
+      </c>
+      <c r="B891" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C891" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D891" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E891" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F891" s="2" t="s">
+        <v>3703</v>
+      </c>
+      <c r="G891" s="2" t="s">
+        <v>3704</v>
+      </c>
+      <c r="H891" s="2" t="s">
+        <v>3705</v>
+      </c>
+      <c r="I891" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J891" s="3" t="s">
+        <v>3706</v>
+      </c>
+    </row>
+    <row r="892" spans="1:10">
+      <c r="A892" s="2">
+        <v>891</v>
+      </c>
+      <c r="B892" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C892" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D892" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E892" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F892" s="2" t="s">
+        <v>3707</v>
+      </c>
+      <c r="G892" s="2" t="s">
+        <v>3708</v>
+      </c>
+      <c r="H892" s="2" t="s">
+        <v>3709</v>
+      </c>
+      <c r="I892" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J892" s="3" t="s">
+        <v>3710</v>
+      </c>
+    </row>
+    <row r="893" spans="1:10">
+      <c r="A893" s="2">
+        <v>892</v>
+      </c>
+      <c r="B893" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C893" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D893" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E893" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F893" s="2" t="s">
+        <v>3711</v>
+      </c>
+      <c r="G893" s="2" t="s">
+        <v>3712</v>
+      </c>
+      <c r="H893" s="2" t="s">
+        <v>3713</v>
+      </c>
+      <c r="I893" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J893" s="3" t="s">
+        <v>3714</v>
+      </c>
+    </row>
+    <row r="894" spans="1:10">
+      <c r="A894" s="2">
+        <v>893</v>
+      </c>
+      <c r="B894" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C894" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D894" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E894" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F894" s="2" t="s">
+        <v>3715</v>
+      </c>
+      <c r="G894" s="2" t="s">
+        <v>3716</v>
+      </c>
+      <c r="H894" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I894" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J894" s="3" t="s">
+        <v>3717</v>
+      </c>
+    </row>
+    <row r="895" spans="1:10">
+      <c r="A895" s="2">
+        <v>894</v>
+      </c>
+      <c r="B895" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C895" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D895" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E895" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F895" s="2" t="s">
+        <v>3718</v>
+      </c>
+      <c r="G895" s="2" t="s">
+        <v>3719</v>
+      </c>
+      <c r="H895" s="2" t="s">
+        <v>3720</v>
+      </c>
+      <c r="I895" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J895" s="3" t="s">
+        <v>3721</v>
+      </c>
+    </row>
+    <row r="896" spans="1:10">
+      <c r="A896" s="2">
+        <v>895</v>
+      </c>
+      <c r="B896" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C896" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D896" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E896" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F896" s="2" t="s">
+        <v>3722</v>
+      </c>
+      <c r="G896" s="2" t="s">
+        <v>3723</v>
+      </c>
+      <c r="H896" s="2" t="s">
+        <v>3724</v>
+      </c>
+      <c r="I896" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J896" s="3" t="s">
+        <v>3725</v>
+      </c>
+    </row>
+    <row r="897" spans="1:10">
+      <c r="A897" s="2">
+        <v>896</v>
+      </c>
+      <c r="B897" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C897" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D897" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E897" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F897" s="2" t="s">
+        <v>3726</v>
+      </c>
+      <c r="G897" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="H897" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I897" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J897" s="3" t="s">
+        <v>3728</v>
+      </c>
+    </row>
+    <row r="898" spans="1:10">
+      <c r="A898" s="2">
+        <v>897</v>
+      </c>
+      <c r="B898" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C898" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D898" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E898" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F898" s="2" t="s">
+        <v>3729</v>
+      </c>
+      <c r="G898" s="2" t="s">
+        <v>3730</v>
+      </c>
+      <c r="H898" s="2" t="s">
+        <v>3731</v>
+      </c>
+      <c r="I898" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J898" s="3" t="s">
+        <v>3732</v>
+      </c>
+    </row>
+    <row r="899" spans="1:10">
+      <c r="A899" s="2">
+        <v>898</v>
+      </c>
+      <c r="B899" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C899" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D899" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E899" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F899" s="2" t="s">
+        <v>3733</v>
+      </c>
+      <c r="G899" s="2" t="s">
+        <v>3734</v>
+      </c>
+      <c r="H899" s="2" t="s">
+        <v>3735</v>
+      </c>
+      <c r="I899" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J899" s="3" t="s">
+        <v>3736</v>
+      </c>
+    </row>
+    <row r="900" spans="1:10">
+      <c r="A900" s="2">
+        <v>899</v>
+      </c>
+      <c r="B900" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C900" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D900" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E900" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F900" s="2" t="s">
+        <v>3737</v>
+      </c>
+      <c r="G900" s="2" t="s">
+        <v>3738</v>
+      </c>
+      <c r="H900" s="2" t="s">
+        <v>3739</v>
+      </c>
+      <c r="I900" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J900" s="3" t="s">
+        <v>3740</v>
+      </c>
+    </row>
+    <row r="901" spans="1:10">
+      <c r="A901" s="2">
+        <v>900</v>
+      </c>
+      <c r="B901" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C901" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D901" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E901" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F901" s="2" t="s">
+        <v>3741</v>
+      </c>
+      <c r="G901" s="2" t="s">
+        <v>3742</v>
+      </c>
+      <c r="H901" s="2" t="s">
+        <v>3743</v>
+      </c>
+      <c r="I901" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J901" s="3" t="s">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="902" spans="1:10">
+      <c r="A902" s="2">
+        <v>901</v>
+      </c>
+      <c r="B902" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C902" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D902" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E902" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="F902" s="2" t="s">
+        <v>3745</v>
+      </c>
+      <c r="G902" s="2" t="s">
+        <v>3746</v>
+      </c>
+      <c r="H902" s="2" t="s">
+        <v>3747</v>
+      </c>
+      <c r="I902" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J902" s="3" t="s">
+        <v>3748</v>
+      </c>
+    </row>
+    <row r="903" spans="1:10">
+      <c r="A903" s="2">
+        <v>902</v>
+      </c>
+      <c r="B903" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C903" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D903" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E903" s="2" t="s">
+        <v>3749</v>
+      </c>
+      <c r="F903" s="2" t="s">
+        <v>3750</v>
+      </c>
+      <c r="G903" s="2" t="s">
+        <v>3751</v>
+      </c>
+      <c r="H903" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I903" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J903" s="3" t="s">
+        <v>3752</v>
+      </c>
+    </row>
+    <row r="904" spans="1:10">
+      <c r="A904" s="2">
+        <v>903</v>
+      </c>
+      <c r="B904" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C904" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D904" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E904" s="2" t="s">
+        <v>3749</v>
+      </c>
+      <c r="F904" s="2" t="s">
+        <v>3753</v>
+      </c>
+      <c r="G904" s="2"/>
+      <c r="H904" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I904" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J904" s="3" t="s">
+        <v>3754</v>
+      </c>
+    </row>
+    <row r="905" spans="1:10">
+      <c r="A905" s="2">
+        <v>904</v>
+      </c>
+      <c r="B905" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C905" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D905" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E905" s="2" t="s">
+        <v>3749</v>
+      </c>
+      <c r="F905" s="2" t="s">
+        <v>3755</v>
+      </c>
+      <c r="G905" s="2" t="s">
+        <v>3756</v>
+      </c>
+      <c r="H905" s="2" t="s">
+        <v>3757</v>
+      </c>
+      <c r="I905" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J905" s="3" t="s">
+        <v>3758</v>
+      </c>
+    </row>
+    <row r="906" spans="1:10">
+      <c r="A906" s="2">
+        <v>905</v>
+      </c>
+      <c r="B906" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C906" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D906" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E906" s="2" t="s">
+        <v>3749</v>
+      </c>
+      <c r="F906" s="2" t="s">
+        <v>3759</v>
+      </c>
+      <c r="G906" s="2" t="s">
+        <v>3760</v>
+      </c>
+      <c r="H906" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I906" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J906" s="3" t="s">
+        <v>3761</v>
+      </c>
+    </row>
+    <row r="907" spans="1:10">
+      <c r="A907" s="2">
+        <v>906</v>
+      </c>
+      <c r="B907" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C907" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D907" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E907" s="2" t="s">
+        <v>3749</v>
+      </c>
+      <c r="F907" s="2" t="s">
+        <v>3762</v>
+      </c>
+      <c r="G907" s="2" t="s">
+        <v>3763</v>
+      </c>
+      <c r="H907" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I907" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J907" s="3" t="s">
+        <v>3764</v>
+      </c>
+    </row>
+    <row r="908" spans="1:10">
+      <c r="A908" s="2">
+        <v>907</v>
+      </c>
+      <c r="B908" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C908" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D908" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E908" s="2" t="s">
+        <v>3749</v>
+      </c>
+      <c r="F908" s="2" t="s">
+        <v>3765</v>
+      </c>
+      <c r="G908" s="2" t="s">
+        <v>3766</v>
+      </c>
+      <c r="H908" s="2" t="s">
+        <v>3767</v>
+      </c>
+      <c r="I908" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J908" s="3" t="s">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="909" spans="1:10">
+      <c r="A909" s="2">
+        <v>908</v>
+      </c>
+      <c r="B909" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C909" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D909" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E909" s="2" t="s">
+        <v>3749</v>
+      </c>
+      <c r="F909" s="2" t="s">
+        <v>3769</v>
+      </c>
+      <c r="G909" s="2" t="s">
+        <v>3770</v>
+      </c>
+      <c r="H909" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I909" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J909" s="3" t="s">
+        <v>3771</v>
+      </c>
+    </row>
+    <row r="910" spans="1:10">
+      <c r="A910" s="2">
+        <v>909</v>
+      </c>
+      <c r="B910" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C910" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D910" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E910" s="2" t="s">
+        <v>3749</v>
+      </c>
+      <c r="F910" s="2" t="s">
+        <v>3772</v>
+      </c>
+      <c r="G910" s="2" t="s">
+        <v>3773</v>
+      </c>
+      <c r="H910" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I910" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J910" s="3" t="s">
+        <v>3774</v>
+      </c>
+    </row>
+    <row r="911" spans="1:10">
+      <c r="A911" s="2">
+        <v>910</v>
+      </c>
+      <c r="B911" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C911" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D911" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E911" s="2" t="s">
+        <v>3749</v>
+      </c>
+      <c r="F911" s="2" t="s">
+        <v>3775</v>
+      </c>
+      <c r="G911" s="2" t="s">
+        <v>3776</v>
+      </c>
+      <c r="H911" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I911" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J911" s="3" t="s">
+        <v>3777</v>
+      </c>
+    </row>
+    <row r="912" spans="1:10">
+      <c r="A912" s="2">
+        <v>911</v>
+      </c>
+      <c r="B912" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C912" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D912" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E912" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F912" s="2" t="s">
+        <v>3780</v>
+      </c>
+      <c r="G912" s="2" t="s">
+        <v>3781</v>
+      </c>
+      <c r="H912" s="2" t="s">
+        <v>3782</v>
+      </c>
+      <c r="I912" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J912" s="3" t="s">
+        <v>3783</v>
+      </c>
+    </row>
+    <row r="913" spans="1:10">
+      <c r="A913" s="2">
+        <v>912</v>
+      </c>
+      <c r="B913" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C913" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D913" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E913" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F913" s="2" t="s">
+        <v>3784</v>
+      </c>
+      <c r="G913" s="2" t="s">
+        <v>3785</v>
+      </c>
+      <c r="H913" s="2" t="s">
+        <v>3786</v>
+      </c>
+      <c r="I913" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J913" s="3" t="s">
+        <v>3787</v>
+      </c>
+    </row>
+    <row r="914" spans="1:10">
+      <c r="A914" s="2">
+        <v>913</v>
+      </c>
+      <c r="B914" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C914" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D914" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E914" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F914" s="2" t="s">
+        <v>3788</v>
+      </c>
+      <c r="G914" s="2" t="s">
+        <v>3789</v>
+      </c>
+      <c r="H914" s="2" t="s">
+        <v>3790</v>
+      </c>
+      <c r="I914" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J914" s="3" t="s">
+        <v>3791</v>
+      </c>
+    </row>
+    <row r="915" spans="1:10">
+      <c r="A915" s="2">
+        <v>914</v>
+      </c>
+      <c r="B915" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C915" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D915" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E915" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F915" s="2" t="s">
+        <v>3792</v>
+      </c>
+      <c r="G915" s="2" t="s">
+        <v>3793</v>
+      </c>
+      <c r="H915" s="2" t="s">
+        <v>3794</v>
+      </c>
+      <c r="I915" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J915" s="3" t="s">
+        <v>3795</v>
+      </c>
+    </row>
+    <row r="916" spans="1:10">
+      <c r="A916" s="2">
+        <v>915</v>
+      </c>
+      <c r="B916" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C916" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D916" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E916" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F916" s="2" t="s">
+        <v>3796</v>
+      </c>
+      <c r="G916" s="2" t="s">
+        <v>3797</v>
+      </c>
+      <c r="H916" s="2" t="s">
+        <v>3798</v>
+      </c>
+      <c r="I916" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J916" s="3" t="s">
+        <v>3799</v>
+      </c>
+    </row>
+    <row r="917" spans="1:10">
+      <c r="A917" s="2">
+        <v>916</v>
+      </c>
+      <c r="B917" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C917" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D917" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E917" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F917" s="2" t="s">
+        <v>3800</v>
+      </c>
+      <c r="G917" s="2" t="s">
+        <v>3801</v>
+      </c>
+      <c r="H917" s="2" t="s">
+        <v>3802</v>
+      </c>
+      <c r="I917" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J917" s="3" t="s">
+        <v>3803</v>
+      </c>
+    </row>
+    <row r="918" spans="1:10">
+      <c r="A918" s="2">
+        <v>917</v>
+      </c>
+      <c r="B918" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C918" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D918" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E918" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F918" s="2" t="s">
+        <v>3804</v>
+      </c>
+      <c r="G918" s="2" t="s">
+        <v>3805</v>
+      </c>
+      <c r="H918" s="2" t="s">
+        <v>3806</v>
+      </c>
+      <c r="I918" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J918" s="3" t="s">
+        <v>3807</v>
+      </c>
+    </row>
+    <row r="919" spans="1:10">
+      <c r="A919" s="2">
+        <v>918</v>
+      </c>
+      <c r="B919" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C919" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D919" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E919" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F919" s="2" t="s">
+        <v>3808</v>
+      </c>
+      <c r="G919" s="2" t="s">
+        <v>3809</v>
+      </c>
+      <c r="H919" s="2" t="s">
+        <v>3810</v>
+      </c>
+      <c r="I919" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J919" s="3" t="s">
+        <v>3811</v>
+      </c>
+    </row>
+    <row r="920" spans="1:10">
+      <c r="A920" s="2">
+        <v>919</v>
+      </c>
+      <c r="B920" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C920" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D920" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E920" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F920" s="2" t="s">
+        <v>3812</v>
+      </c>
+      <c r="G920" s="2" t="s">
+        <v>3813</v>
+      </c>
+      <c r="H920" s="2" t="s">
+        <v>3814</v>
+      </c>
+      <c r="I920" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J920" s="3" t="s">
+        <v>3815</v>
+      </c>
+    </row>
+    <row r="921" spans="1:10">
+      <c r="A921" s="2">
+        <v>920</v>
+      </c>
+      <c r="B921" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C921" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D921" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E921" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F921" s="2" t="s">
+        <v>3816</v>
+      </c>
+      <c r="G921" s="2" t="s">
+        <v>3817</v>
+      </c>
+      <c r="H921" s="2" t="s">
+        <v>3818</v>
+      </c>
+      <c r="I921" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J921" s="3" t="s">
+        <v>3819</v>
+      </c>
+    </row>
+    <row r="922" spans="1:10">
+      <c r="A922" s="2">
+        <v>921</v>
+      </c>
+      <c r="B922" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C922" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D922" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E922" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F922" s="2" t="s">
+        <v>3820</v>
+      </c>
+      <c r="G922" s="2" t="s">
+        <v>3821</v>
+      </c>
+      <c r="H922" s="2" t="s">
+        <v>3822</v>
+      </c>
+      <c r="I922" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J922" s="3" t="s">
+        <v>3823</v>
+      </c>
+    </row>
+    <row r="923" spans="1:10">
+      <c r="A923" s="2">
+        <v>922</v>
+      </c>
+      <c r="B923" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C923" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D923" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E923" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F923" s="2" t="s">
+        <v>3824</v>
+      </c>
+      <c r="G923" s="2" t="s">
+        <v>3825</v>
+      </c>
+      <c r="H923" s="2" t="s">
+        <v>3826</v>
+      </c>
+      <c r="I923" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J923" s="3" t="s">
+        <v>3827</v>
+      </c>
+    </row>
+    <row r="924" spans="1:10">
+      <c r="A924" s="2">
+        <v>923</v>
+      </c>
+      <c r="B924" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C924" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D924" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E924" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F924" s="2" t="s">
+        <v>3828</v>
+      </c>
+      <c r="G924" s="2" t="s">
+        <v>3829</v>
+      </c>
+      <c r="H924" s="2" t="s">
+        <v>3830</v>
+      </c>
+      <c r="I924" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J924" s="3" t="s">
+        <v>3831</v>
+      </c>
+    </row>
+    <row r="925" spans="1:10">
+      <c r="A925" s="2">
+        <v>924</v>
+      </c>
+      <c r="B925" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C925" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D925" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E925" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F925" s="2" t="s">
+        <v>3832</v>
+      </c>
+      <c r="G925" s="2" t="s">
+        <v>3833</v>
+      </c>
+      <c r="H925" s="2" t="s">
+        <v>3834</v>
+      </c>
+      <c r="I925" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J925" s="3" t="s">
+        <v>3835</v>
+      </c>
+    </row>
+    <row r="926" spans="1:10">
+      <c r="A926" s="2">
+        <v>925</v>
+      </c>
+      <c r="B926" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C926" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D926" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E926" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F926" s="2" t="s">
+        <v>3836</v>
+      </c>
+      <c r="G926" s="2" t="s">
+        <v>3837</v>
+      </c>
+      <c r="H926" s="2" t="s">
+        <v>3838</v>
+      </c>
+      <c r="I926" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J926" s="3" t="s">
+        <v>3839</v>
+      </c>
+    </row>
+    <row r="927" spans="1:10">
+      <c r="A927" s="2">
+        <v>926</v>
+      </c>
+      <c r="B927" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C927" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D927" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E927" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F927" s="2" t="s">
+        <v>3840</v>
+      </c>
+      <c r="G927" s="2" t="s">
+        <v>3841</v>
+      </c>
+      <c r="H927" s="2" t="s">
+        <v>3842</v>
+      </c>
+      <c r="I927" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J927" s="3" t="s">
+        <v>3843</v>
+      </c>
+    </row>
+    <row r="928" spans="1:10">
+      <c r="A928" s="2">
+        <v>927</v>
+      </c>
+      <c r="B928" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C928" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D928" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E928" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F928" s="2" t="s">
+        <v>3844</v>
+      </c>
+      <c r="G928" s="2" t="s">
+        <v>3845</v>
+      </c>
+      <c r="H928" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I928" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J928" s="3" t="s">
+        <v>3846</v>
+      </c>
+    </row>
+    <row r="929" spans="1:10">
+      <c r="A929" s="2">
+        <v>928</v>
+      </c>
+      <c r="B929" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C929" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D929" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E929" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F929" s="2" t="s">
+        <v>3847</v>
+      </c>
+      <c r="G929" s="2" t="s">
+        <v>3848</v>
+      </c>
+      <c r="H929" s="2" t="s">
+        <v>3849</v>
+      </c>
+      <c r="I929" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J929" s="3" t="s">
+        <v>3850</v>
+      </c>
+    </row>
+    <row r="930" spans="1:10">
+      <c r="A930" s="2">
+        <v>929</v>
+      </c>
+      <c r="B930" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C930" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D930" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E930" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F930" s="2" t="s">
+        <v>3851</v>
+      </c>
+      <c r="G930" s="2" t="s">
+        <v>3852</v>
+      </c>
+      <c r="H930" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I930" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J930" s="3" t="s">
+        <v>3853</v>
+      </c>
+    </row>
+    <row r="931" spans="1:10">
+      <c r="A931" s="2">
+        <v>930</v>
+      </c>
+      <c r="B931" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C931" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D931" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E931" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F931" s="2" t="s">
+        <v>3854</v>
+      </c>
+      <c r="G931" s="2" t="s">
+        <v>3855</v>
+      </c>
+      <c r="H931" s="2" t="s">
+        <v>3856</v>
+      </c>
+      <c r="I931" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J931" s="3" t="s">
+        <v>3857</v>
+      </c>
+    </row>
+    <row r="932" spans="1:10">
+      <c r="A932" s="2">
+        <v>931</v>
+      </c>
+      <c r="B932" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C932" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D932" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E932" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F932" s="2" t="s">
+        <v>3858</v>
+      </c>
+      <c r="G932" s="2"/>
+      <c r="H932" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I932" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J932" s="3" t="s">
+        <v>3859</v>
+      </c>
+    </row>
+    <row r="933" spans="1:10">
+      <c r="A933" s="2">
+        <v>932</v>
+      </c>
+      <c r="B933" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C933" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D933" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E933" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F933" s="2" t="s">
+        <v>3860</v>
+      </c>
+      <c r="G933" s="2" t="s">
+        <v>3861</v>
+      </c>
+      <c r="H933" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I933" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J933" s="3" t="s">
+        <v>3862</v>
+      </c>
+    </row>
+    <row r="934" spans="1:10">
+      <c r="A934" s="2">
+        <v>933</v>
+      </c>
+      <c r="B934" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C934" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D934" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E934" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F934" s="2" t="s">
+        <v>3863</v>
+      </c>
+      <c r="G934" s="2" t="s">
+        <v>3864</v>
+      </c>
+      <c r="H934" s="2" t="s">
+        <v>3865</v>
+      </c>
+      <c r="I934" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J934" s="3" t="s">
+        <v>3866</v>
+      </c>
+    </row>
+    <row r="935" spans="1:10">
+      <c r="A935" s="2">
+        <v>934</v>
+      </c>
+      <c r="B935" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C935" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D935" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E935" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F935" s="2" t="s">
+        <v>3867</v>
+      </c>
+      <c r="G935" s="2" t="s">
+        <v>3868</v>
+      </c>
+      <c r="H935" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I935" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J935" s="3" t="s">
+        <v>3869</v>
+      </c>
+    </row>
+    <row r="936" spans="1:10">
+      <c r="A936" s="2">
+        <v>935</v>
+      </c>
+      <c r="B936" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C936" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D936" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E936" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="F936" s="2" t="s">
+        <v>3870</v>
+      </c>
+      <c r="G936" s="2" t="s">
+        <v>3871</v>
+      </c>
+      <c r="H936" s="2" t="s">
+        <v>3872</v>
+      </c>
+      <c r="I936" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J936" s="3" t="s">
+        <v>3873</v>
+      </c>
+    </row>
+    <row r="937" spans="1:10">
+      <c r="A937" s="2">
+        <v>936</v>
+      </c>
+      <c r="B937" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C937" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D937" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E937" s="2" t="s">
+        <v>3874</v>
+      </c>
+      <c r="F937" s="2" t="s">
+        <v>3875</v>
+      </c>
+      <c r="G937" s="2" t="s">
+        <v>3876</v>
+      </c>
+      <c r="H937" s="2" t="s">
+        <v>3877</v>
+      </c>
+      <c r="I937" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J937" s="3" t="s">
+        <v>3878</v>
+      </c>
+    </row>
+    <row r="938" spans="1:10">
+      <c r="A938" s="2">
+        <v>937</v>
+      </c>
+      <c r="B938" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C938" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D938" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E938" s="2" t="s">
+        <v>3874</v>
+      </c>
+      <c r="F938" s="2" t="s">
+        <v>3879</v>
+      </c>
+      <c r="G938" s="2" t="s">
+        <v>3880</v>
+      </c>
+      <c r="H938" s="2" t="s">
+        <v>3881</v>
+      </c>
+      <c r="I938" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J938" s="3" t="s">
+        <v>3882</v>
+      </c>
+    </row>
+    <row r="939" spans="1:10">
+      <c r="A939" s="2">
+        <v>938</v>
+      </c>
+      <c r="B939" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C939" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D939" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E939" s="2" t="s">
+        <v>3874</v>
+      </c>
+      <c r="F939" s="2" t="s">
+        <v>3883</v>
+      </c>
+      <c r="G939" s="2" t="s">
+        <v>3884</v>
+      </c>
+      <c r="H939" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I939" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J939" s="3" t="s">
+        <v>3885</v>
+      </c>
+    </row>
+    <row r="940" spans="1:10">
+      <c r="A940" s="2">
+        <v>939</v>
+      </c>
+      <c r="B940" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C940" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D940" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E940" s="2" t="s">
+        <v>3874</v>
+      </c>
+      <c r="F940" s="2" t="s">
+        <v>3886</v>
+      </c>
+      <c r="G940" s="2" t="s">
+        <v>3887</v>
+      </c>
+      <c r="H940" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I940" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J940" s="3" t="s">
+        <v>3888</v>
+      </c>
+    </row>
+    <row r="941" spans="1:10">
+      <c r="A941" s="2">
+        <v>940</v>
+      </c>
+      <c r="B941" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C941" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D941" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E941" s="2" t="s">
+        <v>3874</v>
+      </c>
+      <c r="F941" s="2" t="s">
+        <v>3889</v>
+      </c>
+      <c r="G941" s="2" t="s">
+        <v>3890</v>
+      </c>
+      <c r="H941" s="2" t="s">
+        <v>3891</v>
+      </c>
+      <c r="I941" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J941" s="3" t="s">
+        <v>3892</v>
+      </c>
+    </row>
+    <row r="942" spans="1:10">
+      <c r="A942" s="2">
+        <v>941</v>
+      </c>
+      <c r="B942" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C942" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D942" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E942" s="2" t="s">
+        <v>3874</v>
+      </c>
+      <c r="F942" s="2" t="s">
+        <v>3893</v>
+      </c>
+      <c r="G942" s="2" t="s">
+        <v>3894</v>
+      </c>
+      <c r="H942" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I942" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J942" s="3" t="s">
+        <v>3895</v>
+      </c>
+    </row>
+    <row r="943" spans="1:10">
+      <c r="A943" s="2">
+        <v>942</v>
+      </c>
+      <c r="B943" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C943" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D943" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E943" s="2" t="s">
+        <v>3874</v>
+      </c>
+      <c r="F943" s="2" t="s">
+        <v>3896</v>
+      </c>
+      <c r="G943" s="2" t="s">
+        <v>3897</v>
+      </c>
+      <c r="H943" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I943" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J943" s="3" t="s">
+        <v>3898</v>
+      </c>
+    </row>
+    <row r="944" spans="1:10">
+      <c r="A944" s="2">
+        <v>943</v>
+      </c>
+      <c r="B944" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C944" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D944" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E944" s="2" t="s">
+        <v>3874</v>
+      </c>
+      <c r="F944" s="2" t="s">
+        <v>3899</v>
+      </c>
+      <c r="G944" s="2" t="s">
+        <v>3900</v>
+      </c>
+      <c r="H944" s="2" t="s">
+        <v>3901</v>
+      </c>
+      <c r="I944" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J944" s="3" t="s">
+        <v>3902</v>
+      </c>
+    </row>
+    <row r="945" spans="1:10">
+      <c r="A945" s="2">
+        <v>944</v>
+      </c>
+      <c r="B945" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C945" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D945" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E945" s="2" t="s">
+        <v>3874</v>
+      </c>
+      <c r="F945" s="2" t="s">
+        <v>3903</v>
+      </c>
+      <c r="G945" s="2" t="s">
+        <v>3904</v>
+      </c>
+      <c r="H945" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I945" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J945" s="3" t="s">
+        <v>3905</v>
+      </c>
+    </row>
+    <row r="946" spans="1:10">
+      <c r="A946" s="2">
+        <v>945</v>
+      </c>
+      <c r="B946" s="2" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C946" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D946" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E946" s="2" t="s">
+        <v>3874</v>
+      </c>
+      <c r="F946" s="2" t="s">
+        <v>3889</v>
+      </c>
+      <c r="G946" s="2" t="s">
+        <v>3906</v>
+      </c>
+      <c r="H946" s="2" t="s">
+        <v>3907</v>
+      </c>
+      <c r="I946" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J946" s="3" t="s">
+        <v>3908</v>
+      </c>
+    </row>
+    <row r="947" spans="1:10">
+      <c r="A947" s="2">
+        <v>946</v>
+      </c>
+      <c r="B947" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C947" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D947" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E947" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F947" s="2" t="s">
+        <v>3911</v>
+      </c>
+      <c r="G947" s="2" t="s">
+        <v>3912</v>
+      </c>
+      <c r="H947" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I947" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J947" s="3" t="s">
+        <v>3913</v>
+      </c>
+    </row>
+    <row r="948" spans="1:10">
+      <c r="A948" s="2">
+        <v>947</v>
+      </c>
+      <c r="B948" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C948" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D948" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E948" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F948" s="2" t="s">
+        <v>3914</v>
+      </c>
+      <c r="G948" s="2" t="s">
+        <v>3915</v>
+      </c>
+      <c r="H948" s="2" t="s">
+        <v>3916</v>
+      </c>
+      <c r="I948" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J948" s="3" t="s">
+        <v>3917</v>
+      </c>
+    </row>
+    <row r="949" spans="1:10">
+      <c r="A949" s="2">
+        <v>948</v>
+      </c>
+      <c r="B949" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C949" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D949" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E949" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F949" s="2" t="s">
+        <v>3918</v>
+      </c>
+      <c r="G949" s="2" t="s">
+        <v>3919</v>
+      </c>
+      <c r="H949" s="2" t="s">
+        <v>3920</v>
+      </c>
+      <c r="I949" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J949" s="3" t="s">
+        <v>3921</v>
+      </c>
+    </row>
+    <row r="950" spans="1:10">
+      <c r="A950" s="2">
+        <v>949</v>
+      </c>
+      <c r="B950" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C950" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D950" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E950" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F950" s="2" t="s">
+        <v>3922</v>
+      </c>
+      <c r="G950" s="2" t="s">
+        <v>3923</v>
+      </c>
+      <c r="H950" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I950" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J950" s="3" t="s">
+        <v>3924</v>
+      </c>
+    </row>
+    <row r="951" spans="1:10">
+      <c r="A951" s="2">
+        <v>950</v>
+      </c>
+      <c r="B951" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C951" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D951" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E951" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F951" s="2" t="s">
+        <v>3925</v>
+      </c>
+      <c r="G951" s="2" t="s">
+        <v>3926</v>
+      </c>
+      <c r="H951" s="2" t="s">
+        <v>3927</v>
+      </c>
+      <c r="I951" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J951" s="3" t="s">
+        <v>3928</v>
+      </c>
+    </row>
+    <row r="952" spans="1:10">
+      <c r="A952" s="2">
+        <v>951</v>
+      </c>
+      <c r="B952" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C952" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D952" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E952" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F952" s="2" t="s">
+        <v>3929</v>
+      </c>
+      <c r="G952" s="2" t="s">
+        <v>3930</v>
+      </c>
+      <c r="H952" s="2" t="s">
+        <v>3931</v>
+      </c>
+      <c r="I952" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J952" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="953" spans="1:10">
+      <c r="A953" s="2">
+        <v>952</v>
+      </c>
+      <c r="B953" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C953" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D953" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E953" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F953" s="2" t="s">
+        <v>3933</v>
+      </c>
+      <c r="G953" s="2" t="s">
+        <v>3934</v>
+      </c>
+      <c r="H953" s="2" t="s">
+        <v>3935</v>
+      </c>
+      <c r="I953" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J953" s="3" t="s">
+        <v>3936</v>
+      </c>
+    </row>
+    <row r="954" spans="1:10">
+      <c r="A954" s="2">
+        <v>953</v>
+      </c>
+      <c r="B954" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C954" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D954" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E954" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F954" s="2" t="s">
+        <v>3937</v>
+      </c>
+      <c r="G954" s="2" t="s">
+        <v>3938</v>
+      </c>
+      <c r="H954" s="2" t="s">
+        <v>3939</v>
+      </c>
+      <c r="I954" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J954" s="3" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="955" spans="1:10">
+      <c r="A955" s="2">
+        <v>954</v>
+      </c>
+      <c r="B955" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C955" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D955" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E955" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F955" s="2" t="s">
+        <v>3941</v>
+      </c>
+      <c r="G955" s="2" t="s">
+        <v>3942</v>
+      </c>
+      <c r="H955" s="2" t="s">
+        <v>3943</v>
+      </c>
+      <c r="I955" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J955" s="3" t="s">
+        <v>3944</v>
+      </c>
+    </row>
+    <row r="956" spans="1:10">
+      <c r="A956" s="2">
+        <v>955</v>
+      </c>
+      <c r="B956" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C956" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D956" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E956" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F956" s="2" t="s">
+        <v>3945</v>
+      </c>
+      <c r="G956" s="2" t="s">
+        <v>3946</v>
+      </c>
+      <c r="H956" s="2" t="s">
+        <v>3947</v>
+      </c>
+      <c r="I956" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J956" s="3" t="s">
+        <v>3948</v>
+      </c>
+    </row>
+    <row r="957" spans="1:10">
+      <c r="A957" s="2">
+        <v>956</v>
+      </c>
+      <c r="B957" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C957" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D957" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E957" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F957" s="2" t="s">
+        <v>3949</v>
+      </c>
+      <c r="G957" s="2" t="s">
+        <v>3950</v>
+      </c>
+      <c r="H957" s="2" t="s">
+        <v>3951</v>
+      </c>
+      <c r="I957" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J957" s="3" t="s">
+        <v>3952</v>
+      </c>
+    </row>
+    <row r="958" spans="1:10">
+      <c r="A958" s="2">
+        <v>957</v>
+      </c>
+      <c r="B958" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C958" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D958" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E958" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F958" s="2" t="s">
+        <v>3953</v>
+      </c>
+      <c r="G958" s="2" t="s">
+        <v>3954</v>
+      </c>
+      <c r="H958" s="2" t="s">
+        <v>3955</v>
+      </c>
+      <c r="I958" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J958" s="3" t="s">
+        <v>3956</v>
+      </c>
+    </row>
+    <row r="959" spans="1:10">
+      <c r="A959" s="2">
+        <v>958</v>
+      </c>
+      <c r="B959" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C959" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D959" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E959" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F959" s="2" t="s">
+        <v>3957</v>
+      </c>
+      <c r="G959" s="2" t="s">
+        <v>3958</v>
+      </c>
+      <c r="H959" s="2" t="s">
+        <v>3959</v>
+      </c>
+      <c r="I959" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J959" s="3" t="s">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="960" spans="1:10">
+      <c r="A960" s="2">
+        <v>959</v>
+      </c>
+      <c r="B960" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C960" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D960" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E960" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F960" s="2" t="s">
+        <v>3961</v>
+      </c>
+      <c r="G960" s="2" t="s">
+        <v>3962</v>
+      </c>
+      <c r="H960" s="2" t="s">
+        <v>3963</v>
+      </c>
+      <c r="I960" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J960" s="3" t="s">
+        <v>3964</v>
+      </c>
+    </row>
+    <row r="961" spans="1:10">
+      <c r="A961" s="2">
+        <v>960</v>
+      </c>
+      <c r="B961" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C961" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D961" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E961" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F961" s="2" t="s">
+        <v>3965</v>
+      </c>
+      <c r="G961" s="2" t="s">
+        <v>3966</v>
+      </c>
+      <c r="H961" s="2" t="s">
+        <v>3967</v>
+      </c>
+      <c r="I961" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J961" s="3" t="s">
+        <v>3968</v>
+      </c>
+    </row>
+    <row r="962" spans="1:10">
+      <c r="A962" s="2">
+        <v>961</v>
+      </c>
+      <c r="B962" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C962" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D962" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E962" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F962" s="2" t="s">
+        <v>3969</v>
+      </c>
+      <c r="G962" s="2" t="s">
+        <v>3970</v>
+      </c>
+      <c r="H962" s="2" t="s">
+        <v>3971</v>
+      </c>
+      <c r="I962" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J962" s="3" t="s">
+        <v>3972</v>
+      </c>
+    </row>
+    <row r="963" spans="1:10">
+      <c r="A963" s="2">
+        <v>962</v>
+      </c>
+      <c r="B963" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C963" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D963" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E963" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F963" s="2" t="s">
+        <v>3973</v>
+      </c>
+      <c r="G963" s="2" t="s">
+        <v>3974</v>
+      </c>
+      <c r="H963" s="2" t="s">
+        <v>3975</v>
+      </c>
+      <c r="I963" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J963" s="3" t="s">
+        <v>3976</v>
+      </c>
+    </row>
+    <row r="964" spans="1:10">
+      <c r="A964" s="2">
+        <v>963</v>
+      </c>
+      <c r="B964" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C964" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D964" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E964" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F964" s="2" t="s">
+        <v>3977</v>
+      </c>
+      <c r="G964" s="2" t="s">
+        <v>3978</v>
+      </c>
+      <c r="H964" s="2" t="s">
+        <v>3979</v>
+      </c>
+      <c r="I964" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J964" s="3" t="s">
+        <v>3980</v>
+      </c>
+    </row>
+    <row r="965" spans="1:10">
+      <c r="A965" s="2">
+        <v>964</v>
+      </c>
+      <c r="B965" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C965" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D965" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E965" s="2" t="s">
+        <v>3910</v>
+      </c>
+      <c r="F965" s="2" t="s">
+        <v>3981</v>
+      </c>
+      <c r="G965" s="2" t="s">
+        <v>3982</v>
+      </c>
+      <c r="H965" s="2" t="s">
+        <v>3983</v>
+      </c>
+      <c r="I965" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J965" s="3" t="s">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="966" spans="1:10">
+      <c r="A966" s="2">
+        <v>965</v>
+      </c>
+      <c r="B966" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C966" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D966" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E966" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F966" s="2" t="s">
+        <v>3986</v>
+      </c>
+      <c r="G966" s="2" t="s">
+        <v>3987</v>
+      </c>
+      <c r="H966" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I966" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J966" s="3" t="s">
+        <v>3988</v>
+      </c>
+    </row>
+    <row r="967" spans="1:10">
+      <c r="A967" s="2">
+        <v>966</v>
+      </c>
+      <c r="B967" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C967" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D967" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E967" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F967" s="2" t="s">
+        <v>3989</v>
+      </c>
+      <c r="G967" s="2" t="s">
+        <v>3990</v>
+      </c>
+      <c r="H967" s="2" t="s">
+        <v>3991</v>
+      </c>
+      <c r="I967" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J967" s="3" t="s">
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="968" spans="1:10">
+      <c r="A968" s="2">
+        <v>967</v>
+      </c>
+      <c r="B968" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C968" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D968" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E968" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F968" s="2" t="s">
+        <v>3993</v>
+      </c>
+      <c r="G968" s="2" t="s">
+        <v>3994</v>
+      </c>
+      <c r="H968" s="2" t="s">
+        <v>3995</v>
+      </c>
+      <c r="I968" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J968" s="3" t="s">
+        <v>3996</v>
+      </c>
+    </row>
+    <row r="969" spans="1:10">
+      <c r="A969" s="2">
+        <v>968</v>
+      </c>
+      <c r="B969" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C969" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D969" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E969" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F969" s="2" t="s">
+        <v>3997</v>
+      </c>
+      <c r="G969" s="2" t="s">
+        <v>3998</v>
+      </c>
+      <c r="H969" s="2" t="s">
+        <v>3999</v>
+      </c>
+      <c r="I969" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J969" s="3" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="970" spans="1:10">
+      <c r="A970" s="2">
+        <v>969</v>
+      </c>
+      <c r="B970" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C970" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D970" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E970" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F970" s="2" t="s">
+        <v>4001</v>
+      </c>
+      <c r="G970" s="2" t="s">
+        <v>4002</v>
+      </c>
+      <c r="H970" s="2" t="s">
+        <v>4003</v>
+      </c>
+      <c r="I970" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J970" s="3" t="s">
+        <v>4004</v>
+      </c>
+    </row>
+    <row r="971" spans="1:10">
+      <c r="A971" s="2">
+        <v>970</v>
+      </c>
+      <c r="B971" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C971" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D971" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E971" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F971" s="2" t="s">
+        <v>4005</v>
+      </c>
+      <c r="G971" s="2" t="s">
+        <v>4006</v>
+      </c>
+      <c r="H971" s="2" t="s">
+        <v>4007</v>
+      </c>
+      <c r="I971" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J971" s="3" t="s">
+        <v>4008</v>
+      </c>
+    </row>
+    <row r="972" spans="1:10">
+      <c r="A972" s="2">
+        <v>971</v>
+      </c>
+      <c r="B972" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C972" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D972" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E972" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F972" s="2" t="s">
+        <v>4009</v>
+      </c>
+      <c r="G972" s="2" t="s">
+        <v>4010</v>
+      </c>
+      <c r="H972" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I972" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J972" s="3" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="973" spans="1:10">
+      <c r="A973" s="2">
+        <v>972</v>
+      </c>
+      <c r="B973" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C973" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D973" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E973" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F973" s="2" t="s">
+        <v>4012</v>
+      </c>
+      <c r="G973" s="2" t="s">
+        <v>4013</v>
+      </c>
+      <c r="H973" s="2" t="s">
+        <v>4014</v>
+      </c>
+      <c r="I973" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J973" s="3" t="s">
+        <v>4015</v>
+      </c>
+    </row>
+    <row r="974" spans="1:10">
+      <c r="A974" s="2">
+        <v>973</v>
+      </c>
+      <c r="B974" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C974" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D974" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E974" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F974" s="2" t="s">
+        <v>4016</v>
+      </c>
+      <c r="G974" s="2" t="s">
+        <v>4017</v>
+      </c>
+      <c r="H974" s="2" t="s">
+        <v>4018</v>
+      </c>
+      <c r="I974" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J974" s="3" t="s">
+        <v>4019</v>
+      </c>
+    </row>
+    <row r="975" spans="1:10">
+      <c r="A975" s="2">
+        <v>974</v>
+      </c>
+      <c r="B975" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C975" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D975" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E975" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F975" s="2" t="s">
+        <v>4020</v>
+      </c>
+      <c r="G975" s="2" t="s">
+        <v>4021</v>
+      </c>
+      <c r="H975" s="2" t="s">
+        <v>4022</v>
+      </c>
+      <c r="I975" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J975" s="3" t="s">
+        <v>4023</v>
+      </c>
+    </row>
+    <row r="976" spans="1:10">
+      <c r="A976" s="2">
+        <v>975</v>
+      </c>
+      <c r="B976" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C976" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D976" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E976" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F976" s="2" t="s">
+        <v>4024</v>
+      </c>
+      <c r="G976" s="2" t="s">
+        <v>4025</v>
+      </c>
+      <c r="H976" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I976" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J976" s="3" t="s">
+        <v>4026</v>
+      </c>
+    </row>
+    <row r="977" spans="1:10">
+      <c r="A977" s="2">
+        <v>976</v>
+      </c>
+      <c r="B977" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C977" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D977" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E977" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F977" s="2" t="s">
+        <v>4027</v>
+      </c>
+      <c r="G977" s="2" t="s">
+        <v>4028</v>
+      </c>
+      <c r="H977" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I977" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J977" s="3" t="s">
+        <v>4029</v>
+      </c>
+    </row>
+    <row r="978" spans="1:10">
+      <c r="A978" s="2">
+        <v>977</v>
+      </c>
+      <c r="B978" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C978" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D978" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E978" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F978" s="2" t="s">
+        <v>4030</v>
+      </c>
+      <c r="G978" s="2" t="s">
+        <v>4031</v>
+      </c>
+      <c r="H978" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I978" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J978" s="3" t="s">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="979" spans="1:10">
+      <c r="A979" s="2">
+        <v>978</v>
+      </c>
+      <c r="B979" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C979" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D979" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E979" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F979" s="2" t="s">
+        <v>4033</v>
+      </c>
+      <c r="G979" s="2" t="s">
+        <v>4034</v>
+      </c>
+      <c r="H979" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I979" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J979" s="3" t="s">
+        <v>4035</v>
+      </c>
+    </row>
+    <row r="980" spans="1:10">
+      <c r="A980" s="2">
+        <v>979</v>
+      </c>
+      <c r="B980" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C980" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D980" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E980" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F980" s="2" t="s">
+        <v>4036</v>
+      </c>
+      <c r="G980" s="2" t="s">
+        <v>4037</v>
+      </c>
+      <c r="H980" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I980" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J980" s="3" t="s">
+        <v>4038</v>
+      </c>
+    </row>
+    <row r="981" spans="1:10">
+      <c r="A981" s="2">
+        <v>980</v>
+      </c>
+      <c r="B981" s="2" t="s">
+        <v>3909</v>
+      </c>
+      <c r="C981" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D981" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E981" s="2" t="s">
+        <v>3985</v>
+      </c>
+      <c r="F981" s="2" t="s">
+        <v>4039</v>
+      </c>
+      <c r="G981" s="2" t="s">
+        <v>4040</v>
+      </c>
+      <c r="H981" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I981" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J981" s="3" t="s">
+        <v>4041</v>
+      </c>
+    </row>
+    <row r="982" spans="1:10">
+      <c r="A982" s="2">
+        <v>981</v>
+      </c>
+      <c r="B982" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C982" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D982" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E982" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F982" s="2" t="s">
+        <v>4044</v>
+      </c>
+      <c r="G982" s="2" t="s">
+        <v>4045</v>
+      </c>
+      <c r="H982" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I982" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J982" s="3" t="s">
+        <v>4046</v>
+      </c>
+    </row>
+    <row r="983" spans="1:10">
+      <c r="A983" s="2">
+        <v>982</v>
+      </c>
+      <c r="B983" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C983" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D983" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E983" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F983" s="2" t="s">
+        <v>4047</v>
+      </c>
+      <c r="G983" s="2" t="s">
+        <v>4048</v>
+      </c>
+      <c r="H983" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I983" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J983" s="3" t="s">
+        <v>4049</v>
+      </c>
+    </row>
+    <row r="984" spans="1:10">
+      <c r="A984" s="2">
+        <v>983</v>
+      </c>
+      <c r="B984" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C984" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D984" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E984" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F984" s="2" t="s">
+        <v>4050</v>
+      </c>
+      <c r="G984" s="2" t="s">
+        <v>4051</v>
+      </c>
+      <c r="H984" s="2" t="s">
+        <v>4052</v>
+      </c>
+      <c r="I984" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J984" s="3" t="s">
+        <v>4053</v>
+      </c>
+    </row>
+    <row r="985" spans="1:10">
+      <c r="A985" s="2">
+        <v>984</v>
+      </c>
+      <c r="B985" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C985" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D985" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E985" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F985" s="2" t="s">
+        <v>4054</v>
+      </c>
+      <c r="G985" s="2" t="s">
+        <v>4055</v>
+      </c>
+      <c r="H985" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I985" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J985" s="3" t="s">
+        <v>4056</v>
+      </c>
+    </row>
+    <row r="986" spans="1:10">
+      <c r="A986" s="2">
+        <v>985</v>
+      </c>
+      <c r="B986" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C986" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D986" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E986" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F986" s="2" t="s">
+        <v>4057</v>
+      </c>
+      <c r="G986" s="2" t="s">
+        <v>4058</v>
+      </c>
+      <c r="H986" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I986" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J986" s="3" t="s">
+        <v>4059</v>
+      </c>
+    </row>
+    <row r="987" spans="1:10">
+      <c r="A987" s="2">
+        <v>986</v>
+      </c>
+      <c r="B987" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C987" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D987" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E987" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F987" s="2" t="s">
+        <v>4060</v>
+      </c>
+      <c r="G987" s="2" t="s">
+        <v>4061</v>
+      </c>
+      <c r="H987" s="2" t="s">
+        <v>4062</v>
+      </c>
+      <c r="I987" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J987" s="3" t="s">
+        <v>4063</v>
+      </c>
+    </row>
+    <row r="988" spans="1:10">
+      <c r="A988" s="2">
+        <v>987</v>
+      </c>
+      <c r="B988" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C988" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D988" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E988" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F988" s="2" t="s">
+        <v>4064</v>
+      </c>
+      <c r="G988" s="2" t="s">
+        <v>4065</v>
+      </c>
+      <c r="H988" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I988" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J988" s="3" t="s">
+        <v>4066</v>
+      </c>
+    </row>
+    <row r="989" spans="1:10">
+      <c r="A989" s="2">
+        <v>988</v>
+      </c>
+      <c r="B989" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C989" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D989" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E989" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F989" s="2" t="s">
+        <v>4067</v>
+      </c>
+      <c r="G989" s="2" t="s">
+        <v>4068</v>
+      </c>
+      <c r="H989" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I989" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J989" s="3" t="s">
+        <v>4069</v>
+      </c>
+    </row>
+    <row r="990" spans="1:10">
+      <c r="A990" s="2">
+        <v>989</v>
+      </c>
+      <c r="B990" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C990" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D990" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E990" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F990" s="2" t="s">
+        <v>4070</v>
+      </c>
+      <c r="G990" s="2" t="s">
+        <v>4071</v>
+      </c>
+      <c r="H990" s="2" t="s">
+        <v>4072</v>
+      </c>
+      <c r="I990" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J990" s="3" t="s">
+        <v>4073</v>
+      </c>
+    </row>
+    <row r="991" spans="1:10">
+      <c r="A991" s="2">
+        <v>990</v>
+      </c>
+      <c r="B991" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C991" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D991" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E991" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F991" s="2" t="s">
+        <v>4074</v>
+      </c>
+      <c r="G991" s="2" t="s">
+        <v>4075</v>
+      </c>
+      <c r="H991" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I991" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J991" s="3" t="s">
+        <v>4076</v>
+      </c>
+    </row>
+    <row r="992" spans="1:10">
+      <c r="A992" s="2">
+        <v>991</v>
+      </c>
+      <c r="B992" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C992" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D992" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E992" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F992" s="2" t="s">
+        <v>4077</v>
+      </c>
+      <c r="G992" s="2" t="s">
+        <v>4078</v>
+      </c>
+      <c r="H992" s="2" t="s">
+        <v>4079</v>
+      </c>
+      <c r="I992" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J992" s="3" t="s">
+        <v>4080</v>
+      </c>
+    </row>
+    <row r="993" spans="1:10">
+      <c r="A993" s="2">
+        <v>992</v>
+      </c>
+      <c r="B993" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C993" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D993" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E993" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F993" s="2" t="s">
+        <v>4081</v>
+      </c>
+      <c r="G993" s="2" t="s">
+        <v>4082</v>
+      </c>
+      <c r="H993" s="2" t="s">
+        <v>4083</v>
+      </c>
+      <c r="I993" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J993" s="3" t="s">
+        <v>4084</v>
+      </c>
+    </row>
+    <row r="994" spans="1:10">
+      <c r="A994" s="2">
+        <v>993</v>
+      </c>
+      <c r="B994" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C994" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D994" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E994" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F994" s="2" t="s">
+        <v>4085</v>
+      </c>
+      <c r="G994" s="2" t="s">
+        <v>4086</v>
+      </c>
+      <c r="H994" s="2" t="s">
+        <v>4087</v>
+      </c>
+      <c r="I994" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J994" s="3" t="s">
+        <v>4088</v>
+      </c>
+    </row>
+    <row r="995" spans="1:10">
+      <c r="A995" s="2">
+        <v>994</v>
+      </c>
+      <c r="B995" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C995" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D995" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E995" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F995" s="2" t="s">
+        <v>4089</v>
+      </c>
+      <c r="G995" s="2" t="s">
+        <v>4090</v>
+      </c>
+      <c r="H995" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I995" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J995" s="3" t="s">
+        <v>4091</v>
+      </c>
+    </row>
+    <row r="996" spans="1:10">
+      <c r="A996" s="2">
+        <v>995</v>
+      </c>
+      <c r="B996" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C996" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D996" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E996" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F996" s="2" t="s">
+        <v>4092</v>
+      </c>
+      <c r="G996" s="2" t="s">
+        <v>4093</v>
+      </c>
+      <c r="H996" s="2" t="s">
+        <v>4094</v>
+      </c>
+      <c r="I996" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J996" s="3" t="s">
+        <v>4095</v>
+      </c>
+    </row>
+    <row r="997" spans="1:10">
+      <c r="A997" s="2">
+        <v>996</v>
+      </c>
+      <c r="B997" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C997" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D997" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E997" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F997" s="2" t="s">
+        <v>4096</v>
+      </c>
+      <c r="G997" s="2">
+        <f>&gt; 나이 들어서 살다보면 응급실 갈 일도 있고, 대학병원에 가서 정기적으로 진찰 받을 일도 있는데 그 때마다 서울 올라오는 것은 너무 힘든 일입닏. 주변에 이것 때문에 귀촌했다가도 돌아오시는 분 몇 봤습니다. 차로 대학병원을 힘들지 않게 갈 수 있는 거리여야 한다는 걸 중요하게 생각했는데요. 서천에는 큰 병원이 없는데요 여기서는 차로 20분이면 군산입니다. 군산에 큰 병원들이 있고 전북대학교 병원도...</f>
+        <v>0</v>
+      </c>
+      <c r="H997" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I997" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J997" s="3" t="s">
+        <v>4097</v>
+      </c>
+    </row>
+    <row r="998" spans="1:10">
+      <c r="A998" s="2">
+        <v>997</v>
+      </c>
+      <c r="B998" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C998" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D998" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E998" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F998" s="2" t="s">
+        <v>4098</v>
+      </c>
+      <c r="G998" s="2" t="s">
+        <v>4099</v>
+      </c>
+      <c r="H998" s="2" t="s">
+        <v>4100</v>
+      </c>
+      <c r="I998" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J998" s="3" t="s">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="999" spans="1:10">
+      <c r="A999" s="2">
+        <v>998</v>
+      </c>
+      <c r="B999" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C999" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D999" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E999" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F999" s="2" t="s">
+        <v>4102</v>
+      </c>
+      <c r="G999" s="2" t="s">
+        <v>4103</v>
+      </c>
+      <c r="H999" s="2" t="s">
+        <v>4104</v>
+      </c>
+      <c r="I999" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J999" s="3" t="s">
+        <v>4105</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:10">
+      <c r="A1000" s="2">
+        <v>999</v>
+      </c>
+      <c r="B1000" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1000" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1000" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1000" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F1000" s="2" t="s">
+        <v>4106</v>
+      </c>
+      <c r="G1000" s="2" t="s">
+        <v>4107</v>
+      </c>
+      <c r="H1000" s="2" t="s">
+        <v>4108</v>
+      </c>
+      <c r="I1000" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1000" s="3" t="s">
+        <v>4109</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:10">
+      <c r="A1001" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B1001" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1001" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1001" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1001" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F1001" s="2" t="s">
+        <v>4110</v>
+      </c>
+      <c r="G1001" s="2" t="s">
+        <v>4111</v>
+      </c>
+      <c r="H1001" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1001" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1001" s="3" t="s">
+        <v>4112</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:10">
+      <c r="A1002" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B1002" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1002" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1002" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1002" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F1002" s="2" t="s">
+        <v>4113</v>
+      </c>
+      <c r="G1002" s="2" t="s">
+        <v>4114</v>
+      </c>
+      <c r="H1002" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1002" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1002" s="3" t="s">
+        <v>4115</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:10">
+      <c r="A1003" s="2">
+        <v>1002</v>
+      </c>
+      <c r="B1003" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1003" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1003" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1003" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F1003" s="2" t="s">
+        <v>4116</v>
+      </c>
+      <c r="G1003" s="2" t="s">
+        <v>4117</v>
+      </c>
+      <c r="H1003" s="2" t="s">
+        <v>4118</v>
+      </c>
+      <c r="I1003" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1003" s="3" t="s">
+        <v>4119</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:10">
+      <c r="A1004" s="2">
+        <v>1003</v>
+      </c>
+      <c r="B1004" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1004" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1004" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1004" s="2" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F1004" s="2" t="s">
+        <v>4120</v>
+      </c>
+      <c r="G1004" s="2" t="s">
+        <v>4121</v>
+      </c>
+      <c r="H1004" s="2" t="s">
+        <v>4122</v>
+      </c>
+      <c r="I1004" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1004" s="3" t="s">
+        <v>4123</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:10">
+      <c r="A1005" s="2">
+        <v>1004</v>
+      </c>
+      <c r="B1005" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1005" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1005" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1005" s="2" t="s">
+        <v>4124</v>
+      </c>
+      <c r="F1005" s="2" t="s">
+        <v>4125</v>
+      </c>
+      <c r="G1005" s="2" t="s">
+        <v>4126</v>
+      </c>
+      <c r="H1005" s="2" t="s">
+        <v>4127</v>
+      </c>
+      <c r="I1005" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1005" s="3" t="s">
+        <v>4128</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:10">
+      <c r="A1006" s="2">
+        <v>1005</v>
+      </c>
+      <c r="B1006" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1006" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1006" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1006" s="2" t="s">
+        <v>4124</v>
+      </c>
+      <c r="F1006" s="2" t="s">
+        <v>4129</v>
+      </c>
+      <c r="G1006" s="2" t="s">
+        <v>4130</v>
+      </c>
+      <c r="H1006" s="2" t="s">
+        <v>4131</v>
+      </c>
+      <c r="I1006" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1006" s="3" t="s">
+        <v>4132</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:10">
+      <c r="A1007" s="2">
+        <v>1006</v>
+      </c>
+      <c r="B1007" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1007" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1007" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1007" s="2" t="s">
+        <v>4124</v>
+      </c>
+      <c r="F1007" s="2" t="s">
+        <v>4133</v>
+      </c>
+      <c r="G1007" s="2" t="s">
+        <v>4134</v>
+      </c>
+      <c r="H1007" s="2" t="s">
+        <v>4135</v>
+      </c>
+      <c r="I1007" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1007" s="3" t="s">
+        <v>4136</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:10">
+      <c r="A1008" s="2">
+        <v>1007</v>
+      </c>
+      <c r="B1008" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1008" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1008" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1008" s="2" t="s">
+        <v>4124</v>
+      </c>
+      <c r="F1008" s="2" t="s">
+        <v>4137</v>
+      </c>
+      <c r="G1008" s="2" t="s">
+        <v>4138</v>
+      </c>
+      <c r="H1008" s="2" t="s">
+        <v>4139</v>
+      </c>
+      <c r="I1008" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1008" s="3" t="s">
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:10">
+      <c r="A1009" s="2">
+        <v>1008</v>
+      </c>
+      <c r="B1009" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1009" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1009" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1009" s="2" t="s">
+        <v>4124</v>
+      </c>
+      <c r="F1009" s="2" t="s">
+        <v>4141</v>
+      </c>
+      <c r="G1009" s="2" t="s">
+        <v>4142</v>
+      </c>
+      <c r="H1009" s="2" t="s">
+        <v>4143</v>
+      </c>
+      <c r="I1009" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1009" s="3" t="s">
+        <v>4144</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:10">
+      <c r="A1010" s="2">
+        <v>1009</v>
+      </c>
+      <c r="B1010" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1010" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1010" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1010" s="2" t="s">
+        <v>4124</v>
+      </c>
+      <c r="F1010" s="2" t="s">
+        <v>4145</v>
+      </c>
+      <c r="G1010" s="2" t="s">
+        <v>4146</v>
+      </c>
+      <c r="H1010" s="2" t="s">
+        <v>4147</v>
+      </c>
+      <c r="I1010" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1010" s="3" t="s">
+        <v>4148</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:10">
+      <c r="A1011" s="2">
+        <v>1010</v>
+      </c>
+      <c r="B1011" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1011" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1011" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1011" s="2" t="s">
+        <v>4124</v>
+      </c>
+      <c r="F1011" s="2" t="s">
+        <v>4149</v>
+      </c>
+      <c r="G1011" s="2" t="s">
+        <v>4150</v>
+      </c>
+      <c r="H1011" s="2" t="s">
+        <v>4151</v>
+      </c>
+      <c r="I1011" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1011" s="3" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:10">
+      <c r="A1012" s="2">
+        <v>1011</v>
+      </c>
+      <c r="B1012" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1012" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1012" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1012" s="2" t="s">
+        <v>4124</v>
+      </c>
+      <c r="F1012" s="2" t="s">
+        <v>4153</v>
+      </c>
+      <c r="G1012" s="2" t="s">
+        <v>4154</v>
+      </c>
+      <c r="H1012" s="2" t="s">
+        <v>4155</v>
+      </c>
+      <c r="I1012" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1012" s="3" t="s">
+        <v>4156</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:10">
+      <c r="A1013" s="2">
+        <v>1012</v>
+      </c>
+      <c r="B1013" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1013" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1013" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1013" s="2" t="s">
+        <v>4124</v>
+      </c>
+      <c r="F1013" s="2" t="s">
+        <v>4157</v>
+      </c>
+      <c r="G1013" s="2" t="s">
+        <v>4158</v>
+      </c>
+      <c r="H1013" s="2" t="s">
+        <v>4159</v>
+      </c>
+      <c r="I1013" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1013" s="3" t="s">
+        <v>4160</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:10">
+      <c r="A1014" s="2">
+        <v>1013</v>
+      </c>
+      <c r="B1014" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1014" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1014" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1014" s="2" t="s">
+        <v>4124</v>
+      </c>
+      <c r="F1014" s="2" t="s">
+        <v>4161</v>
+      </c>
+      <c r="G1014" s="2" t="s">
+        <v>4162</v>
+      </c>
+      <c r="H1014" s="2" t="s">
+        <v>4163</v>
+      </c>
+      <c r="I1014" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1014" s="3" t="s">
+        <v>4164</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:10">
+      <c r="A1015" s="2">
+        <v>1014</v>
+      </c>
+      <c r="B1015" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1015" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1015" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1015" s="2" t="s">
+        <v>4124</v>
+      </c>
+      <c r="F1015" s="2" t="s">
+        <v>4165</v>
+      </c>
+      <c r="G1015" s="2" t="s">
+        <v>4166</v>
+      </c>
+      <c r="H1015" s="2" t="s">
+        <v>4167</v>
+      </c>
+      <c r="I1015" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1015" s="3" t="s">
+        <v>4168</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:10">
+      <c r="A1016" s="2">
+        <v>1015</v>
+      </c>
+      <c r="B1016" s="2" t="s">
+        <v>4042</v>
+      </c>
+      <c r="C1016" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1016" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1016" s="2" t="s">
+        <v>4124</v>
+      </c>
+      <c r="F1016" s="2" t="s">
+        <v>4169</v>
+      </c>
+      <c r="G1016" s="2" t="s">
+        <v>4170</v>
+      </c>
+      <c r="H1016" s="2" t="s">
+        <v>4171</v>
+      </c>
+      <c r="I1016" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1016" s="3" t="s">
+        <v>4172</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:10">
+      <c r="A1017" s="2">
+        <v>1016</v>
+      </c>
+      <c r="B1017" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1017" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1017" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1017" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1017" s="2" t="s">
+        <v>4175</v>
+      </c>
+      <c r="G1017" s="2" t="s">
+        <v>4176</v>
+      </c>
+      <c r="H1017" s="2" t="s">
+        <v>4177</v>
+      </c>
+      <c r="I1017" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1017" s="3" t="s">
+        <v>4178</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:10">
+      <c r="A1018" s="2">
+        <v>1017</v>
+      </c>
+      <c r="B1018" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1018" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1018" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1018" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1018" s="2" t="s">
+        <v>4179</v>
+      </c>
+      <c r="G1018" s="2" t="s">
+        <v>4180</v>
+      </c>
+      <c r="H1018" s="2" t="s">
+        <v>4181</v>
+      </c>
+      <c r="I1018" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1018" s="3" t="s">
+        <v>4182</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:10">
+      <c r="A1019" s="2">
+        <v>1018</v>
+      </c>
+      <c r="B1019" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1019" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1019" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1019" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1019" s="2" t="s">
+        <v>4183</v>
+      </c>
+      <c r="G1019" s="2" t="s">
+        <v>4184</v>
+      </c>
+      <c r="H1019" s="2" t="s">
+        <v>4185</v>
+      </c>
+      <c r="I1019" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1019" s="3" t="s">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:10">
+      <c r="A1020" s="2">
+        <v>1019</v>
+      </c>
+      <c r="B1020" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1020" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1020" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1020" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1020" s="2" t="s">
+        <v>4187</v>
+      </c>
+      <c r="G1020" s="2" t="s">
+        <v>4188</v>
+      </c>
+      <c r="H1020" s="2" t="s">
+        <v>4189</v>
+      </c>
+      <c r="I1020" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1020" s="3" t="s">
+        <v>4190</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:10">
+      <c r="A1021" s="2">
+        <v>1020</v>
+      </c>
+      <c r="B1021" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1021" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1021" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1021" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1021" s="2" t="s">
+        <v>4191</v>
+      </c>
+      <c r="G1021" s="2" t="s">
+        <v>4192</v>
+      </c>
+      <c r="H1021" s="2" t="s">
+        <v>4193</v>
+      </c>
+      <c r="I1021" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1021" s="3" t="s">
+        <v>4194</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:10">
+      <c r="A1022" s="2">
+        <v>1021</v>
+      </c>
+      <c r="B1022" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1022" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1022" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1022" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1022" s="2" t="s">
+        <v>4195</v>
+      </c>
+      <c r="G1022" s="2" t="s">
+        <v>4196</v>
+      </c>
+      <c r="H1022" s="2" t="s">
+        <v>4197</v>
+      </c>
+      <c r="I1022" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1022" s="3" t="s">
+        <v>4198</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:10">
+      <c r="A1023" s="2">
+        <v>1022</v>
+      </c>
+      <c r="B1023" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1023" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1023" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1023" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1023" s="2" t="s">
+        <v>4199</v>
+      </c>
+      <c r="G1023" s="2" t="s">
+        <v>4200</v>
+      </c>
+      <c r="H1023" s="2" t="s">
+        <v>4201</v>
+      </c>
+      <c r="I1023" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1023" s="3" t="s">
+        <v>4202</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:10">
+      <c r="A1024" s="2">
+        <v>1023</v>
+      </c>
+      <c r="B1024" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1024" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1024" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1024" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1024" s="2" t="s">
+        <v>4203</v>
+      </c>
+      <c r="G1024" s="2" t="s">
+        <v>4204</v>
+      </c>
+      <c r="H1024" s="2" t="s">
+        <v>4205</v>
+      </c>
+      <c r="I1024" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1024" s="3" t="s">
+        <v>4206</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:10">
+      <c r="A1025" s="2">
+        <v>1024</v>
+      </c>
+      <c r="B1025" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1025" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1025" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1025" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1025" s="2" t="s">
+        <v>4207</v>
+      </c>
+      <c r="G1025" s="2" t="s">
+        <v>4208</v>
+      </c>
+      <c r="H1025" s="2" t="s">
+        <v>4209</v>
+      </c>
+      <c r="I1025" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1025" s="3" t="s">
+        <v>4210</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:10">
+      <c r="A1026" s="2">
+        <v>1025</v>
+      </c>
+      <c r="B1026" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1026" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1026" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1026" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1026" s="2" t="s">
+        <v>4211</v>
+      </c>
+      <c r="G1026" s="2" t="s">
+        <v>4212</v>
+      </c>
+      <c r="H1026" s="2" t="s">
+        <v>4213</v>
+      </c>
+      <c r="I1026" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1026" s="3" t="s">
+        <v>4214</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:10">
+      <c r="A1027" s="2">
+        <v>1026</v>
+      </c>
+      <c r="B1027" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1027" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1027" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1027" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1027" s="2" t="s">
+        <v>4215</v>
+      </c>
+      <c r="G1027" s="2" t="s">
+        <v>4216</v>
+      </c>
+      <c r="H1027" s="2" t="s">
+        <v>4217</v>
+      </c>
+      <c r="I1027" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1027" s="3" t="s">
+        <v>4218</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:10">
+      <c r="A1028" s="2">
+        <v>1027</v>
+      </c>
+      <c r="B1028" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1028" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1028" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1028" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1028" s="2" t="s">
+        <v>4219</v>
+      </c>
+      <c r="G1028" s="2" t="s">
+        <v>4220</v>
+      </c>
+      <c r="H1028" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1028" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1028" s="3" t="s">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:10">
+      <c r="A1029" s="2">
+        <v>1028</v>
+      </c>
+      <c r="B1029" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1029" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1029" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1029" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1029" s="2" t="s">
+        <v>4222</v>
+      </c>
+      <c r="G1029" s="2" t="s">
+        <v>4223</v>
+      </c>
+      <c r="H1029" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1029" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1029" s="3" t="s">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:10">
+      <c r="A1030" s="2">
+        <v>1029</v>
+      </c>
+      <c r="B1030" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1030" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1030" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1030" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1030" s="2" t="s">
+        <v>4225</v>
+      </c>
+      <c r="G1030" s="2" t="s">
+        <v>4226</v>
+      </c>
+      <c r="H1030" s="2" t="s">
+        <v>4227</v>
+      </c>
+      <c r="I1030" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1030" s="3" t="s">
+        <v>4228</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:10">
+      <c r="A1031" s="2">
+        <v>1030</v>
+      </c>
+      <c r="B1031" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1031" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1031" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1031" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1031" s="2" t="s">
+        <v>4229</v>
+      </c>
+      <c r="G1031" s="2" t="s">
+        <v>4230</v>
+      </c>
+      <c r="H1031" s="2" t="s">
+        <v>4231</v>
+      </c>
+      <c r="I1031" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1031" s="3" t="s">
+        <v>4232</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:10">
+      <c r="A1032" s="2">
+        <v>1031</v>
+      </c>
+      <c r="B1032" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1032" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1032" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1032" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1032" s="2" t="s">
+        <v>4233</v>
+      </c>
+      <c r="G1032" s="2" t="s">
+        <v>4234</v>
+      </c>
+      <c r="H1032" s="2" t="s">
+        <v>4235</v>
+      </c>
+      <c r="I1032" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1032" s="3" t="s">
+        <v>4236</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:10">
+      <c r="A1033" s="2">
+        <v>1032</v>
+      </c>
+      <c r="B1033" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1033" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1033" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1033" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1033" s="2" t="s">
+        <v>4237</v>
+      </c>
+      <c r="G1033" s="2" t="s">
+        <v>4238</v>
+      </c>
+      <c r="H1033" s="2" t="s">
+        <v>4239</v>
+      </c>
+      <c r="I1033" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1033" s="3" t="s">
+        <v>4240</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:10">
+      <c r="A1034" s="2">
+        <v>1033</v>
+      </c>
+      <c r="B1034" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1034" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1034" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1034" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1034" s="2" t="s">
+        <v>4241</v>
+      </c>
+      <c r="G1034" s="2" t="s">
+        <v>4242</v>
+      </c>
+      <c r="H1034" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1034" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1034" s="3" t="s">
+        <v>4243</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:10">
+      <c r="A1035" s="2">
+        <v>1034</v>
+      </c>
+      <c r="B1035" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1035" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1035" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1035" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1035" s="2" t="s">
+        <v>4244</v>
+      </c>
+      <c r="G1035" s="2" t="s">
+        <v>4245</v>
+      </c>
+      <c r="H1035" s="2" t="s">
+        <v>4246</v>
+      </c>
+      <c r="I1035" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1035" s="3" t="s">
+        <v>4247</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:10">
+      <c r="A1036" s="2">
+        <v>1035</v>
+      </c>
+      <c r="B1036" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1036" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1036" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1036" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1036" s="2" t="s">
+        <v>4248</v>
+      </c>
+      <c r="G1036" s="2" t="s">
+        <v>4249</v>
+      </c>
+      <c r="H1036" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1036" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1036" s="3" t="s">
+        <v>4250</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:10">
+      <c r="A1037" s="2">
+        <v>1036</v>
+      </c>
+      <c r="B1037" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1037" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1037" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1037" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1037" s="2" t="s">
+        <v>4251</v>
+      </c>
+      <c r="G1037" s="2" t="s">
+        <v>4252</v>
+      </c>
+      <c r="H1037" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1037" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1037" s="3" t="s">
+        <v>4253</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:10">
+      <c r="A1038" s="2">
+        <v>1037</v>
+      </c>
+      <c r="B1038" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1038" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1038" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1038" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1038" s="2" t="s">
+        <v>4254</v>
+      </c>
+      <c r="G1038" s="2" t="s">
+        <v>4255</v>
+      </c>
+      <c r="H1038" s="2" t="s">
+        <v>4256</v>
+      </c>
+      <c r="I1038" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1038" s="3" t="s">
+        <v>4257</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:10">
+      <c r="A1039" s="2">
+        <v>1038</v>
+      </c>
+      <c r="B1039" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1039" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1039" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1039" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1039" s="2" t="s">
+        <v>4258</v>
+      </c>
+      <c r="G1039" s="2" t="s">
+        <v>4259</v>
+      </c>
+      <c r="H1039" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1039" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1039" s="3" t="s">
+        <v>4260</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:10">
+      <c r="A1040" s="2">
+        <v>1039</v>
+      </c>
+      <c r="B1040" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1040" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1040" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1040" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1040" s="2" t="s">
+        <v>4261</v>
+      </c>
+      <c r="G1040" s="2" t="s">
+        <v>4262</v>
+      </c>
+      <c r="H1040" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1040" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1040" s="3" t="s">
+        <v>4263</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:10">
+      <c r="A1041" s="2">
+        <v>1040</v>
+      </c>
+      <c r="B1041" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1041" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1041" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1041" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1041" s="2" t="s">
+        <v>4264</v>
+      </c>
+      <c r="G1041" s="2" t="s">
+        <v>4265</v>
+      </c>
+      <c r="H1041" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1041" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1041" s="3" t="s">
+        <v>4266</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:10">
+      <c r="A1042" s="2">
+        <v>1041</v>
+      </c>
+      <c r="B1042" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1042" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1042" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1042" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1042" s="2" t="s">
+        <v>4267</v>
+      </c>
+      <c r="G1042" s="2" t="s">
+        <v>4268</v>
+      </c>
+      <c r="H1042" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1042" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1042" s="3" t="s">
+        <v>4269</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:10">
+      <c r="A1043" s="2">
+        <v>1042</v>
+      </c>
+      <c r="B1043" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1043" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1043" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1043" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1043" s="2" t="s">
+        <v>4270</v>
+      </c>
+      <c r="G1043" s="2" t="s">
+        <v>4271</v>
+      </c>
+      <c r="H1043" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1043" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1043" s="3" t="s">
+        <v>4272</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:10">
+      <c r="A1044" s="2">
+        <v>1043</v>
+      </c>
+      <c r="B1044" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1044" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1044" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1044" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1044" s="2" t="s">
+        <v>4273</v>
+      </c>
+      <c r="G1044" s="2" t="s">
+        <v>4274</v>
+      </c>
+      <c r="H1044" s="2" t="s">
+        <v>4275</v>
+      </c>
+      <c r="I1044" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1044" s="3" t="s">
+        <v>4276</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:10">
+      <c r="A1045" s="2">
+        <v>1044</v>
+      </c>
+      <c r="B1045" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1045" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1045" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1045" s="2" t="s">
+        <v>4174</v>
+      </c>
+      <c r="F1045" s="2" t="s">
+        <v>4277</v>
+      </c>
+      <c r="G1045" s="2" t="s">
+        <v>4278</v>
+      </c>
+      <c r="H1045" s="2" t="s">
+        <v>4279</v>
+      </c>
+      <c r="I1045" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1045" s="3" t="s">
+        <v>4280</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:10">
+      <c r="A1046" s="2">
+        <v>1045</v>
+      </c>
+      <c r="B1046" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1046" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1046" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1046" s="2" t="s">
+        <v>4281</v>
+      </c>
+      <c r="F1046" s="2" t="s">
+        <v>4282</v>
+      </c>
+      <c r="G1046" s="2" t="s">
+        <v>4283</v>
+      </c>
+      <c r="H1046" s="2" t="s">
+        <v>4284</v>
+      </c>
+      <c r="I1046" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1046" s="3" t="s">
+        <v>4285</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:10">
+      <c r="A1047" s="2">
+        <v>1046</v>
+      </c>
+      <c r="B1047" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1047" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1047" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1047" s="2" t="s">
+        <v>4281</v>
+      </c>
+      <c r="F1047" s="2" t="s">
+        <v>4286</v>
+      </c>
+      <c r="G1047" s="2" t="s">
+        <v>4287</v>
+      </c>
+      <c r="H1047" s="2" t="s">
+        <v>4288</v>
+      </c>
+      <c r="I1047" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1047" s="3" t="s">
+        <v>4289</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:10">
+      <c r="A1048" s="2">
+        <v>1047</v>
+      </c>
+      <c r="B1048" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1048" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1048" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1048" s="2" t="s">
+        <v>4281</v>
+      </c>
+      <c r="F1048" s="2" t="s">
+        <v>4290</v>
+      </c>
+      <c r="G1048" s="2" t="s">
+        <v>4291</v>
+      </c>
+      <c r="H1048" s="2" t="s">
+        <v>4292</v>
+      </c>
+      <c r="I1048" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1048" s="3" t="s">
+        <v>4293</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:10">
+      <c r="A1049" s="2">
+        <v>1048</v>
+      </c>
+      <c r="B1049" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1049" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1049" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1049" s="2" t="s">
+        <v>4281</v>
+      </c>
+      <c r="F1049" s="2" t="s">
+        <v>4294</v>
+      </c>
+      <c r="G1049" s="2" t="s">
+        <v>4295</v>
+      </c>
+      <c r="H1049" s="2" t="s">
+        <v>4296</v>
+      </c>
+      <c r="I1049" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1049" s="3" t="s">
+        <v>4297</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:10">
+      <c r="A1050" s="2">
+        <v>1049</v>
+      </c>
+      <c r="B1050" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1050" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1050" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1050" s="2" t="s">
+        <v>4281</v>
+      </c>
+      <c r="F1050" s="2" t="s">
+        <v>4298</v>
+      </c>
+      <c r="G1050" s="2" t="s">
+        <v>4299</v>
+      </c>
+      <c r="H1050" s="2" t="s">
+        <v>4300</v>
+      </c>
+      <c r="I1050" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1050" s="3" t="s">
+        <v>4301</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:10">
+      <c r="A1051" s="2">
+        <v>1050</v>
+      </c>
+      <c r="B1051" s="2" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1051" s="2" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1051" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1051" s="2" t="s">
+        <v>4281</v>
+      </c>
+      <c r="F1051" s="2" t="s">
+        <v>4302</v>
+      </c>
+      <c r="G1051" s="2" t="s">
+        <v>4303</v>
+      </c>
+      <c r="H1051" s="2" t="s">
+        <v>4304</v>
+      </c>
+      <c r="I1051" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1051" s="3" t="s">
+        <v>4305</v>
       </c>
     </row>
   </sheetData>
@@ -40257,6 +47828,183 @@
     <hyperlink ref="J874" r:id="rId874"/>
     <hyperlink ref="J875" r:id="rId875"/>
     <hyperlink ref="J876" r:id="rId876"/>
+    <hyperlink ref="J877" r:id="rId877"/>
+    <hyperlink ref="J878" r:id="rId878"/>
+    <hyperlink ref="J879" r:id="rId879"/>
+    <hyperlink ref="J880" r:id="rId880"/>
+    <hyperlink ref="J881" r:id="rId881"/>
+    <hyperlink ref="J882" r:id="rId882"/>
+    <hyperlink ref="J883" r:id="rId883"/>
+    <hyperlink ref="G884" r:id="rId884"/>
+    <hyperlink ref="J884" r:id="rId885"/>
+    <hyperlink ref="J885" r:id="rId886"/>
+    <hyperlink ref="J886" r:id="rId887"/>
+    <hyperlink ref="J887" r:id="rId888"/>
+    <hyperlink ref="J888" r:id="rId889"/>
+    <hyperlink ref="J889" r:id="rId890"/>
+    <hyperlink ref="J890" r:id="rId891"/>
+    <hyperlink ref="J891" r:id="rId892"/>
+    <hyperlink ref="J892" r:id="rId893"/>
+    <hyperlink ref="J893" r:id="rId894"/>
+    <hyperlink ref="J894" r:id="rId895"/>
+    <hyperlink ref="J895" r:id="rId896"/>
+    <hyperlink ref="J896" r:id="rId897"/>
+    <hyperlink ref="J897" r:id="rId898"/>
+    <hyperlink ref="J898" r:id="rId899"/>
+    <hyperlink ref="J899" r:id="rId900"/>
+    <hyperlink ref="J900" r:id="rId901"/>
+    <hyperlink ref="J901" r:id="rId902"/>
+    <hyperlink ref="J902" r:id="rId903"/>
+    <hyperlink ref="J903" r:id="rId904"/>
+    <hyperlink ref="J904" r:id="rId905"/>
+    <hyperlink ref="J905" r:id="rId906"/>
+    <hyperlink ref="J906" r:id="rId907"/>
+    <hyperlink ref="J907" r:id="rId908"/>
+    <hyperlink ref="J908" r:id="rId909"/>
+    <hyperlink ref="G909" r:id="rId910"/>
+    <hyperlink ref="J909" r:id="rId911"/>
+    <hyperlink ref="J910" r:id="rId912"/>
+    <hyperlink ref="J911" r:id="rId913"/>
+    <hyperlink ref="J912" r:id="rId914"/>
+    <hyperlink ref="J913" r:id="rId915"/>
+    <hyperlink ref="J914" r:id="rId916"/>
+    <hyperlink ref="J915" r:id="rId917"/>
+    <hyperlink ref="J916" r:id="rId918"/>
+    <hyperlink ref="J917" r:id="rId919"/>
+    <hyperlink ref="J918" r:id="rId920"/>
+    <hyperlink ref="J919" r:id="rId921"/>
+    <hyperlink ref="J920" r:id="rId922"/>
+    <hyperlink ref="J921" r:id="rId923"/>
+    <hyperlink ref="J922" r:id="rId924"/>
+    <hyperlink ref="J923" r:id="rId925"/>
+    <hyperlink ref="J924" r:id="rId926"/>
+    <hyperlink ref="J925" r:id="rId927"/>
+    <hyperlink ref="J926" r:id="rId928"/>
+    <hyperlink ref="J927" r:id="rId929"/>
+    <hyperlink ref="J928" r:id="rId930"/>
+    <hyperlink ref="J929" r:id="rId931"/>
+    <hyperlink ref="J930" r:id="rId932"/>
+    <hyperlink ref="J931" r:id="rId933"/>
+    <hyperlink ref="J932" r:id="rId934"/>
+    <hyperlink ref="J933" r:id="rId935"/>
+    <hyperlink ref="J934" r:id="rId936"/>
+    <hyperlink ref="J935" r:id="rId937"/>
+    <hyperlink ref="J936" r:id="rId938"/>
+    <hyperlink ref="J937" r:id="rId939"/>
+    <hyperlink ref="J938" r:id="rId940"/>
+    <hyperlink ref="J939" r:id="rId941"/>
+    <hyperlink ref="J940" r:id="rId942"/>
+    <hyperlink ref="J941" r:id="rId943"/>
+    <hyperlink ref="J942" r:id="rId944"/>
+    <hyperlink ref="J943" r:id="rId945"/>
+    <hyperlink ref="J944" r:id="rId946"/>
+    <hyperlink ref="J945" r:id="rId947"/>
+    <hyperlink ref="J946" r:id="rId948"/>
+    <hyperlink ref="J947" r:id="rId949"/>
+    <hyperlink ref="J948" r:id="rId950"/>
+    <hyperlink ref="J949" r:id="rId951"/>
+    <hyperlink ref="J950" r:id="rId952"/>
+    <hyperlink ref="J951" r:id="rId953"/>
+    <hyperlink ref="J952" r:id="rId954"/>
+    <hyperlink ref="J953" r:id="rId955"/>
+    <hyperlink ref="J954" r:id="rId956"/>
+    <hyperlink ref="J955" r:id="rId957"/>
+    <hyperlink ref="J956" r:id="rId958"/>
+    <hyperlink ref="J957" r:id="rId959"/>
+    <hyperlink ref="J958" r:id="rId960"/>
+    <hyperlink ref="J959" r:id="rId961"/>
+    <hyperlink ref="J960" r:id="rId962"/>
+    <hyperlink ref="J961" r:id="rId963"/>
+    <hyperlink ref="J962" r:id="rId964"/>
+    <hyperlink ref="J963" r:id="rId965"/>
+    <hyperlink ref="J964" r:id="rId966"/>
+    <hyperlink ref="J965" r:id="rId967"/>
+    <hyperlink ref="J966" r:id="rId968"/>
+    <hyperlink ref="J967" r:id="rId969"/>
+    <hyperlink ref="J968" r:id="rId970"/>
+    <hyperlink ref="J969" r:id="rId971"/>
+    <hyperlink ref="J970" r:id="rId972"/>
+    <hyperlink ref="J971" r:id="rId973"/>
+    <hyperlink ref="J972" r:id="rId974"/>
+    <hyperlink ref="J973" r:id="rId975"/>
+    <hyperlink ref="J974" r:id="rId976"/>
+    <hyperlink ref="J975" r:id="rId977"/>
+    <hyperlink ref="J976" r:id="rId978"/>
+    <hyperlink ref="J977" r:id="rId979"/>
+    <hyperlink ref="J978" r:id="rId980"/>
+    <hyperlink ref="J979" r:id="rId981"/>
+    <hyperlink ref="J980" r:id="rId982"/>
+    <hyperlink ref="J981" r:id="rId983"/>
+    <hyperlink ref="J982" r:id="rId984"/>
+    <hyperlink ref="J983" r:id="rId985"/>
+    <hyperlink ref="J984" r:id="rId986"/>
+    <hyperlink ref="J985" r:id="rId987"/>
+    <hyperlink ref="J986" r:id="rId988"/>
+    <hyperlink ref="J987" r:id="rId989"/>
+    <hyperlink ref="J988" r:id="rId990"/>
+    <hyperlink ref="J989" r:id="rId991"/>
+    <hyperlink ref="J990" r:id="rId992"/>
+    <hyperlink ref="J991" r:id="rId993"/>
+    <hyperlink ref="J992" r:id="rId994"/>
+    <hyperlink ref="J993" r:id="rId995"/>
+    <hyperlink ref="J994" r:id="rId996"/>
+    <hyperlink ref="J995" r:id="rId997"/>
+    <hyperlink ref="J996" r:id="rId998"/>
+    <hyperlink ref="J997" r:id="rId999"/>
+    <hyperlink ref="J998" r:id="rId1000"/>
+    <hyperlink ref="J999" r:id="rId1001"/>
+    <hyperlink ref="J1000" r:id="rId1002"/>
+    <hyperlink ref="J1001" r:id="rId1003"/>
+    <hyperlink ref="J1002" r:id="rId1004"/>
+    <hyperlink ref="J1003" r:id="rId1005"/>
+    <hyperlink ref="J1004" r:id="rId1006"/>
+    <hyperlink ref="J1005" r:id="rId1007"/>
+    <hyperlink ref="J1006" r:id="rId1008"/>
+    <hyperlink ref="J1007" r:id="rId1009"/>
+    <hyperlink ref="J1008" r:id="rId1010"/>
+    <hyperlink ref="J1009" r:id="rId1011"/>
+    <hyperlink ref="J1010" r:id="rId1012"/>
+    <hyperlink ref="J1011" r:id="rId1013"/>
+    <hyperlink ref="J1012" r:id="rId1014"/>
+    <hyperlink ref="J1013" r:id="rId1015"/>
+    <hyperlink ref="J1014" r:id="rId1016"/>
+    <hyperlink ref="J1015" r:id="rId1017"/>
+    <hyperlink ref="J1016" r:id="rId1018"/>
+    <hyperlink ref="J1017" r:id="rId1019"/>
+    <hyperlink ref="J1018" r:id="rId1020"/>
+    <hyperlink ref="J1019" r:id="rId1021"/>
+    <hyperlink ref="J1020" r:id="rId1022"/>
+    <hyperlink ref="J1021" r:id="rId1023"/>
+    <hyperlink ref="J1022" r:id="rId1024"/>
+    <hyperlink ref="J1023" r:id="rId1025"/>
+    <hyperlink ref="J1024" r:id="rId1026"/>
+    <hyperlink ref="J1025" r:id="rId1027"/>
+    <hyperlink ref="J1026" r:id="rId1028"/>
+    <hyperlink ref="J1027" r:id="rId1029"/>
+    <hyperlink ref="J1028" r:id="rId1030"/>
+    <hyperlink ref="J1029" r:id="rId1031"/>
+    <hyperlink ref="J1030" r:id="rId1032"/>
+    <hyperlink ref="J1031" r:id="rId1033"/>
+    <hyperlink ref="J1032" r:id="rId1034"/>
+    <hyperlink ref="J1033" r:id="rId1035"/>
+    <hyperlink ref="J1034" r:id="rId1036"/>
+    <hyperlink ref="J1035" r:id="rId1037"/>
+    <hyperlink ref="J1036" r:id="rId1038"/>
+    <hyperlink ref="J1037" r:id="rId1039"/>
+    <hyperlink ref="J1038" r:id="rId1040"/>
+    <hyperlink ref="J1039" r:id="rId1041"/>
+    <hyperlink ref="J1040" r:id="rId1042"/>
+    <hyperlink ref="J1041" r:id="rId1043"/>
+    <hyperlink ref="J1042" r:id="rId1044"/>
+    <hyperlink ref="J1043" r:id="rId1045"/>
+    <hyperlink ref="J1044" r:id="rId1046"/>
+    <hyperlink ref="J1045" r:id="rId1047"/>
+    <hyperlink ref="J1046" r:id="rId1048"/>
+    <hyperlink ref="J1047" r:id="rId1049"/>
+    <hyperlink ref="J1048" r:id="rId1050"/>
+    <hyperlink ref="J1049" r:id="rId1051"/>
+    <hyperlink ref="J1050" r:id="rId1052"/>
+    <hyperlink ref="J1051" r:id="rId1053"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
